--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -15966,10 +15966,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>117443188</v>
+        <v>117442206</v>
       </c>
       <c r="B142" t="n">
-        <v>97857</v>
+        <v>90517</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15978,25 +15978,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>478607</v>
+        <v>479018</v>
       </c>
       <c r="R142" t="n">
-        <v>7034343</v>
+        <v>7034302</v>
       </c>
       <c r="S142" t="n">
         <v>20</v>
@@ -16068,10 +16068,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>117444411</v>
+        <v>117442455</v>
       </c>
       <c r="B143" t="n">
-        <v>79527</v>
+        <v>90499</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16080,25 +16080,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229748</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16108,10 +16108,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>478515</v>
+        <v>478995</v>
       </c>
       <c r="R143" t="n">
-        <v>7034191</v>
+        <v>7034485</v>
       </c>
       <c r="S143" t="n">
         <v>20</v>
@@ -16170,10 +16170,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>117442455</v>
+        <v>117444567</v>
       </c>
       <c r="B144" t="n">
-        <v>90499</v>
+        <v>97742</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16182,38 +16182,42 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>504</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>478995</v>
+        <v>478429</v>
       </c>
       <c r="R144" t="n">
-        <v>7034485</v>
+        <v>7034123</v>
       </c>
       <c r="S144" t="n">
         <v>20</v>
@@ -16248,12 +16252,18 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ett stort antal spridda över hela sumpskogen.</t>
+        </is>
+      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -16272,10 +16282,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>117444567</v>
+        <v>117444345</v>
       </c>
       <c r="B145" t="n">
-        <v>97742</v>
+        <v>96954</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16288,38 +16298,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>504</v>
+        <v>222741</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>478429</v>
+        <v>478544</v>
       </c>
       <c r="R145" t="n">
-        <v>7034123</v>
+        <v>7034199</v>
       </c>
       <c r="S145" t="n">
         <v>20</v>
@@ -16354,18 +16360,12 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Ett stort antal spridda över hela sumpskogen.</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -16384,10 +16384,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>117444345</v>
+        <v>117444411</v>
       </c>
       <c r="B146" t="n">
-        <v>96954</v>
+        <v>79527</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16400,21 +16400,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>222741</v>
+        <v>229748</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16424,10 +16424,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>478544</v>
+        <v>478515</v>
       </c>
       <c r="R146" t="n">
-        <v>7034199</v>
+        <v>7034191</v>
       </c>
       <c r="S146" t="n">
         <v>20</v>
@@ -16486,10 +16486,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>117442206</v>
+        <v>117443188</v>
       </c>
       <c r="B147" t="n">
-        <v>90517</v>
+        <v>97857</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16498,25 +16498,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16526,10 +16526,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>479018</v>
+        <v>478607</v>
       </c>
       <c r="R147" t="n">
-        <v>7034302</v>
+        <v>7034343</v>
       </c>
       <c r="S147" t="n">
         <v>20</v>
@@ -16588,10 +16588,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>117546452</v>
+        <v>117444330</v>
       </c>
       <c r="B148" t="n">
-        <v>90841</v>
+        <v>74583</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16604,21 +16604,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2062</v>
+        <v>492</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16627,17 +16627,17 @@
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Stenbäcken, Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>478487</v>
+        <v>478550</v>
       </c>
       <c r="R148" t="n">
-        <v>7034175</v>
+        <v>7034207</v>
       </c>
       <c r="S148" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16667,6 +16667,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>På grov björkstubbe</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16678,6 +16683,11 @@
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
@@ -16694,10 +16704,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>117546456</v>
+        <v>117546452</v>
       </c>
       <c r="B149" t="n">
-        <v>90499</v>
+        <v>90841</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16706,25 +16716,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16800,10 +16810,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>117444330</v>
+        <v>117546456</v>
       </c>
       <c r="B150" t="n">
-        <v>74583</v>
+        <v>90499</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16812,25 +16822,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16839,17 +16849,17 @@
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478550</v>
+        <v>478487</v>
       </c>
       <c r="R150" t="n">
-        <v>7034207</v>
+        <v>7034175</v>
       </c>
       <c r="S150" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16879,11 +16889,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>På grov björkstubbe</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16895,11 +16900,6 @@
       <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
@@ -16916,10 +16916,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>117786220</v>
+        <v>117787185</v>
       </c>
       <c r="B151" t="n">
-        <v>91195</v>
+        <v>74584</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16928,25 +16928,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>67</v>
+        <v>308</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16956,10 +16956,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478538</v>
+        <v>478201</v>
       </c>
       <c r="R151" t="n">
-        <v>7034581</v>
+        <v>7035191</v>
       </c>
       <c r="S151" t="n">
         <v>20</v>
@@ -17018,10 +17018,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>117787995</v>
+        <v>117787464</v>
       </c>
       <c r="B152" t="n">
-        <v>104914</v>
+        <v>82259</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17030,38 +17030,38 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221725</v>
+        <v>1312</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Landvågen (Landvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>477885</v>
+        <v>478160</v>
       </c>
       <c r="R152" t="n">
-        <v>7035557</v>
+        <v>7035272</v>
       </c>
       <c r="S152" t="n">
         <v>20</v>
@@ -17222,10 +17222,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>117787185</v>
+        <v>117787692</v>
       </c>
       <c r="B154" t="n">
-        <v>74584</v>
+        <v>80437</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17238,34 +17238,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>478201</v>
+        <v>478112</v>
       </c>
       <c r="R154" t="n">
-        <v>7035191</v>
+        <v>7035369</v>
       </c>
       <c r="S154" t="n">
         <v>20</v>
@@ -17306,6 +17309,7 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17324,10 +17328,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>117787464</v>
+        <v>117790359</v>
       </c>
       <c r="B155" t="n">
-        <v>82259</v>
+        <v>90499</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17340,21 +17344,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17364,10 +17368,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>478160</v>
+        <v>478427</v>
       </c>
       <c r="R155" t="n">
-        <v>7035272</v>
+        <v>7034145</v>
       </c>
       <c r="S155" t="n">
         <v>20</v>
@@ -17528,10 +17532,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>117791178</v>
+        <v>117788387</v>
       </c>
       <c r="B157" t="n">
-        <v>74583</v>
+        <v>100007</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17540,38 +17544,38 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>492</v>
+        <v>222771</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Landvågen (Landvågen), Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>478368</v>
+        <v>477820</v>
       </c>
       <c r="R157" t="n">
-        <v>7034114</v>
+        <v>7035670</v>
       </c>
       <c r="S157" t="n">
         <v>20</v>
@@ -17630,10 +17634,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>117787893</v>
+        <v>117790354</v>
       </c>
       <c r="B158" t="n">
-        <v>90495</v>
+        <v>90782</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17646,21 +17650,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17670,10 +17674,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>477931</v>
+        <v>478427</v>
       </c>
       <c r="R158" t="n">
-        <v>7035494</v>
+        <v>7034145</v>
       </c>
       <c r="S158" t="n">
         <v>20</v>
@@ -17732,10 +17736,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>117788387</v>
+        <v>117791178</v>
       </c>
       <c r="B159" t="n">
-        <v>100007</v>
+        <v>74583</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17744,38 +17748,38 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>222771</v>
+        <v>492</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Landvågen (Landvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>477820</v>
+        <v>478368</v>
       </c>
       <c r="R159" t="n">
-        <v>7035670</v>
+        <v>7034114</v>
       </c>
       <c r="S159" t="n">
         <v>20</v>
@@ -17936,10 +17940,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>117790354</v>
+        <v>117787995</v>
       </c>
       <c r="B161" t="n">
-        <v>90782</v>
+        <v>104914</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17948,38 +17952,38 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>658</v>
+        <v>221725</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Landvågen (Landvågen), Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>478427</v>
+        <v>477885</v>
       </c>
       <c r="R161" t="n">
-        <v>7034145</v>
+        <v>7035557</v>
       </c>
       <c r="S161" t="n">
         <v>20</v>
@@ -18038,10 +18042,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>117790359</v>
+        <v>117787893</v>
       </c>
       <c r="B162" t="n">
-        <v>90499</v>
+        <v>90495</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18054,21 +18058,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18078,10 +18082,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478427</v>
+        <v>477931</v>
       </c>
       <c r="R162" t="n">
-        <v>7034145</v>
+        <v>7035494</v>
       </c>
       <c r="S162" t="n">
         <v>20</v>
@@ -18140,10 +18144,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>117787692</v>
+        <v>117791069</v>
       </c>
       <c r="B163" t="n">
-        <v>80437</v>
+        <v>74584</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18156,37 +18160,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478112</v>
+        <v>478463</v>
       </c>
       <c r="R163" t="n">
-        <v>7035369</v>
+        <v>7034153</v>
       </c>
       <c r="S163" t="n">
         <v>20</v>
@@ -18227,7 +18228,6 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -18246,10 +18246,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>117791069</v>
+        <v>117786220</v>
       </c>
       <c r="B164" t="n">
-        <v>74584</v>
+        <v>91195</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18258,25 +18258,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>308</v>
+        <v>67</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18286,10 +18286,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478463</v>
+        <v>478538</v>
       </c>
       <c r="R164" t="n">
-        <v>7034153</v>
+        <v>7034581</v>
       </c>
       <c r="S164" t="n">
         <v>20</v>
@@ -18348,10 +18348,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>117919042</v>
+        <v>117919197</v>
       </c>
       <c r="B165" t="n">
-        <v>79562</v>
+        <v>91195</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18360,45 +18360,38 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2081</v>
+        <v>67</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>478388</v>
+        <v>478228</v>
       </c>
       <c r="R165" t="n">
-        <v>7034926</v>
+        <v>7035109</v>
       </c>
       <c r="S165" t="n">
         <v>20</v>
@@ -18439,7 +18432,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -18458,10 +18450,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>117919197</v>
+        <v>117918578</v>
       </c>
       <c r="B166" t="n">
-        <v>91195</v>
+        <v>86816</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18470,25 +18462,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>67</v>
+        <v>510</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18498,10 +18490,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478228</v>
+        <v>478699</v>
       </c>
       <c r="R166" t="n">
-        <v>7035109</v>
+        <v>7034732</v>
       </c>
       <c r="S166" t="n">
         <v>20</v>
@@ -18662,10 +18654,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>117918578</v>
+        <v>117919042</v>
       </c>
       <c r="B168" t="n">
-        <v>86816</v>
+        <v>79562</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18678,34 +18670,41 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478699</v>
+        <v>478388</v>
       </c>
       <c r="R168" t="n">
-        <v>7034732</v>
+        <v>7034926</v>
       </c>
       <c r="S168" t="n">
         <v>20</v>
@@ -18746,6 +18745,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -20387,10 +20387,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>117448244</v>
+        <v>117448064</v>
       </c>
       <c r="B184" t="n">
-        <v>90517</v>
+        <v>90495</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20403,21 +20403,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20427,10 +20427,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>477439</v>
+        <v>477365</v>
       </c>
       <c r="R184" t="n">
-        <v>7033047</v>
+        <v>7032988</v>
       </c>
       <c r="S184" t="n">
         <v>20</v>
@@ -20489,10 +20489,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>117448064</v>
+        <v>117448244</v>
       </c>
       <c r="B185" t="n">
-        <v>90495</v>
+        <v>90517</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20505,21 +20505,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20529,10 +20529,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>477365</v>
+        <v>477439</v>
       </c>
       <c r="R185" t="n">
-        <v>7032988</v>
+        <v>7033047</v>
       </c>
       <c r="S185" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>110968033</v>
       </c>
       <c r="B3" t="n">
-        <v>74583</v>
+        <v>74585</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -15966,10 +15966,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>117442206</v>
+        <v>117444567</v>
       </c>
       <c r="B142" t="n">
-        <v>90517</v>
+        <v>97744</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15978,38 +15978,42 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5432</v>
+        <v>504</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>479018</v>
+        <v>478429</v>
       </c>
       <c r="R142" t="n">
-        <v>7034302</v>
+        <v>7034123</v>
       </c>
       <c r="S142" t="n">
         <v>20</v>
@@ -16044,12 +16048,18 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ett stort antal spridda över hela sumpskogen.</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -16068,10 +16078,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>117442455</v>
+        <v>117443188</v>
       </c>
       <c r="B143" t="n">
-        <v>90499</v>
+        <v>97859</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16080,25 +16090,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16108,10 +16118,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>478995</v>
+        <v>478607</v>
       </c>
       <c r="R143" t="n">
-        <v>7034485</v>
+        <v>7034343</v>
       </c>
       <c r="S143" t="n">
         <v>20</v>
@@ -16170,10 +16180,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>117444567</v>
+        <v>117442206</v>
       </c>
       <c r="B144" t="n">
-        <v>97742</v>
+        <v>90519</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16182,42 +16192,38 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>504</v>
+        <v>5432</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>478429</v>
+        <v>479018</v>
       </c>
       <c r="R144" t="n">
-        <v>7034123</v>
+        <v>7034302</v>
       </c>
       <c r="S144" t="n">
         <v>20</v>
@@ -16252,18 +16258,12 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Ett stort antal spridda över hela sumpskogen.</t>
-        </is>
-      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -16282,10 +16282,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>117444345</v>
+        <v>117442455</v>
       </c>
       <c r="B145" t="n">
-        <v>96954</v>
+        <v>90501</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16294,25 +16294,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>222741</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16322,10 +16322,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>478544</v>
+        <v>478995</v>
       </c>
       <c r="R145" t="n">
-        <v>7034199</v>
+        <v>7034485</v>
       </c>
       <c r="S145" t="n">
         <v>20</v>
@@ -16387,7 +16387,7 @@
         <v>117444411</v>
       </c>
       <c r="B146" t="n">
-        <v>79527</v>
+        <v>79529</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16486,10 +16486,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>117443188</v>
+        <v>117444345</v>
       </c>
       <c r="B147" t="n">
-        <v>97857</v>
+        <v>96956</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16502,21 +16502,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>221952</v>
+        <v>222741</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16526,10 +16526,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>478607</v>
+        <v>478544</v>
       </c>
       <c r="R147" t="n">
-        <v>7034343</v>
+        <v>7034199</v>
       </c>
       <c r="S147" t="n">
         <v>20</v>
@@ -16591,7 +16591,7 @@
         <v>117444330</v>
       </c>
       <c r="B148" t="n">
-        <v>74583</v>
+        <v>74585</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>117546452</v>
       </c>
       <c r="B149" t="n">
-        <v>90841</v>
+        <v>90843</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>117546456</v>
       </c>
       <c r="B150" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16916,10 +16916,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>117787185</v>
+        <v>117787304</v>
       </c>
       <c r="B151" t="n">
-        <v>74584</v>
+        <v>94447</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16928,25 +16928,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>308</v>
+        <v>2682</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16956,10 +16956,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478201</v>
+        <v>478165</v>
       </c>
       <c r="R151" t="n">
-        <v>7035191</v>
+        <v>7035288</v>
       </c>
       <c r="S151" t="n">
         <v>20</v>
@@ -17018,10 +17018,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>117787464</v>
+        <v>117791069</v>
       </c>
       <c r="B152" t="n">
-        <v>82259</v>
+        <v>74586</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17034,21 +17034,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17058,10 +17058,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>478160</v>
+        <v>478463</v>
       </c>
       <c r="R152" t="n">
-        <v>7035272</v>
+        <v>7034153</v>
       </c>
       <c r="S152" t="n">
         <v>20</v>
@@ -17120,10 +17120,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>117787324</v>
+        <v>117787893</v>
       </c>
       <c r="B153" t="n">
-        <v>97740</v>
+        <v>90497</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17132,25 +17132,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220093</v>
+        <v>1108</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17160,10 +17160,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>478165</v>
+        <v>477931</v>
       </c>
       <c r="R153" t="n">
-        <v>7035288</v>
+        <v>7035494</v>
       </c>
       <c r="S153" t="n">
         <v>20</v>
@@ -17225,7 +17225,7 @@
         <v>117787692</v>
       </c>
       <c r="B154" t="n">
-        <v>80437</v>
+        <v>80439</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17328,10 +17328,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>117790359</v>
+        <v>117791178</v>
       </c>
       <c r="B155" t="n">
-        <v>90499</v>
+        <v>74585</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17340,25 +17340,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17368,10 +17368,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>478427</v>
+        <v>478368</v>
       </c>
       <c r="R155" t="n">
-        <v>7034145</v>
+        <v>7034114</v>
       </c>
       <c r="S155" t="n">
         <v>20</v>
@@ -17430,10 +17430,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>117787350</v>
+        <v>117790354</v>
       </c>
       <c r="B156" t="n">
-        <v>97857</v>
+        <v>90784</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17442,25 +17442,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17470,10 +17470,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>478165</v>
+        <v>478427</v>
       </c>
       <c r="R156" t="n">
-        <v>7035288</v>
+        <v>7034145</v>
       </c>
       <c r="S156" t="n">
         <v>20</v>
@@ -17532,10 +17532,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>117788387</v>
+        <v>117786220</v>
       </c>
       <c r="B157" t="n">
-        <v>100007</v>
+        <v>91197</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17544,38 +17544,38 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>222771</v>
+        <v>67</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Landvågen (Landvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>477820</v>
+        <v>478538</v>
       </c>
       <c r="R157" t="n">
-        <v>7035670</v>
+        <v>7034581</v>
       </c>
       <c r="S157" t="n">
         <v>20</v>
@@ -17634,10 +17634,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>117790354</v>
+        <v>117787464</v>
       </c>
       <c r="B158" t="n">
-        <v>90782</v>
+        <v>82261</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17650,21 +17650,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17674,10 +17674,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>478427</v>
+        <v>478160</v>
       </c>
       <c r="R158" t="n">
-        <v>7034145</v>
+        <v>7035272</v>
       </c>
       <c r="S158" t="n">
         <v>20</v>
@@ -17736,10 +17736,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>117791178</v>
+        <v>117787324</v>
       </c>
       <c r="B159" t="n">
-        <v>74583</v>
+        <v>97742</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17748,25 +17748,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>492</v>
+        <v>220093</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17776,10 +17776,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>478368</v>
+        <v>478165</v>
       </c>
       <c r="R159" t="n">
-        <v>7034114</v>
+        <v>7035288</v>
       </c>
       <c r="S159" t="n">
         <v>20</v>
@@ -17838,10 +17838,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>117787304</v>
+        <v>117790359</v>
       </c>
       <c r="B160" t="n">
-        <v>94445</v>
+        <v>90501</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17850,25 +17850,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2682</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17878,10 +17878,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>478165</v>
+        <v>478427</v>
       </c>
       <c r="R160" t="n">
-        <v>7035288</v>
+        <v>7034145</v>
       </c>
       <c r="S160" t="n">
         <v>20</v>
@@ -17940,10 +17940,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>117787995</v>
+        <v>117787185</v>
       </c>
       <c r="B161" t="n">
-        <v>104914</v>
+        <v>74586</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17952,38 +17952,38 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>221725</v>
+        <v>308</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Landvågen (Landvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>477885</v>
+        <v>478201</v>
       </c>
       <c r="R161" t="n">
-        <v>7035557</v>
+        <v>7035191</v>
       </c>
       <c r="S161" t="n">
         <v>20</v>
@@ -18042,10 +18042,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>117787893</v>
+        <v>117787350</v>
       </c>
       <c r="B162" t="n">
-        <v>90495</v>
+        <v>97859</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18054,25 +18054,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1108</v>
+        <v>221952</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18082,10 +18082,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>477931</v>
+        <v>478165</v>
       </c>
       <c r="R162" t="n">
-        <v>7035494</v>
+        <v>7035288</v>
       </c>
       <c r="S162" t="n">
         <v>20</v>
@@ -18144,10 +18144,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>117791069</v>
+        <v>117787995</v>
       </c>
       <c r="B163" t="n">
-        <v>74584</v>
+        <v>104916</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18156,38 +18156,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>308</v>
+        <v>221725</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Landvågen (Landvågen), Jmt</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478463</v>
+        <v>477885</v>
       </c>
       <c r="R163" t="n">
-        <v>7034153</v>
+        <v>7035557</v>
       </c>
       <c r="S163" t="n">
         <v>20</v>
@@ -18246,10 +18246,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>117786220</v>
+        <v>117788387</v>
       </c>
       <c r="B164" t="n">
-        <v>91195</v>
+        <v>100009</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18258,38 +18258,38 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>67</v>
+        <v>222771</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Landvågen (Landvågen), Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478538</v>
+        <v>477820</v>
       </c>
       <c r="R164" t="n">
-        <v>7034581</v>
+        <v>7035670</v>
       </c>
       <c r="S164" t="n">
         <v>20</v>
@@ -18351,7 +18351,7 @@
         <v>117919197</v>
       </c>
       <c r="B165" t="n">
-        <v>91195</v>
+        <v>91197</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18450,10 +18450,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>117918578</v>
+        <v>117919893</v>
       </c>
       <c r="B166" t="n">
-        <v>86816</v>
+        <v>90519</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18466,34 +18466,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Landvågen (Landvågen), Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478699</v>
+        <v>477826</v>
       </c>
       <c r="R166" t="n">
-        <v>7034732</v>
+        <v>7035676</v>
       </c>
       <c r="S166" t="n">
         <v>20</v>
@@ -18552,10 +18552,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>117919893</v>
+        <v>117918578</v>
       </c>
       <c r="B167" t="n">
-        <v>90517</v>
+        <v>86818</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18568,34 +18568,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Landvågen (Landvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>477826</v>
+        <v>478699</v>
       </c>
       <c r="R167" t="n">
-        <v>7035676</v>
+        <v>7034732</v>
       </c>
       <c r="S167" t="n">
         <v>20</v>
@@ -18657,7 +18657,7 @@
         <v>117919042</v>
       </c>
       <c r="B168" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>117792165</v>
       </c>
       <c r="B183" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>117448064</v>
       </c>
       <c r="B184" t="n">
-        <v>90495</v>
+        <v>90497</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>117448244</v>
       </c>
       <c r="B185" t="n">
-        <v>90517</v>
+        <v>90519</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -17430,10 +17430,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>117790354</v>
+        <v>117786220</v>
       </c>
       <c r="B156" t="n">
-        <v>90784</v>
+        <v>91197</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17442,25 +17442,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>658</v>
+        <v>67</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17470,10 +17470,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>478427</v>
+        <v>478538</v>
       </c>
       <c r="R156" t="n">
-        <v>7034145</v>
+        <v>7034581</v>
       </c>
       <c r="S156" t="n">
         <v>20</v>
@@ -17532,10 +17532,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>117786220</v>
+        <v>117790354</v>
       </c>
       <c r="B157" t="n">
-        <v>91197</v>
+        <v>90784</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17544,25 +17544,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>67</v>
+        <v>658</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17572,10 +17572,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>478538</v>
+        <v>478427</v>
       </c>
       <c r="R157" t="n">
-        <v>7034581</v>
+        <v>7034145</v>
       </c>
       <c r="S157" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY209"/>
+  <dimension ref="A1:AY211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19682,10 +19682,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>118698381</v>
+        <v>118701025</v>
       </c>
       <c r="B178" t="n">
-        <v>90039</v>
+        <v>97844</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19694,41 +19694,38 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5747</v>
+        <v>620</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>477867</v>
+        <v>478191</v>
       </c>
       <c r="R178" t="n">
-        <v>7035632</v>
+        <v>7033866</v>
       </c>
       <c r="S178" t="n">
         <v>20</v>
@@ -19769,7 +19766,6 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19788,10 +19784,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>118701025</v>
+        <v>118700473</v>
       </c>
       <c r="B179" t="n">
-        <v>97844</v>
+        <v>86820</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19804,21 +19800,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>620</v>
+        <v>510</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19828,10 +19824,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478191</v>
+        <v>478540</v>
       </c>
       <c r="R179" t="n">
-        <v>7033866</v>
+        <v>7034211</v>
       </c>
       <c r="S179" t="n">
         <v>20</v>
@@ -19890,10 +19886,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>118700473</v>
+        <v>118697531</v>
       </c>
       <c r="B180" t="n">
-        <v>86820</v>
+        <v>97745</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19902,38 +19898,38 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>510</v>
+        <v>219795</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478540</v>
+        <v>478312</v>
       </c>
       <c r="R180" t="n">
-        <v>7034211</v>
+        <v>7035206</v>
       </c>
       <c r="S180" t="n">
         <v>20</v>
@@ -19992,10 +19988,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>118697531</v>
+        <v>118696189</v>
       </c>
       <c r="B181" t="n">
-        <v>97745</v>
+        <v>83951</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20004,38 +20000,38 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>219795</v>
+        <v>5589</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478312</v>
+        <v>478945</v>
       </c>
       <c r="R181" t="n">
-        <v>7035206</v>
+        <v>7034451</v>
       </c>
       <c r="S181" t="n">
         <v>20</v>
@@ -20094,10 +20090,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>118696189</v>
+        <v>118697497</v>
       </c>
       <c r="B182" t="n">
-        <v>83951</v>
+        <v>94455</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20106,38 +20102,38 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5589</v>
+        <v>2682</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>478945</v>
+        <v>478312</v>
       </c>
       <c r="R182" t="n">
-        <v>7034451</v>
+        <v>7035206</v>
       </c>
       <c r="S182" t="n">
         <v>20</v>
@@ -20196,10 +20192,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>118697497</v>
+        <v>118700665</v>
       </c>
       <c r="B183" t="n">
-        <v>94455</v>
+        <v>83951</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20208,38 +20204,38 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2682</v>
+        <v>5589</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>478312</v>
+        <v>478375</v>
       </c>
       <c r="R183" t="n">
-        <v>7035206</v>
+        <v>7034114</v>
       </c>
       <c r="S183" t="n">
         <v>20</v>
@@ -20298,7 +20294,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>118700665</v>
+        <v>118696519</v>
       </c>
       <c r="B184" t="n">
         <v>83951</v>
@@ -20338,10 +20334,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>478375</v>
+        <v>478742</v>
       </c>
       <c r="R184" t="n">
-        <v>7034114</v>
+        <v>7034663</v>
       </c>
       <c r="S184" t="n">
         <v>20</v>
@@ -20400,10 +20396,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>118696519</v>
+        <v>118698082</v>
       </c>
       <c r="B185" t="n">
-        <v>83951</v>
+        <v>85791</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20412,38 +20408,41 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5589</v>
+        <v>236437</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>478742</v>
+        <v>478001</v>
       </c>
       <c r="R185" t="n">
-        <v>7034663</v>
+        <v>7035456</v>
       </c>
       <c r="S185" t="n">
         <v>20</v>
@@ -20484,6 +20483,7 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -20502,37 +20502,37 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>118698082</v>
+        <v>118698422</v>
       </c>
       <c r="B186" t="n">
-        <v>85791</v>
+        <v>90048</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>236437</v>
+        <v>5754</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20545,10 +20545,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>478001</v>
+        <v>477893</v>
       </c>
       <c r="R186" t="n">
-        <v>7035456</v>
+        <v>7035630</v>
       </c>
       <c r="S186" t="n">
         <v>20</v>
@@ -20608,53 +20608,50 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>118698422</v>
+        <v>118854701</v>
       </c>
       <c r="B187" t="n">
-        <v>90048</v>
+        <v>91436</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5754</v>
+        <v>4769</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>477893</v>
+        <v>478743</v>
       </c>
       <c r="R187" t="n">
-        <v>7035630</v>
+        <v>7034675</v>
       </c>
       <c r="S187" t="n">
         <v>20</v>
@@ -20681,12 +20678,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20695,7 +20692,6 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
-      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
@@ -20714,10 +20710,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>111901519</v>
+        <v>118858244</v>
       </c>
       <c r="B188" t="n">
-        <v>86371</v>
+        <v>86351</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20726,41 +20722,41 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4412</v>
+        <v>1988</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>477765</v>
+        <v>477907</v>
       </c>
       <c r="R188" t="n">
-        <v>7033404</v>
+        <v>7035514</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20784,12 +20780,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20804,22 +20800,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>111901546</v>
+        <v>111901519</v>
       </c>
       <c r="B189" t="n">
-        <v>56430</v>
+        <v>86371</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20832,38 +20828,34 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>477668</v>
+        <v>477765</v>
       </c>
       <c r="R189" t="n">
-        <v>7033374</v>
+        <v>7033404</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20896,11 +20888,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20927,7 +20914,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>111901547</v>
+        <v>111901546</v>
       </c>
       <c r="B190" t="n">
         <v>56430</v>
@@ -20971,10 +20958,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>477524</v>
+        <v>477668</v>
       </c>
       <c r="R190" t="n">
-        <v>7033330</v>
+        <v>7033374</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21011,7 +20998,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21038,7 +21025,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>111901551</v>
+        <v>111901547</v>
       </c>
       <c r="B191" t="n">
         <v>56430</v>
@@ -21082,10 +21069,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>477433</v>
+        <v>477524</v>
       </c>
       <c r="R191" t="n">
-        <v>7033429</v>
+        <v>7033330</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21149,10 +21136,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>111901518</v>
+        <v>111901551</v>
       </c>
       <c r="B192" t="n">
-        <v>86371</v>
+        <v>56430</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21165,34 +21152,38 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>477674</v>
+        <v>477433</v>
       </c>
       <c r="R192" t="n">
-        <v>7033500</v>
+        <v>7033429</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21225,6 +21216,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21251,10 +21247,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>111901587</v>
+        <v>111901518</v>
       </c>
       <c r="B193" t="n">
-        <v>56575</v>
+        <v>86371</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21267,46 +21263,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>103021</v>
+        <v>4412</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>477611</v>
+        <v>477674</v>
       </c>
       <c r="R193" t="n">
-        <v>7033311</v>
+        <v>7033500</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21365,10 +21349,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>111901548</v>
+        <v>111901587</v>
       </c>
       <c r="B194" t="n">
-        <v>56430</v>
+        <v>56575</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21381,38 +21365,46 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>477476</v>
+        <v>477611</v>
       </c>
       <c r="R194" t="n">
-        <v>7033385</v>
+        <v>7033311</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21445,11 +21437,6 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21476,10 +21463,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>111901618</v>
+        <v>111901548</v>
       </c>
       <c r="B195" t="n">
-        <v>85197</v>
+        <v>56430</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21492,34 +21479,38 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>249278</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>477471</v>
+        <v>477476</v>
       </c>
       <c r="R195" t="n">
-        <v>7033412</v>
+        <v>7033385</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21552,6 +21543,11 @@
       <c r="AA195" t="inlineStr">
         <is>
           <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21578,10 +21574,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>111901549</v>
+        <v>111901618</v>
       </c>
       <c r="B196" t="n">
-        <v>56430</v>
+        <v>85197</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21594,38 +21590,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100109</v>
+        <v>249278</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>477464</v>
+        <v>477471</v>
       </c>
       <c r="R196" t="n">
-        <v>7033364</v>
+        <v>7033412</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21658,11 +21650,6 @@
       <c r="AA196" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21689,7 +21676,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>111901544</v>
+        <v>111901549</v>
       </c>
       <c r="B197" t="n">
         <v>56430</v>
@@ -21733,10 +21720,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>477639</v>
+        <v>477464</v>
       </c>
       <c r="R197" t="n">
-        <v>7033515</v>
+        <v>7033364</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21773,7 +21760,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21800,7 +21787,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>111901550</v>
+        <v>111901544</v>
       </c>
       <c r="B198" t="n">
         <v>56430</v>
@@ -21844,10 +21831,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>477473</v>
+        <v>477639</v>
       </c>
       <c r="R198" t="n">
-        <v>7033404</v>
+        <v>7033515</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21911,7 +21898,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>111901545</v>
+        <v>111901550</v>
       </c>
       <c r="B199" t="n">
         <v>56430</v>
@@ -21955,10 +21942,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>477667</v>
+        <v>477473</v>
       </c>
       <c r="R199" t="n">
-        <v>7033500</v>
+        <v>7033404</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22022,10 +22009,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>117085837</v>
+        <v>111901545</v>
       </c>
       <c r="B200" t="n">
-        <v>90463</v>
+        <v>56430</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22038,37 +22025,41 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>477402</v>
+        <v>477667</v>
       </c>
       <c r="R200" t="n">
-        <v>7033066</v>
+        <v>7033500</v>
       </c>
       <c r="S200" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22092,12 +22083,17 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22112,22 +22108,22 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>117130130</v>
+        <v>117085837</v>
       </c>
       <c r="B201" t="n">
-        <v>91236</v>
+        <v>90463</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22136,44 +22132,41 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>717</v>
+        <v>1202</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Stenbäcken, Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>477651</v>
+        <v>477402</v>
       </c>
       <c r="R201" t="n">
-        <v>7033403</v>
+        <v>7033066</v>
       </c>
       <c r="S201" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22205,18 +22198,12 @@
           <t>2024-05-19</t>
         </is>
       </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>På levande asp. Trötta fruktkroppar.</t>
-        </is>
-      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
       <c r="AE201" t="b">
         <v>0</v>
       </c>
-      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
@@ -22235,10 +22222,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>117792165</v>
+        <v>117130130</v>
       </c>
       <c r="B202" t="n">
-        <v>90503</v>
+        <v>91236</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22247,41 +22234,44 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1202</v>
+        <v>717</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>477450</v>
+        <v>477651</v>
       </c>
       <c r="R202" t="n">
-        <v>7033406</v>
+        <v>7033403</v>
       </c>
       <c r="S202" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22305,12 +22295,17 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>På levande asp. Trötta fruktkroppar.</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22319,6 +22314,7 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
+      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
@@ -22337,10 +22333,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>118701501</v>
+        <v>117792165</v>
       </c>
       <c r="B203" t="n">
-        <v>97844</v>
+        <v>90503</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22353,21 +22349,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>620</v>
+        <v>1202</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22377,10 +22373,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>477755</v>
+        <v>477450</v>
       </c>
       <c r="R203" t="n">
-        <v>7033301</v>
+        <v>7033406</v>
       </c>
       <c r="S203" t="n">
         <v>20</v>
@@ -22407,12 +22403,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22439,10 +22435,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>118703040</v>
+        <v>118701501</v>
       </c>
       <c r="B204" t="n">
-        <v>91791</v>
+        <v>97844</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22451,25 +22447,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4366</v>
+        <v>620</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22479,10 +22475,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>477689</v>
+        <v>477755</v>
       </c>
       <c r="R204" t="n">
-        <v>7033262</v>
+        <v>7033301</v>
       </c>
       <c r="S204" t="n">
         <v>20</v>
@@ -22541,10 +22537,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>117448064</v>
+        <v>118703040</v>
       </c>
       <c r="B205" t="n">
-        <v>90497</v>
+        <v>91791</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22553,38 +22549,38 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1108</v>
+        <v>4366</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>477365</v>
+        <v>477689</v>
       </c>
       <c r="R205" t="n">
-        <v>7032988</v>
+        <v>7033262</v>
       </c>
       <c r="S205" t="n">
         <v>20</v>
@@ -22611,12 +22607,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22643,10 +22639,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>117448244</v>
+        <v>118861806</v>
       </c>
       <c r="B206" t="n">
-        <v>90519</v>
+        <v>91764</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22659,21 +22655,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>5432</v>
+        <v>1968</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -22683,10 +22679,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>477439</v>
+        <v>477318</v>
       </c>
       <c r="R206" t="n">
-        <v>7033047</v>
+        <v>7033069</v>
       </c>
       <c r="S206" t="n">
         <v>20</v>
@@ -22713,12 +22709,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22745,10 +22741,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>118414846</v>
+        <v>117448064</v>
       </c>
       <c r="B207" t="n">
-        <v>91791</v>
+        <v>90497</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22757,41 +22753,38 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4366</v>
+        <v>1108</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>477357</v>
+        <v>477365</v>
       </c>
       <c r="R207" t="n">
-        <v>7033041</v>
+        <v>7032988</v>
       </c>
       <c r="S207" t="n">
         <v>20</v>
@@ -22818,17 +22811,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22837,7 +22825,6 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
-      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
@@ -22856,10 +22843,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>118414787</v>
+        <v>117448244</v>
       </c>
       <c r="B208" t="n">
-        <v>90500</v>
+        <v>90519</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -22872,21 +22859,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -22896,10 +22883,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>477367</v>
+        <v>477439</v>
       </c>
       <c r="R208" t="n">
-        <v>7032995</v>
+        <v>7033047</v>
       </c>
       <c r="S208" t="n">
         <v>20</v>
@@ -22926,12 +22913,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22958,10 +22945,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>118702006</v>
+        <v>118414846</v>
       </c>
       <c r="B209" t="n">
-        <v>91764</v>
+        <v>91791</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22970,38 +22957,41 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1968</v>
+        <v>4366</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>477332</v>
+        <v>477357</v>
       </c>
       <c r="R209" t="n">
-        <v>7033029</v>
+        <v>7033041</v>
       </c>
       <c r="S209" t="n">
         <v>20</v>
@@ -23028,12 +23018,17 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23042,6 +23037,7 @@
       <c r="AE209" t="b">
         <v>0</v>
       </c>
+      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>
@@ -23057,6 +23053,210 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>118414787</v>
+      </c>
+      <c r="B210" t="n">
+        <v>90500</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Klingvågen (Klingvågen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>477367</v>
+      </c>
+      <c r="R210" t="n">
+        <v>7032995</v>
+      </c>
+      <c r="S210" t="n">
+        <v>20</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AD210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>118702006</v>
+      </c>
+      <c r="B211" t="n">
+        <v>91764</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Bankera violascens</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Klingvågen (Klingvågen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>477332</v>
+      </c>
+      <c r="R211" t="n">
+        <v>7033029</v>
+      </c>
+      <c r="S211" t="n">
+        <v>20</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -18866,10 +18866,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>118410708</v>
+        <v>118417044</v>
       </c>
       <c r="B170" t="n">
-        <v>97848</v>
+        <v>77431</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18878,38 +18878,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>219811</v>
+        <v>314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478167</v>
+        <v>478568</v>
       </c>
       <c r="R170" t="n">
-        <v>7035268</v>
+        <v>7034212</v>
       </c>
       <c r="S170" t="n">
         <v>20</v>
@@ -19172,10 +19172,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>118417044</v>
+        <v>118410708</v>
       </c>
       <c r="B173" t="n">
-        <v>77431</v>
+        <v>97848</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19184,38 +19184,38 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>314</v>
+        <v>219811</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>478568</v>
+        <v>478167</v>
       </c>
       <c r="R173" t="n">
-        <v>7034212</v>
+        <v>7035268</v>
       </c>
       <c r="S173" t="n">
         <v>20</v>
@@ -19274,10 +19274,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>118700504</v>
+        <v>118699891</v>
       </c>
       <c r="B174" t="n">
-        <v>97844</v>
+        <v>79593</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19286,25 +19286,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>620</v>
+        <v>6461</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19314,10 +19314,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>478529</v>
+        <v>478328</v>
       </c>
       <c r="R174" t="n">
-        <v>7034182</v>
+        <v>7034844</v>
       </c>
       <c r="S174" t="n">
         <v>20</v>
@@ -19376,10 +19376,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>118699891</v>
+        <v>118700473</v>
       </c>
       <c r="B175" t="n">
-        <v>79593</v>
+        <v>86820</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19388,25 +19388,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6461</v>
+        <v>510</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19416,10 +19416,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>478328</v>
+        <v>478540</v>
       </c>
       <c r="R175" t="n">
-        <v>7034844</v>
+        <v>7034211</v>
       </c>
       <c r="S175" t="n">
         <v>20</v>
@@ -19478,10 +19478,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>118699023</v>
+        <v>118697497</v>
       </c>
       <c r="B176" t="n">
-        <v>97844</v>
+        <v>94455</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19490,25 +19490,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>620</v>
+        <v>2682</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19518,10 +19518,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>478036</v>
+        <v>478312</v>
       </c>
       <c r="R176" t="n">
-        <v>7035367</v>
+        <v>7035206</v>
       </c>
       <c r="S176" t="n">
         <v>20</v>
@@ -19682,7 +19682,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>118701025</v>
+        <v>118699023</v>
       </c>
       <c r="B178" t="n">
         <v>97844</v>
@@ -19718,14 +19718,14 @@
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>478191</v>
+        <v>478036</v>
       </c>
       <c r="R178" t="n">
-        <v>7033866</v>
+        <v>7035367</v>
       </c>
       <c r="S178" t="n">
         <v>20</v>
@@ -19784,10 +19784,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>118700473</v>
+        <v>118696189</v>
       </c>
       <c r="B179" t="n">
-        <v>86820</v>
+        <v>83951</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19800,21 +19800,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>510</v>
+        <v>5589</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19824,10 +19824,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478540</v>
+        <v>478945</v>
       </c>
       <c r="R179" t="n">
-        <v>7034211</v>
+        <v>7034451</v>
       </c>
       <c r="S179" t="n">
         <v>20</v>
@@ -19886,10 +19886,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>118697531</v>
+        <v>118700665</v>
       </c>
       <c r="B180" t="n">
-        <v>97745</v>
+        <v>83951</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19898,38 +19898,38 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>219795</v>
+        <v>5589</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478312</v>
+        <v>478375</v>
       </c>
       <c r="R180" t="n">
-        <v>7035206</v>
+        <v>7034114</v>
       </c>
       <c r="S180" t="n">
         <v>20</v>
@@ -19988,10 +19988,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>118696189</v>
+        <v>118701025</v>
       </c>
       <c r="B181" t="n">
-        <v>83951</v>
+        <v>97844</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20004,21 +20004,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5589</v>
+        <v>620</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20028,10 +20028,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478945</v>
+        <v>478191</v>
       </c>
       <c r="R181" t="n">
-        <v>7034451</v>
+        <v>7033866</v>
       </c>
       <c r="S181" t="n">
         <v>20</v>
@@ -20090,10 +20090,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>118697497</v>
+        <v>118697531</v>
       </c>
       <c r="B182" t="n">
-        <v>94455</v>
+        <v>97745</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20106,21 +20106,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2682</v>
+        <v>219795</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20192,7 +20192,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>118700665</v>
+        <v>118696519</v>
       </c>
       <c r="B183" t="n">
         <v>83951</v>
@@ -20232,10 +20232,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>478375</v>
+        <v>478742</v>
       </c>
       <c r="R183" t="n">
-        <v>7034114</v>
+        <v>7034663</v>
       </c>
       <c r="S183" t="n">
         <v>20</v>
@@ -20294,10 +20294,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>118696519</v>
+        <v>118700504</v>
       </c>
       <c r="B184" t="n">
-        <v>83951</v>
+        <v>97844</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20310,21 +20310,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5589</v>
+        <v>620</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20334,10 +20334,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>478742</v>
+        <v>478529</v>
       </c>
       <c r="R184" t="n">
-        <v>7034663</v>
+        <v>7034182</v>
       </c>
       <c r="S184" t="n">
         <v>20</v>
@@ -20608,10 +20608,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>118854701</v>
+        <v>118858244</v>
       </c>
       <c r="B187" t="n">
-        <v>91436</v>
+        <v>86351</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20624,34 +20624,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>478743</v>
+        <v>477907</v>
       </c>
       <c r="R187" t="n">
-        <v>7034675</v>
+        <v>7035514</v>
       </c>
       <c r="S187" t="n">
         <v>20</v>
@@ -20710,10 +20710,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>118858244</v>
+        <v>118854701</v>
       </c>
       <c r="B188" t="n">
-        <v>86351</v>
+        <v>91436</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20726,34 +20726,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>477907</v>
+        <v>478743</v>
       </c>
       <c r="R188" t="n">
-        <v>7035514</v>
+        <v>7034675</v>
       </c>
       <c r="S188" t="n">
         <v>20</v>
@@ -22435,10 +22435,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>118701501</v>
+        <v>118703040</v>
       </c>
       <c r="B204" t="n">
-        <v>97844</v>
+        <v>91791</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22447,25 +22447,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>620</v>
+        <v>4366</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22475,10 +22475,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>477755</v>
+        <v>477689</v>
       </c>
       <c r="R204" t="n">
-        <v>7033301</v>
+        <v>7033262</v>
       </c>
       <c r="S204" t="n">
         <v>20</v>
@@ -22537,10 +22537,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>118703040</v>
+        <v>118701501</v>
       </c>
       <c r="B205" t="n">
-        <v>91791</v>
+        <v>97844</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22549,25 +22549,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4366</v>
+        <v>620</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22577,10 +22577,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>477689</v>
+        <v>477755</v>
       </c>
       <c r="R205" t="n">
-        <v>7033262</v>
+        <v>7033301</v>
       </c>
       <c r="S205" t="n">
         <v>20</v>
@@ -22945,10 +22945,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>118414846</v>
+        <v>118414787</v>
       </c>
       <c r="B209" t="n">
-        <v>91791</v>
+        <v>90500</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22957,41 +22957,38 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4366</v>
+        <v>1108</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>477357</v>
+        <v>477367</v>
       </c>
       <c r="R209" t="n">
-        <v>7033041</v>
+        <v>7032995</v>
       </c>
       <c r="S209" t="n">
         <v>20</v>
@@ -23026,18 +23023,12 @@
           <t>2024-07-13</t>
         </is>
       </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
-        </is>
-      </c>
       <c r="AD209" t="b">
         <v>0</v>
       </c>
       <c r="AE209" t="b">
         <v>0</v>
       </c>
-      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>
@@ -23056,10 +23047,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>118414787</v>
+        <v>118414846</v>
       </c>
       <c r="B210" t="n">
-        <v>90500</v>
+        <v>91791</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23068,38 +23059,41 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1108</v>
+        <v>4366</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>477367</v>
+        <v>477357</v>
       </c>
       <c r="R210" t="n">
-        <v>7032995</v>
+        <v>7033041</v>
       </c>
       <c r="S210" t="n">
         <v>20</v>
@@ -23134,12 +23128,18 @@
           <t>2024-07-13</t>
         </is>
       </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
+        </is>
+      </c>
       <c r="AD210" t="b">
         <v>0</v>
       </c>
       <c r="AE210" t="b">
         <v>0</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -20090,10 +20090,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>118697531</v>
+        <v>118696519</v>
       </c>
       <c r="B182" t="n">
-        <v>97745</v>
+        <v>83951</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20102,38 +20102,38 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>219795</v>
+        <v>5589</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>478312</v>
+        <v>478742</v>
       </c>
       <c r="R182" t="n">
-        <v>7035206</v>
+        <v>7034663</v>
       </c>
       <c r="S182" t="n">
         <v>20</v>
@@ -20192,10 +20192,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>118696519</v>
+        <v>118700504</v>
       </c>
       <c r="B183" t="n">
-        <v>83951</v>
+        <v>97844</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20208,21 +20208,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5589</v>
+        <v>620</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20232,10 +20232,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>478742</v>
+        <v>478529</v>
       </c>
       <c r="R183" t="n">
-        <v>7034663</v>
+        <v>7034182</v>
       </c>
       <c r="S183" t="n">
         <v>20</v>
@@ -20294,10 +20294,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>118700504</v>
+        <v>118697531</v>
       </c>
       <c r="B184" t="n">
-        <v>97844</v>
+        <v>97745</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20306,38 +20306,38 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>620</v>
+        <v>219795</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>478529</v>
+        <v>478312</v>
       </c>
       <c r="R184" t="n">
-        <v>7034182</v>
+        <v>7035206</v>
       </c>
       <c r="S184" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -18764,10 +18764,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>118417219</v>
+        <v>118409601</v>
       </c>
       <c r="B169" t="n">
-        <v>74587</v>
+        <v>97750</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18776,25 +18776,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>492</v>
+        <v>220093</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18804,10 +18804,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478663</v>
+        <v>478966</v>
       </c>
       <c r="R169" t="n">
-        <v>7034261</v>
+        <v>7034476</v>
       </c>
       <c r="S169" t="n">
         <v>20</v>
@@ -18866,10 +18866,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>118417044</v>
+        <v>118417219</v>
       </c>
       <c r="B170" t="n">
-        <v>77431</v>
+        <v>74587</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18878,25 +18878,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>314</v>
+        <v>492</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18906,10 +18906,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478568</v>
+        <v>478663</v>
       </c>
       <c r="R170" t="n">
-        <v>7034212</v>
+        <v>7034261</v>
       </c>
       <c r="S170" t="n">
         <v>20</v>
@@ -18968,10 +18968,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>118409948</v>
+        <v>118410708</v>
       </c>
       <c r="B171" t="n">
-        <v>90451</v>
+        <v>97848</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18980,38 +18980,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>112</v>
+        <v>219811</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>478757</v>
+        <v>478167</v>
       </c>
       <c r="R171" t="n">
-        <v>7034700</v>
+        <v>7035268</v>
       </c>
       <c r="S171" t="n">
         <v>20</v>
@@ -19070,10 +19070,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>118409601</v>
+        <v>118409948</v>
       </c>
       <c r="B172" t="n">
-        <v>97750</v>
+        <v>90451</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19082,25 +19082,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220093</v>
+        <v>112</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19110,10 +19110,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>478966</v>
+        <v>478757</v>
       </c>
       <c r="R172" t="n">
-        <v>7034476</v>
+        <v>7034700</v>
       </c>
       <c r="S172" t="n">
         <v>20</v>
@@ -19172,10 +19172,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>118410708</v>
+        <v>118417044</v>
       </c>
       <c r="B173" t="n">
-        <v>97848</v>
+        <v>77431</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19184,38 +19184,38 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>219811</v>
+        <v>314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>478167</v>
+        <v>478568</v>
       </c>
       <c r="R173" t="n">
-        <v>7035268</v>
+        <v>7034212</v>
       </c>
       <c r="S173" t="n">
         <v>20</v>
@@ -19580,10 +19580,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>118700794</v>
+        <v>118701025</v>
       </c>
       <c r="B177" t="n">
-        <v>83951</v>
+        <v>97844</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19596,21 +19596,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5589</v>
+        <v>620</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19620,10 +19620,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>478325</v>
+        <v>478191</v>
       </c>
       <c r="R177" t="n">
-        <v>7034027</v>
+        <v>7033866</v>
       </c>
       <c r="S177" t="n">
         <v>20</v>
@@ -19682,10 +19682,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>118699023</v>
+        <v>118700665</v>
       </c>
       <c r="B178" t="n">
-        <v>97844</v>
+        <v>83951</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19698,34 +19698,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>620</v>
+        <v>5589</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>478036</v>
+        <v>478375</v>
       </c>
       <c r="R178" t="n">
-        <v>7035367</v>
+        <v>7034114</v>
       </c>
       <c r="S178" t="n">
         <v>20</v>
@@ -19784,10 +19784,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>118696189</v>
+        <v>118700504</v>
       </c>
       <c r="B179" t="n">
-        <v>83951</v>
+        <v>97844</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19800,21 +19800,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5589</v>
+        <v>620</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19824,10 +19824,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478945</v>
+        <v>478529</v>
       </c>
       <c r="R179" t="n">
-        <v>7034451</v>
+        <v>7034182</v>
       </c>
       <c r="S179" t="n">
         <v>20</v>
@@ -19886,7 +19886,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>118700665</v>
+        <v>118696189</v>
       </c>
       <c r="B180" t="n">
         <v>83951</v>
@@ -19926,10 +19926,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478375</v>
+        <v>478945</v>
       </c>
       <c r="R180" t="n">
-        <v>7034114</v>
+        <v>7034451</v>
       </c>
       <c r="S180" t="n">
         <v>20</v>
@@ -19988,10 +19988,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>118701025</v>
+        <v>118697531</v>
       </c>
       <c r="B181" t="n">
-        <v>97844</v>
+        <v>97745</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20000,38 +20000,38 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>620</v>
+        <v>219795</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478191</v>
+        <v>478312</v>
       </c>
       <c r="R181" t="n">
-        <v>7033866</v>
+        <v>7035206</v>
       </c>
       <c r="S181" t="n">
         <v>20</v>
@@ -20090,10 +20090,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>118696519</v>
+        <v>118699023</v>
       </c>
       <c r="B182" t="n">
-        <v>83951</v>
+        <v>97844</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20106,34 +20106,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5589</v>
+        <v>620</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>478742</v>
+        <v>478036</v>
       </c>
       <c r="R182" t="n">
-        <v>7034663</v>
+        <v>7035367</v>
       </c>
       <c r="S182" t="n">
         <v>20</v>
@@ -20192,10 +20192,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>118700504</v>
+        <v>118696519</v>
       </c>
       <c r="B183" t="n">
-        <v>97844</v>
+        <v>83951</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20208,21 +20208,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>620</v>
+        <v>5589</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20232,10 +20232,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>478529</v>
+        <v>478742</v>
       </c>
       <c r="R183" t="n">
-        <v>7034182</v>
+        <v>7034663</v>
       </c>
       <c r="S183" t="n">
         <v>20</v>
@@ -20294,10 +20294,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>118697531</v>
+        <v>118700794</v>
       </c>
       <c r="B184" t="n">
-        <v>97745</v>
+        <v>83951</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20306,38 +20306,38 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>219795</v>
+        <v>5589</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>478312</v>
+        <v>478325</v>
       </c>
       <c r="R184" t="n">
-        <v>7035206</v>
+        <v>7034027</v>
       </c>
       <c r="S184" t="n">
         <v>20</v>
@@ -20608,10 +20608,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>118858244</v>
+        <v>118854701</v>
       </c>
       <c r="B187" t="n">
-        <v>86351</v>
+        <v>91436</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20624,34 +20624,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>477907</v>
+        <v>478743</v>
       </c>
       <c r="R187" t="n">
-        <v>7035514</v>
+        <v>7034675</v>
       </c>
       <c r="S187" t="n">
         <v>20</v>
@@ -20710,10 +20710,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>118854701</v>
+        <v>118858244</v>
       </c>
       <c r="B188" t="n">
-        <v>91436</v>
+        <v>86351</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20726,34 +20726,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>478743</v>
+        <v>477907</v>
       </c>
       <c r="R188" t="n">
-        <v>7034675</v>
+        <v>7035514</v>
       </c>
       <c r="S188" t="n">
         <v>20</v>
@@ -22435,10 +22435,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>118703040</v>
+        <v>118701501</v>
       </c>
       <c r="B204" t="n">
-        <v>91791</v>
+        <v>97844</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22447,25 +22447,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4366</v>
+        <v>620</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22475,10 +22475,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>477689</v>
+        <v>477755</v>
       </c>
       <c r="R204" t="n">
-        <v>7033262</v>
+        <v>7033301</v>
       </c>
       <c r="S204" t="n">
         <v>20</v>
@@ -22537,10 +22537,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>118701501</v>
+        <v>118703040</v>
       </c>
       <c r="B205" t="n">
-        <v>97844</v>
+        <v>91791</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22549,25 +22549,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>620</v>
+        <v>4366</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22577,10 +22577,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>477755</v>
+        <v>477689</v>
       </c>
       <c r="R205" t="n">
-        <v>7033301</v>
+        <v>7033262</v>
       </c>
       <c r="S205" t="n">
         <v>20</v>
@@ -22945,10 +22945,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>118414787</v>
+        <v>118414846</v>
       </c>
       <c r="B209" t="n">
-        <v>90500</v>
+        <v>91791</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22957,38 +22957,41 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1108</v>
+        <v>4366</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>477367</v>
+        <v>477357</v>
       </c>
       <c r="R209" t="n">
-        <v>7032995</v>
+        <v>7033041</v>
       </c>
       <c r="S209" t="n">
         <v>20</v>
@@ -23023,12 +23026,18 @@
           <t>2024-07-13</t>
         </is>
       </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
+        </is>
+      </c>
       <c r="AD209" t="b">
         <v>0</v>
       </c>
       <c r="AE209" t="b">
         <v>0</v>
       </c>
+      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>
@@ -23047,10 +23056,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>118414846</v>
+        <v>118414787</v>
       </c>
       <c r="B210" t="n">
-        <v>91791</v>
+        <v>90500</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23059,41 +23068,38 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>4366</v>
+        <v>1108</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>477357</v>
+        <v>477367</v>
       </c>
       <c r="R210" t="n">
-        <v>7033041</v>
+        <v>7032995</v>
       </c>
       <c r="S210" t="n">
         <v>20</v>
@@ -23128,18 +23134,12 @@
           <t>2024-07-13</t>
         </is>
       </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
-        </is>
-      </c>
       <c r="AD210" t="b">
         <v>0</v>
       </c>
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -18767,7 +18767,7 @@
         <v>118409601</v>
       </c>
       <c r="B169" t="n">
-        <v>97750</v>
+        <v>97757</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18866,10 +18866,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>118417219</v>
+        <v>118410708</v>
       </c>
       <c r="B170" t="n">
-        <v>74587</v>
+        <v>97855</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18878,38 +18878,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>492</v>
+        <v>219811</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478663</v>
+        <v>478167</v>
       </c>
       <c r="R170" t="n">
-        <v>7034261</v>
+        <v>7035268</v>
       </c>
       <c r="S170" t="n">
         <v>20</v>
@@ -18968,10 +18968,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>118410708</v>
+        <v>118417044</v>
       </c>
       <c r="B171" t="n">
-        <v>97848</v>
+        <v>77438</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18980,38 +18980,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>219811</v>
+        <v>314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>478167</v>
+        <v>478568</v>
       </c>
       <c r="R171" t="n">
-        <v>7035268</v>
+        <v>7034212</v>
       </c>
       <c r="S171" t="n">
         <v>20</v>
@@ -19070,10 +19070,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>118409948</v>
+        <v>118417219</v>
       </c>
       <c r="B172" t="n">
-        <v>90451</v>
+        <v>74594</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19082,25 +19082,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>112</v>
+        <v>492</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19110,10 +19110,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>478757</v>
+        <v>478663</v>
       </c>
       <c r="R172" t="n">
-        <v>7034700</v>
+        <v>7034261</v>
       </c>
       <c r="S172" t="n">
         <v>20</v>
@@ -19172,10 +19172,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>118417044</v>
+        <v>118409948</v>
       </c>
       <c r="B173" t="n">
-        <v>77431</v>
+        <v>90458</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19188,21 +19188,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>314</v>
+        <v>112</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19212,10 +19212,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>478568</v>
+        <v>478757</v>
       </c>
       <c r="R173" t="n">
-        <v>7034212</v>
+        <v>7034700</v>
       </c>
       <c r="S173" t="n">
         <v>20</v>
@@ -19274,10 +19274,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>118699891</v>
+        <v>118696519</v>
       </c>
       <c r="B174" t="n">
-        <v>79593</v>
+        <v>83958</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19286,25 +19286,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6461</v>
+        <v>5589</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19314,10 +19314,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>478328</v>
+        <v>478742</v>
       </c>
       <c r="R174" t="n">
-        <v>7034844</v>
+        <v>7034663</v>
       </c>
       <c r="S174" t="n">
         <v>20</v>
@@ -19376,10 +19376,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>118700473</v>
+        <v>118701025</v>
       </c>
       <c r="B175" t="n">
-        <v>86820</v>
+        <v>97851</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19392,21 +19392,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>510</v>
+        <v>620</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19416,10 +19416,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>478540</v>
+        <v>478191</v>
       </c>
       <c r="R175" t="n">
-        <v>7034211</v>
+        <v>7033866</v>
       </c>
       <c r="S175" t="n">
         <v>20</v>
@@ -19478,10 +19478,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>118697497</v>
+        <v>118700473</v>
       </c>
       <c r="B176" t="n">
-        <v>94455</v>
+        <v>86827</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19490,38 +19490,38 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2682</v>
+        <v>510</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>478312</v>
+        <v>478540</v>
       </c>
       <c r="R176" t="n">
-        <v>7035206</v>
+        <v>7034211</v>
       </c>
       <c r="S176" t="n">
         <v>20</v>
@@ -19580,10 +19580,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>118701025</v>
+        <v>118696189</v>
       </c>
       <c r="B177" t="n">
-        <v>97844</v>
+        <v>83958</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19596,21 +19596,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>620</v>
+        <v>5589</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19620,10 +19620,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>478191</v>
+        <v>478945</v>
       </c>
       <c r="R177" t="n">
-        <v>7033866</v>
+        <v>7034451</v>
       </c>
       <c r="S177" t="n">
         <v>20</v>
@@ -19682,10 +19682,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>118700665</v>
+        <v>118697531</v>
       </c>
       <c r="B178" t="n">
-        <v>83951</v>
+        <v>97752</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19694,38 +19694,38 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5589</v>
+        <v>219795</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>478375</v>
+        <v>478312</v>
       </c>
       <c r="R178" t="n">
-        <v>7034114</v>
+        <v>7035206</v>
       </c>
       <c r="S178" t="n">
         <v>20</v>
@@ -19787,7 +19787,7 @@
         <v>118700504</v>
       </c>
       <c r="B179" t="n">
-        <v>97844</v>
+        <v>97851</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19886,10 +19886,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>118696189</v>
+        <v>118700794</v>
       </c>
       <c r="B180" t="n">
-        <v>83951</v>
+        <v>83958</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19926,10 +19926,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478945</v>
+        <v>478325</v>
       </c>
       <c r="R180" t="n">
-        <v>7034451</v>
+        <v>7034027</v>
       </c>
       <c r="S180" t="n">
         <v>20</v>
@@ -19988,10 +19988,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>118697531</v>
+        <v>118697497</v>
       </c>
       <c r="B181" t="n">
-        <v>97745</v>
+        <v>94462</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20004,21 +20004,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>219795</v>
+        <v>2682</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20093,7 +20093,7 @@
         <v>118699023</v>
       </c>
       <c r="B182" t="n">
-        <v>97844</v>
+        <v>97851</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20192,10 +20192,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>118696519</v>
+        <v>118699891</v>
       </c>
       <c r="B183" t="n">
-        <v>83951</v>
+        <v>79600</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20204,25 +20204,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5589</v>
+        <v>6461</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20232,10 +20232,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>478742</v>
+        <v>478328</v>
       </c>
       <c r="R183" t="n">
-        <v>7034663</v>
+        <v>7034844</v>
       </c>
       <c r="S183" t="n">
         <v>20</v>
@@ -20294,10 +20294,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>118700794</v>
+        <v>118700665</v>
       </c>
       <c r="B184" t="n">
-        <v>83951</v>
+        <v>83958</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20334,10 +20334,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>478325</v>
+        <v>478375</v>
       </c>
       <c r="R184" t="n">
-        <v>7034027</v>
+        <v>7034114</v>
       </c>
       <c r="S184" t="n">
         <v>20</v>
@@ -20399,7 +20399,7 @@
         <v>118698082</v>
       </c>
       <c r="B185" t="n">
-        <v>85791</v>
+        <v>85798</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>118698422</v>
       </c>
       <c r="B186" t="n">
-        <v>90048</v>
+        <v>90055</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20608,10 +20608,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>118854701</v>
+        <v>118858244</v>
       </c>
       <c r="B187" t="n">
-        <v>91436</v>
+        <v>86358</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20624,34 +20624,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4769</v>
+        <v>1988</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>478743</v>
+        <v>477907</v>
       </c>
       <c r="R187" t="n">
-        <v>7034675</v>
+        <v>7035514</v>
       </c>
       <c r="S187" t="n">
         <v>20</v>
@@ -20710,10 +20710,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>118858244</v>
+        <v>118854701</v>
       </c>
       <c r="B188" t="n">
-        <v>86351</v>
+        <v>91443</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20726,34 +20726,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1988</v>
+        <v>4769</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>477907</v>
+        <v>478743</v>
       </c>
       <c r="R188" t="n">
-        <v>7035514</v>
+        <v>7034675</v>
       </c>
       <c r="S188" t="n">
         <v>20</v>
@@ -22438,7 +22438,7 @@
         <v>118701501</v>
       </c>
       <c r="B204" t="n">
-        <v>97844</v>
+        <v>97851</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>118703040</v>
       </c>
       <c r="B205" t="n">
-        <v>91791</v>
+        <v>91798</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>118861806</v>
       </c>
       <c r="B206" t="n">
-        <v>91764</v>
+        <v>91771</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>118414846</v>
       </c>
       <c r="B209" t="n">
-        <v>91791</v>
+        <v>91798</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>118414787</v>
       </c>
       <c r="B210" t="n">
-        <v>90500</v>
+        <v>90507</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>118702006</v>
       </c>
       <c r="B211" t="n">
-        <v>91764</v>
+        <v>91771</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -22435,10 +22435,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>118701501</v>
+        <v>118703040</v>
       </c>
       <c r="B204" t="n">
-        <v>97851</v>
+        <v>91798</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22447,25 +22447,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>620</v>
+        <v>4366</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22475,10 +22475,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>477755</v>
+        <v>477689</v>
       </c>
       <c r="R204" t="n">
-        <v>7033301</v>
+        <v>7033262</v>
       </c>
       <c r="S204" t="n">
         <v>20</v>
@@ -22537,10 +22537,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>118703040</v>
+        <v>118701501</v>
       </c>
       <c r="B205" t="n">
-        <v>91798</v>
+        <v>97851</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22549,25 +22549,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4366</v>
+        <v>620</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22577,10 +22577,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>477689</v>
+        <v>477755</v>
       </c>
       <c r="R205" t="n">
-        <v>7033262</v>
+        <v>7033301</v>
       </c>
       <c r="S205" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -18764,10 +18764,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>118409601</v>
+        <v>118417219</v>
       </c>
       <c r="B169" t="n">
-        <v>97757</v>
+        <v>74594</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18776,25 +18776,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220093</v>
+        <v>492</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18804,10 +18804,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478966</v>
+        <v>478663</v>
       </c>
       <c r="R169" t="n">
-        <v>7034476</v>
+        <v>7034261</v>
       </c>
       <c r="S169" t="n">
         <v>20</v>
@@ -18866,10 +18866,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>118410708</v>
+        <v>118409948</v>
       </c>
       <c r="B170" t="n">
-        <v>97855</v>
+        <v>90458</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18878,38 +18878,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>219811</v>
+        <v>112</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478167</v>
+        <v>478757</v>
       </c>
       <c r="R170" t="n">
-        <v>7035268</v>
+        <v>7034700</v>
       </c>
       <c r="S170" t="n">
         <v>20</v>
@@ -19070,10 +19070,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>118417219</v>
+        <v>118409601</v>
       </c>
       <c r="B172" t="n">
-        <v>74594</v>
+        <v>97757</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19082,25 +19082,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>492</v>
+        <v>220093</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19110,10 +19110,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>478663</v>
+        <v>478966</v>
       </c>
       <c r="R172" t="n">
-        <v>7034261</v>
+        <v>7034476</v>
       </c>
       <c r="S172" t="n">
         <v>20</v>
@@ -19172,10 +19172,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>118409948</v>
+        <v>118410708</v>
       </c>
       <c r="B173" t="n">
-        <v>90458</v>
+        <v>97855</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19184,38 +19184,38 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>112</v>
+        <v>219811</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>478757</v>
+        <v>478167</v>
       </c>
       <c r="R173" t="n">
-        <v>7034700</v>
+        <v>7035268</v>
       </c>
       <c r="S173" t="n">
         <v>20</v>
@@ -19274,10 +19274,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>118696519</v>
+        <v>118701025</v>
       </c>
       <c r="B174" t="n">
-        <v>83958</v>
+        <v>97851</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19290,21 +19290,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5589</v>
+        <v>620</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19314,10 +19314,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>478742</v>
+        <v>478191</v>
       </c>
       <c r="R174" t="n">
-        <v>7034663</v>
+        <v>7033866</v>
       </c>
       <c r="S174" t="n">
         <v>20</v>
@@ -19376,10 +19376,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>118701025</v>
+        <v>118700665</v>
       </c>
       <c r="B175" t="n">
-        <v>97851</v>
+        <v>83958</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19392,21 +19392,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>620</v>
+        <v>5589</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19416,10 +19416,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>478191</v>
+        <v>478375</v>
       </c>
       <c r="R175" t="n">
-        <v>7033866</v>
+        <v>7034114</v>
       </c>
       <c r="S175" t="n">
         <v>20</v>
@@ -19580,7 +19580,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>118696189</v>
+        <v>118696519</v>
       </c>
       <c r="B177" t="n">
         <v>83958</v>
@@ -19620,10 +19620,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>478945</v>
+        <v>478742</v>
       </c>
       <c r="R177" t="n">
-        <v>7034451</v>
+        <v>7034663</v>
       </c>
       <c r="S177" t="n">
         <v>20</v>
@@ -19682,10 +19682,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>118697531</v>
+        <v>118697497</v>
       </c>
       <c r="B178" t="n">
-        <v>97752</v>
+        <v>94462</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19698,21 +19698,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>219795</v>
+        <v>2682</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19784,10 +19784,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>118700504</v>
+        <v>118699891</v>
       </c>
       <c r="B179" t="n">
-        <v>97851</v>
+        <v>79600</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19796,25 +19796,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>620</v>
+        <v>6461</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19824,10 +19824,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478529</v>
+        <v>478328</v>
       </c>
       <c r="R179" t="n">
-        <v>7034182</v>
+        <v>7034844</v>
       </c>
       <c r="S179" t="n">
         <v>20</v>
@@ -19886,7 +19886,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>118700794</v>
+        <v>118696189</v>
       </c>
       <c r="B180" t="n">
         <v>83958</v>
@@ -19926,10 +19926,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>478325</v>
+        <v>478945</v>
       </c>
       <c r="R180" t="n">
-        <v>7034027</v>
+        <v>7034451</v>
       </c>
       <c r="S180" t="n">
         <v>20</v>
@@ -19988,10 +19988,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>118697497</v>
+        <v>118700794</v>
       </c>
       <c r="B181" t="n">
-        <v>94462</v>
+        <v>83958</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20000,38 +20000,38 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2682</v>
+        <v>5589</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>478312</v>
+        <v>478325</v>
       </c>
       <c r="R181" t="n">
-        <v>7035206</v>
+        <v>7034027</v>
       </c>
       <c r="S181" t="n">
         <v>20</v>
@@ -20090,10 +20090,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>118699023</v>
+        <v>118697531</v>
       </c>
       <c r="B182" t="n">
-        <v>97851</v>
+        <v>97752</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20102,25 +20102,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>620</v>
+        <v>219795</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20130,10 +20130,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>478036</v>
+        <v>478312</v>
       </c>
       <c r="R182" t="n">
-        <v>7035367</v>
+        <v>7035206</v>
       </c>
       <c r="S182" t="n">
         <v>20</v>
@@ -20192,10 +20192,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>118699891</v>
+        <v>118699023</v>
       </c>
       <c r="B183" t="n">
-        <v>79600</v>
+        <v>97851</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20204,38 +20204,38 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6461</v>
+        <v>620</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Storbäcken (Storbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>478328</v>
+        <v>478036</v>
       </c>
       <c r="R183" t="n">
-        <v>7034844</v>
+        <v>7035367</v>
       </c>
       <c r="S183" t="n">
         <v>20</v>
@@ -20294,10 +20294,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>118700665</v>
+        <v>118700504</v>
       </c>
       <c r="B184" t="n">
-        <v>83958</v>
+        <v>97851</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20310,21 +20310,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5589</v>
+        <v>620</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20334,10 +20334,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>478375</v>
+        <v>478529</v>
       </c>
       <c r="R184" t="n">
-        <v>7034114</v>
+        <v>7034182</v>
       </c>
       <c r="S184" t="n">
         <v>20</v>
@@ -22435,10 +22435,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>118703040</v>
+        <v>118701501</v>
       </c>
       <c r="B204" t="n">
-        <v>91798</v>
+        <v>97851</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22447,25 +22447,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4366</v>
+        <v>620</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22475,10 +22475,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>477689</v>
+        <v>477755</v>
       </c>
       <c r="R204" t="n">
-        <v>7033262</v>
+        <v>7033301</v>
       </c>
       <c r="S204" t="n">
         <v>20</v>
@@ -22537,10 +22537,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>118701501</v>
+        <v>118703040</v>
       </c>
       <c r="B205" t="n">
-        <v>97851</v>
+        <v>91798</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22549,25 +22549,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>620</v>
+        <v>4366</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22577,10 +22577,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>477755</v>
+        <v>477689</v>
       </c>
       <c r="R205" t="n">
-        <v>7033301</v>
+        <v>7033262</v>
       </c>
       <c r="S205" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -23414,10 +23414,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119475515</v>
+        <v>119494947</v>
       </c>
       <c r="B219" t="n">
-        <v>86350</v>
+        <v>74633</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23426,25 +23426,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>449</v>
+        <v>310</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23453,17 +23453,17 @@
       <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>478607</v>
+        <v>478414</v>
       </c>
       <c r="R219" t="n">
-        <v>7034142</v>
+        <v>7034159</v>
       </c>
       <c r="S219" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -23493,11 +23493,6 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Ganska stark och frän doft. Ingen KOH reaktion på någon del av svampen. På myrstack vid bäckdråg.</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23525,10 +23520,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119494947</v>
+        <v>119473822</v>
       </c>
       <c r="B220" t="n">
-        <v>74633</v>
+        <v>86336</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23537,25 +23532,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>310</v>
+        <v>3595</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -23564,17 +23559,17 @@
       <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Stenbäcken, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>478414</v>
+        <v>478422</v>
       </c>
       <c r="R220" t="n">
-        <v>7034159</v>
+        <v>7034044</v>
       </c>
       <c r="S220" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -23604,6 +23599,11 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Ytliga karaktärer passar väldigt bra, dock reagerar kött och fot rött? På barrmatta vid bäckdråg.</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23631,10 +23631,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119473822</v>
+        <v>119475515</v>
       </c>
       <c r="B221" t="n">
-        <v>86336</v>
+        <v>86350</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23647,21 +23647,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>3595</v>
+        <v>449</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23674,10 +23674,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>478422</v>
+        <v>478607</v>
       </c>
       <c r="R221" t="n">
-        <v>7034044</v>
+        <v>7034142</v>
       </c>
       <c r="S221" t="n">
         <v>20</v>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>Ytliga karaktärer passar väldigt bra, dock reagerar kött och fot rött? På barrmatta vid bäckdråg.</t>
+          <t>Ganska stark och frän doft. Ingen KOH reaktion på någon del av svampen. På myrstack vid bäckdråg.</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23742,10 +23742,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119930975</v>
+        <v>119931445</v>
       </c>
       <c r="B222" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23758,34 +23758,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Landvågen, Landvågen, Jmt</t>
+          <t>Storbäcken, Storbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>477856</v>
+        <v>477968</v>
       </c>
       <c r="R222" t="n">
-        <v>7035623</v>
+        <v>7035551</v>
       </c>
       <c r="S222" t="n">
         <v>20</v>
@@ -23844,10 +23844,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119926437</v>
+        <v>119927771</v>
       </c>
       <c r="B223" t="n">
-        <v>87392</v>
+        <v>91839</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23856,25 +23856,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>4405</v>
+        <v>1435</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23884,10 +23884,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>478883</v>
+        <v>478349</v>
       </c>
       <c r="R223" t="n">
-        <v>7034275</v>
+        <v>7034098</v>
       </c>
       <c r="S223" t="n">
         <v>20</v>
@@ -23946,10 +23946,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119927209</v>
+        <v>119930145</v>
       </c>
       <c r="B224" t="n">
-        <v>91832</v>
+        <v>91259</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23958,25 +23958,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4361</v>
+        <v>67</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23986,10 +23986,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>478801</v>
+        <v>478186</v>
       </c>
       <c r="R224" t="n">
-        <v>7034150</v>
+        <v>7035146</v>
       </c>
       <c r="S224" t="n">
         <v>20</v>
@@ -24048,10 +24048,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119927395</v>
+        <v>119926530</v>
       </c>
       <c r="B225" t="n">
-        <v>86289</v>
+        <v>86334</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24060,25 +24060,25 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -24088,10 +24088,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>478642</v>
+        <v>478870</v>
       </c>
       <c r="R225" t="n">
-        <v>7034140</v>
+        <v>7034193</v>
       </c>
       <c r="S225" t="n">
         <v>20</v>
@@ -24150,10 +24150,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119926530</v>
+        <v>119930975</v>
       </c>
       <c r="B226" t="n">
-        <v>86334</v>
+        <v>91832</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24162,38 +24162,38 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>445</v>
+        <v>4361</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Landvågen, Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>478870</v>
+        <v>477856</v>
       </c>
       <c r="R226" t="n">
-        <v>7034193</v>
+        <v>7035623</v>
       </c>
       <c r="S226" t="n">
         <v>20</v>
@@ -24252,10 +24252,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119930145</v>
+        <v>119927184</v>
       </c>
       <c r="B227" t="n">
-        <v>91259</v>
+        <v>86410</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24264,25 +24264,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>67</v>
+        <v>249228</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24292,10 +24292,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>478186</v>
+        <v>478801</v>
       </c>
       <c r="R227" t="n">
-        <v>7035146</v>
+        <v>7034150</v>
       </c>
       <c r="S227" t="n">
         <v>20</v>
@@ -24354,10 +24354,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119931445</v>
+        <v>119927209</v>
       </c>
       <c r="B228" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24370,34 +24370,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Storbäcken, Storbäcken, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>477968</v>
+        <v>478801</v>
       </c>
       <c r="R228" t="n">
-        <v>7035551</v>
+        <v>7034150</v>
       </c>
       <c r="S228" t="n">
         <v>20</v>
@@ -24456,10 +24456,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119927771</v>
+        <v>119927395</v>
       </c>
       <c r="B229" t="n">
-        <v>91839</v>
+        <v>86289</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24468,25 +24468,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1435</v>
+        <v>427</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24496,10 +24496,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>478349</v>
+        <v>478642</v>
       </c>
       <c r="R229" t="n">
-        <v>7034098</v>
+        <v>7034140</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -24558,10 +24558,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119927184</v>
+        <v>119926437</v>
       </c>
       <c r="B230" t="n">
-        <v>86410</v>
+        <v>87392</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24574,21 +24574,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>249228</v>
+        <v>4405</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24598,10 +24598,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>478801</v>
+        <v>478883</v>
       </c>
       <c r="R230" t="n">
-        <v>7034150</v>
+        <v>7034275</v>
       </c>
       <c r="S230" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -17875,7 +17875,7 @@
         <v>117919042</v>
       </c>
       <c r="B165" t="n">
-        <v>79566</v>
+        <v>79608</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
@@ -23742,10 +23742,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119931445</v>
+        <v>119926437</v>
       </c>
       <c r="B222" t="n">
-        <v>91834</v>
+        <v>87392</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23754,38 +23754,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4362</v>
+        <v>4405</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Storbäcken, Storbäcken, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>477968</v>
+        <v>478883</v>
       </c>
       <c r="R222" t="n">
-        <v>7035551</v>
+        <v>7034275</v>
       </c>
       <c r="S222" t="n">
         <v>20</v>
@@ -23844,10 +23844,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119927771</v>
+        <v>119927209</v>
       </c>
       <c r="B223" t="n">
-        <v>91839</v>
+        <v>91832</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23856,25 +23856,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1435</v>
+        <v>4361</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23884,10 +23884,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>478349</v>
+        <v>478801</v>
       </c>
       <c r="R223" t="n">
-        <v>7034098</v>
+        <v>7034150</v>
       </c>
       <c r="S223" t="n">
         <v>20</v>
@@ -23946,10 +23946,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119930145</v>
+        <v>119927771</v>
       </c>
       <c r="B224" t="n">
-        <v>91259</v>
+        <v>91839</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23962,21 +23962,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>67</v>
+        <v>1435</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23986,10 +23986,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>478186</v>
+        <v>478349</v>
       </c>
       <c r="R224" t="n">
-        <v>7035146</v>
+        <v>7034098</v>
       </c>
       <c r="S224" t="n">
         <v>20</v>
@@ -24048,10 +24048,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119926530</v>
+        <v>119931445</v>
       </c>
       <c r="B225" t="n">
-        <v>86334</v>
+        <v>91834</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24060,38 +24060,38 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>445</v>
+        <v>4362</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Storbäcken, Storbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>478870</v>
+        <v>477968</v>
       </c>
       <c r="R225" t="n">
-        <v>7034193</v>
+        <v>7035551</v>
       </c>
       <c r="S225" t="n">
         <v>20</v>
@@ -24150,10 +24150,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119930975</v>
+        <v>119930145</v>
       </c>
       <c r="B226" t="n">
-        <v>91832</v>
+        <v>91259</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24162,38 +24162,38 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4361</v>
+        <v>67</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Landvågen, Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>477856</v>
+        <v>478186</v>
       </c>
       <c r="R226" t="n">
-        <v>7035623</v>
+        <v>7035146</v>
       </c>
       <c r="S226" t="n">
         <v>20</v>
@@ -24252,10 +24252,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119927184</v>
+        <v>119930975</v>
       </c>
       <c r="B227" t="n">
-        <v>86410</v>
+        <v>91832</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24264,38 +24264,38 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>249228</v>
+        <v>4361</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Landvågen, Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>478801</v>
+        <v>477856</v>
       </c>
       <c r="R227" t="n">
-        <v>7034150</v>
+        <v>7035623</v>
       </c>
       <c r="S227" t="n">
         <v>20</v>
@@ -24354,10 +24354,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119927209</v>
+        <v>119926530</v>
       </c>
       <c r="B228" t="n">
-        <v>91832</v>
+        <v>86334</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24366,25 +24366,25 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4361</v>
+        <v>445</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -24394,10 +24394,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>478801</v>
+        <v>478870</v>
       </c>
       <c r="R228" t="n">
-        <v>7034150</v>
+        <v>7034193</v>
       </c>
       <c r="S228" t="n">
         <v>20</v>
@@ -24456,10 +24456,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119927395</v>
+        <v>119927184</v>
       </c>
       <c r="B229" t="n">
-        <v>86289</v>
+        <v>86410</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24468,25 +24468,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>427</v>
+        <v>249228</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24496,10 +24496,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>478642</v>
+        <v>478801</v>
       </c>
       <c r="R229" t="n">
-        <v>7034140</v>
+        <v>7034150</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -24558,10 +24558,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119926437</v>
+        <v>119927395</v>
       </c>
       <c r="B230" t="n">
-        <v>87392</v>
+        <v>86289</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24570,25 +24570,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4405</v>
+        <v>427</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24598,10 +24598,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>478883</v>
+        <v>478642</v>
       </c>
       <c r="R230" t="n">
-        <v>7034275</v>
+        <v>7034140</v>
       </c>
       <c r="S230" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY257"/>
+  <dimension ref="A1:AY258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24660,10 +24660,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>111901519</v>
+        <v>120211708</v>
       </c>
       <c r="B231" t="n">
-        <v>86371</v>
+        <v>56522</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24672,41 +24672,45 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4412</v>
+        <v>100138</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>477765</v>
+        <v>478428</v>
       </c>
       <c r="R231" t="n">
-        <v>7033404</v>
+        <v>7034296</v>
       </c>
       <c r="S231" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -24730,12 +24734,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24750,22 +24754,22 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>111901546</v>
+        <v>111901519</v>
       </c>
       <c r="B232" t="n">
-        <v>56430</v>
+        <v>86371</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24778,38 +24782,34 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>477668</v>
+        <v>477765</v>
       </c>
       <c r="R232" t="n">
-        <v>7033374</v>
+        <v>7033404</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24842,11 +24842,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24873,7 +24868,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>111901547</v>
+        <v>111901546</v>
       </c>
       <c r="B233" t="n">
         <v>56430</v>
@@ -24917,10 +24912,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>477524</v>
+        <v>477668</v>
       </c>
       <c r="R233" t="n">
-        <v>7033330</v>
+        <v>7033374</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24957,7 +24952,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24984,7 +24979,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>111901551</v>
+        <v>111901547</v>
       </c>
       <c r="B234" t="n">
         <v>56430</v>
@@ -25028,10 +25023,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>477433</v>
+        <v>477524</v>
       </c>
       <c r="R234" t="n">
-        <v>7033429</v>
+        <v>7033330</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25095,10 +25090,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>111901518</v>
+        <v>111901551</v>
       </c>
       <c r="B235" t="n">
-        <v>86371</v>
+        <v>56430</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25111,34 +25106,38 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>477674</v>
+        <v>477433</v>
       </c>
       <c r="R235" t="n">
-        <v>7033500</v>
+        <v>7033429</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25171,6 +25170,11 @@
       <c r="AA235" t="inlineStr">
         <is>
           <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -25197,10 +25201,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>111901587</v>
+        <v>111901518</v>
       </c>
       <c r="B236" t="n">
-        <v>56575</v>
+        <v>86371</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25213,46 +25217,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>103021</v>
+        <v>4412</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>477611</v>
+        <v>477674</v>
       </c>
       <c r="R236" t="n">
-        <v>7033311</v>
+        <v>7033500</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25311,10 +25303,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>111901548</v>
+        <v>111901587</v>
       </c>
       <c r="B237" t="n">
-        <v>56430</v>
+        <v>56575</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -25327,38 +25319,46 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>477476</v>
+        <v>477611</v>
       </c>
       <c r="R237" t="n">
-        <v>7033385</v>
+        <v>7033311</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25391,11 +25391,6 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25422,10 +25417,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>111901618</v>
+        <v>111901548</v>
       </c>
       <c r="B238" t="n">
-        <v>85197</v>
+        <v>56430</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25438,34 +25433,38 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>249278</v>
+        <v>100109</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>477471</v>
+        <v>477476</v>
       </c>
       <c r="R238" t="n">
-        <v>7033412</v>
+        <v>7033385</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25498,6 +25497,11 @@
       <c r="AA238" t="inlineStr">
         <is>
           <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -25524,10 +25528,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>111901549</v>
+        <v>111901618</v>
       </c>
       <c r="B239" t="n">
-        <v>56430</v>
+        <v>85197</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25540,38 +25544,34 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100109</v>
+        <v>249278</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>477464</v>
+        <v>477471</v>
       </c>
       <c r="R239" t="n">
-        <v>7033364</v>
+        <v>7033412</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25604,11 +25604,6 @@
       <c r="AA239" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -25635,7 +25630,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>111901544</v>
+        <v>111901549</v>
       </c>
       <c r="B240" t="n">
         <v>56430</v>
@@ -25679,10 +25674,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>477639</v>
+        <v>477464</v>
       </c>
       <c r="R240" t="n">
-        <v>7033515</v>
+        <v>7033364</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25719,7 +25714,7 @@
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -25746,7 +25741,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>111901550</v>
+        <v>111901544</v>
       </c>
       <c r="B241" t="n">
         <v>56430</v>
@@ -25790,10 +25785,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>477473</v>
+        <v>477639</v>
       </c>
       <c r="R241" t="n">
-        <v>7033404</v>
+        <v>7033515</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25857,7 +25852,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>111901545</v>
+        <v>111901550</v>
       </c>
       <c r="B242" t="n">
         <v>56430</v>
@@ -25901,10 +25896,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>477667</v>
+        <v>477473</v>
       </c>
       <c r="R242" t="n">
-        <v>7033500</v>
+        <v>7033404</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25968,10 +25963,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>117085837</v>
+        <v>111901545</v>
       </c>
       <c r="B243" t="n">
-        <v>90463</v>
+        <v>56430</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25984,37 +25979,41 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>477402</v>
+        <v>477667</v>
       </c>
       <c r="R243" t="n">
-        <v>7033066</v>
+        <v>7033500</v>
       </c>
       <c r="S243" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -26038,12 +26037,17 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -26058,22 +26062,22 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>117130130</v>
+        <v>117085837</v>
       </c>
       <c r="B244" t="n">
-        <v>91236</v>
+        <v>90463</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -26082,44 +26086,41 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>717</v>
+        <v>1202</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Stenbäcken, Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>477651</v>
+        <v>477402</v>
       </c>
       <c r="R244" t="n">
-        <v>7033403</v>
+        <v>7033066</v>
       </c>
       <c r="S244" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -26151,18 +26152,12 @@
           <t>2024-05-19</t>
         </is>
       </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>På levande asp. Trötta fruktkroppar.</t>
-        </is>
-      </c>
       <c r="AD244" t="b">
         <v>0</v>
       </c>
       <c r="AE244" t="b">
         <v>0</v>
       </c>
-      <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="b">
         <v>0</v>
       </c>
@@ -26181,10 +26176,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>117792165</v>
+        <v>117130130</v>
       </c>
       <c r="B245" t="n">
-        <v>90503</v>
+        <v>91236</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -26193,41 +26188,44 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1202</v>
+        <v>717</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>477450</v>
+        <v>477651</v>
       </c>
       <c r="R245" t="n">
-        <v>7033406</v>
+        <v>7033403</v>
       </c>
       <c r="S245" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -26251,12 +26249,17 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>På levande asp. Trötta fruktkroppar.</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -26265,6 +26268,7 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
@@ -26283,10 +26287,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>118701501</v>
+        <v>117792165</v>
       </c>
       <c r="B246" t="n">
-        <v>97856</v>
+        <v>90503</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -26299,21 +26303,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>620</v>
+        <v>1202</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -26323,10 +26327,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>477755</v>
+        <v>477450</v>
       </c>
       <c r="R246" t="n">
-        <v>7033301</v>
+        <v>7033406</v>
       </c>
       <c r="S246" t="n">
         <v>20</v>
@@ -26353,12 +26357,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26385,10 +26389,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>118703040</v>
+        <v>118701501</v>
       </c>
       <c r="B247" t="n">
-        <v>91803</v>
+        <v>97856</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -26397,25 +26401,25 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>4366</v>
+        <v>620</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -26425,10 +26429,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>477689</v>
+        <v>477755</v>
       </c>
       <c r="R247" t="n">
-        <v>7033262</v>
+        <v>7033301</v>
       </c>
       <c r="S247" t="n">
         <v>20</v>
@@ -26487,10 +26491,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>118861806</v>
+        <v>118703040</v>
       </c>
       <c r="B248" t="n">
-        <v>91776</v>
+        <v>91803</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26499,38 +26503,38 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1968</v>
+        <v>4366</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>477318</v>
+        <v>477689</v>
       </c>
       <c r="R248" t="n">
-        <v>7033069</v>
+        <v>7033262</v>
       </c>
       <c r="S248" t="n">
         <v>20</v>
@@ -26557,12 +26561,12 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26589,10 +26593,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>119048941</v>
+        <v>118861806</v>
       </c>
       <c r="B249" t="n">
-        <v>87388</v>
+        <v>91776</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26605,21 +26609,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -26629,10 +26633,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>477338</v>
+        <v>477318</v>
       </c>
       <c r="R249" t="n">
-        <v>7033068</v>
+        <v>7033069</v>
       </c>
       <c r="S249" t="n">
         <v>20</v>
@@ -26659,12 +26663,12 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26691,10 +26695,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>119048382</v>
+        <v>119048941</v>
       </c>
       <c r="B250" t="n">
-        <v>91807</v>
+        <v>87388</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26707,34 +26711,34 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>477617</v>
+        <v>477338</v>
       </c>
       <c r="R250" t="n">
-        <v>7033532</v>
+        <v>7033068</v>
       </c>
       <c r="S250" t="n">
         <v>20</v>
@@ -26793,10 +26797,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>119221941</v>
+        <v>119048382</v>
       </c>
       <c r="B251" t="n">
-        <v>84007</v>
+        <v>91807</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26809,21 +26813,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>5589</v>
+        <v>1968</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -26833,10 +26837,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>477845</v>
+        <v>477617</v>
       </c>
       <c r="R251" t="n">
-        <v>7033413</v>
+        <v>7033532</v>
       </c>
       <c r="S251" t="n">
         <v>20</v>
@@ -26863,12 +26867,12 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26895,10 +26899,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>117448064</v>
+        <v>119221941</v>
       </c>
       <c r="B252" t="n">
-        <v>90497</v>
+        <v>84007</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26911,34 +26915,34 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1108</v>
+        <v>5589</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>477365</v>
+        <v>477845</v>
       </c>
       <c r="R252" t="n">
-        <v>7032988</v>
+        <v>7033413</v>
       </c>
       <c r="S252" t="n">
         <v>20</v>
@@ -26965,12 +26969,12 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -26997,10 +27001,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>117448244</v>
+        <v>117448064</v>
       </c>
       <c r="B253" t="n">
-        <v>90519</v>
+        <v>90497</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -27013,21 +27017,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -27037,10 +27041,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>477439</v>
+        <v>477365</v>
       </c>
       <c r="R253" t="n">
-        <v>7033047</v>
+        <v>7032988</v>
       </c>
       <c r="S253" t="n">
         <v>20</v>
@@ -27099,10 +27103,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>118414846</v>
+        <v>117448244</v>
       </c>
       <c r="B254" t="n">
-        <v>91800</v>
+        <v>90519</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -27111,41 +27115,38 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4366</v>
+        <v>5432</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
           <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>477357</v>
+        <v>477439</v>
       </c>
       <c r="R254" t="n">
-        <v>7033041</v>
+        <v>7033047</v>
       </c>
       <c r="S254" t="n">
         <v>20</v>
@@ -27172,17 +27173,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27191,7 +27187,6 @@
       <c r="AE254" t="b">
         <v>0</v>
       </c>
-      <c r="AF254" t="inlineStr"/>
       <c r="AG254" t="b">
         <v>0</v>
       </c>
@@ -27210,10 +27205,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>118414787</v>
+        <v>118414846</v>
       </c>
       <c r="B255" t="n">
-        <v>90509</v>
+        <v>91800</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -27222,38 +27217,41 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1108</v>
+        <v>4366</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
           <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>477367</v>
+        <v>477357</v>
       </c>
       <c r="R255" t="n">
-        <v>7032995</v>
+        <v>7033041</v>
       </c>
       <c r="S255" t="n">
         <v>20</v>
@@ -27288,12 +27286,18 @@
           <t>2024-07-13</t>
         </is>
       </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
+        </is>
+      </c>
       <c r="AD255" t="b">
         <v>0</v>
       </c>
       <c r="AE255" t="b">
         <v>0</v>
       </c>
+      <c r="AF255" t="inlineStr"/>
       <c r="AG255" t="b">
         <v>0</v>
       </c>
@@ -27312,10 +27316,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>118702006</v>
+        <v>118414787</v>
       </c>
       <c r="B256" t="n">
-        <v>91776</v>
+        <v>90509</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -27328,21 +27332,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -27352,10 +27356,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>477332</v>
+        <v>477367</v>
       </c>
       <c r="R256" t="n">
-        <v>7033029</v>
+        <v>7032995</v>
       </c>
       <c r="S256" t="n">
         <v>20</v>
@@ -27382,12 +27386,12 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27414,10 +27418,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>119477054</v>
+        <v>118702006</v>
       </c>
       <c r="B257" t="n">
-        <v>91883</v>
+        <v>91776</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -27430,34 +27434,34 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>5448</v>
+        <v>1968</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Klingvågen, Klingvågen, Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>477342</v>
+        <v>477332</v>
       </c>
       <c r="R257" t="n">
-        <v>7033020</v>
+        <v>7033029</v>
       </c>
       <c r="S257" t="n">
         <v>20</v>
@@ -27484,12 +27488,12 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27513,6 +27517,108 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>119477054</v>
+      </c>
+      <c r="B258" t="n">
+        <v>91883</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Klingvågen, Klingvågen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>477342</v>
+      </c>
+      <c r="R258" t="n">
+        <v>7033020</v>
+      </c>
+      <c r="S258" t="n">
+        <v>20</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AD258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY258"/>
+  <dimension ref="A1:AY261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23742,10 +23742,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119926437</v>
+        <v>119930975</v>
       </c>
       <c r="B222" t="n">
-        <v>87392</v>
+        <v>91832</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23754,38 +23754,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4405</v>
+        <v>4361</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Landvågen, Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>478883</v>
+        <v>477856</v>
       </c>
       <c r="R222" t="n">
-        <v>7034275</v>
+        <v>7035623</v>
       </c>
       <c r="S222" t="n">
         <v>20</v>
@@ -23844,10 +23844,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119927209</v>
+        <v>119927184</v>
       </c>
       <c r="B223" t="n">
-        <v>91832</v>
+        <v>86410</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23856,25 +23856,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>4361</v>
+        <v>249228</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23946,10 +23946,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119927771</v>
+        <v>119926530</v>
       </c>
       <c r="B224" t="n">
-        <v>91839</v>
+        <v>86334</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23962,21 +23962,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1435</v>
+        <v>445</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23986,10 +23986,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>478349</v>
+        <v>478870</v>
       </c>
       <c r="R224" t="n">
-        <v>7034098</v>
+        <v>7034193</v>
       </c>
       <c r="S224" t="n">
         <v>20</v>
@@ -24048,10 +24048,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119931445</v>
+        <v>119927395</v>
       </c>
       <c r="B225" t="n">
-        <v>91834</v>
+        <v>86289</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24064,34 +24064,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4362</v>
+        <v>427</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Storbäcken, Storbäcken, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>477968</v>
+        <v>478642</v>
       </c>
       <c r="R225" t="n">
-        <v>7035551</v>
+        <v>7034140</v>
       </c>
       <c r="S225" t="n">
         <v>20</v>
@@ -24150,10 +24150,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119930145</v>
+        <v>119927771</v>
       </c>
       <c r="B226" t="n">
-        <v>91259</v>
+        <v>91839</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24166,21 +24166,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>67</v>
+        <v>1435</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -24190,10 +24190,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>478186</v>
+        <v>478349</v>
       </c>
       <c r="R226" t="n">
-        <v>7035146</v>
+        <v>7034098</v>
       </c>
       <c r="S226" t="n">
         <v>20</v>
@@ -24252,10 +24252,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119930975</v>
+        <v>119930145</v>
       </c>
       <c r="B227" t="n">
-        <v>91832</v>
+        <v>91259</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24264,38 +24264,38 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4361</v>
+        <v>67</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Landvågen, Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>477856</v>
+        <v>478186</v>
       </c>
       <c r="R227" t="n">
-        <v>7035623</v>
+        <v>7035146</v>
       </c>
       <c r="S227" t="n">
         <v>20</v>
@@ -24354,10 +24354,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119926530</v>
+        <v>119927209</v>
       </c>
       <c r="B228" t="n">
-        <v>86334</v>
+        <v>91832</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24366,25 +24366,25 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>445</v>
+        <v>4361</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -24394,10 +24394,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>478870</v>
+        <v>478801</v>
       </c>
       <c r="R228" t="n">
-        <v>7034193</v>
+        <v>7034150</v>
       </c>
       <c r="S228" t="n">
         <v>20</v>
@@ -24456,10 +24456,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119927184</v>
+        <v>119931445</v>
       </c>
       <c r="B229" t="n">
-        <v>86410</v>
+        <v>91834</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24468,38 +24468,38 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>249228</v>
+        <v>4362</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Storbäcken, Storbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>478801</v>
+        <v>477968</v>
       </c>
       <c r="R229" t="n">
-        <v>7034150</v>
+        <v>7035551</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -24558,10 +24558,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119927395</v>
+        <v>119926437</v>
       </c>
       <c r="B230" t="n">
-        <v>86289</v>
+        <v>87392</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24570,25 +24570,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>427</v>
+        <v>4405</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24598,10 +24598,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>478642</v>
+        <v>478883</v>
       </c>
       <c r="R230" t="n">
-        <v>7034140</v>
+        <v>7034275</v>
       </c>
       <c r="S230" t="n">
         <v>20</v>
@@ -24766,10 +24766,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>111901519</v>
+        <v>120222779</v>
       </c>
       <c r="B232" t="n">
-        <v>86371</v>
+        <v>86334</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24778,41 +24778,41 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4412</v>
+        <v>445</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>477765</v>
+        <v>478400</v>
       </c>
       <c r="R232" t="n">
-        <v>7033404</v>
+        <v>7034025</v>
       </c>
       <c r="S232" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -24836,12 +24836,12 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24856,22 +24856,22 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>111901546</v>
+        <v>120224045</v>
       </c>
       <c r="B233" t="n">
-        <v>56430</v>
+        <v>79478</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24880,45 +24880,41 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100109</v>
+        <v>389</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>477668</v>
+        <v>478726</v>
       </c>
       <c r="R233" t="n">
-        <v>7033374</v>
+        <v>7034115</v>
       </c>
       <c r="S233" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -24942,17 +24938,12 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24967,22 +24958,22 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>111901547</v>
+        <v>120219366</v>
       </c>
       <c r="B234" t="n">
-        <v>56430</v>
+        <v>91839</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24991,45 +24982,41 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100109</v>
+        <v>1435</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>477524</v>
+        <v>478826</v>
       </c>
       <c r="R234" t="n">
-        <v>7033330</v>
+        <v>7034174</v>
       </c>
       <c r="S234" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -25053,17 +25040,12 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -25078,22 +25060,22 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>111901551</v>
+        <v>111901519</v>
       </c>
       <c r="B235" t="n">
-        <v>56430</v>
+        <v>86371</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25106,38 +25088,34 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>477433</v>
+        <v>477765</v>
       </c>
       <c r="R235" t="n">
-        <v>7033429</v>
+        <v>7033404</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25170,11 +25148,6 @@
       <c r="AA235" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -25201,10 +25174,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>111901518</v>
+        <v>111901546</v>
       </c>
       <c r="B236" t="n">
-        <v>86371</v>
+        <v>56430</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25217,34 +25190,38 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>477674</v>
+        <v>477668</v>
       </c>
       <c r="R236" t="n">
-        <v>7033500</v>
+        <v>7033374</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25277,6 +25254,11 @@
       <c r="AA236" t="inlineStr">
         <is>
           <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25303,10 +25285,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>111901587</v>
+        <v>111901547</v>
       </c>
       <c r="B237" t="n">
-        <v>56575</v>
+        <v>56430</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -25319,46 +25301,38 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>477611</v>
+        <v>477524</v>
       </c>
       <c r="R237" t="n">
-        <v>7033311</v>
+        <v>7033330</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25391,6 +25365,11 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25417,7 +25396,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>111901548</v>
+        <v>111901551</v>
       </c>
       <c r="B238" t="n">
         <v>56430</v>
@@ -25461,10 +25440,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>477476</v>
+        <v>477433</v>
       </c>
       <c r="R238" t="n">
-        <v>7033385</v>
+        <v>7033429</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25501,7 +25480,7 @@
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -25528,10 +25507,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>111901618</v>
+        <v>111901518</v>
       </c>
       <c r="B239" t="n">
-        <v>85197</v>
+        <v>86371</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25544,21 +25523,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>249278</v>
+        <v>4412</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -25568,10 +25547,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>477471</v>
+        <v>477674</v>
       </c>
       <c r="R239" t="n">
-        <v>7033412</v>
+        <v>7033500</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25630,10 +25609,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>111901549</v>
+        <v>111901587</v>
       </c>
       <c r="B240" t="n">
-        <v>56430</v>
+        <v>56575</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25646,38 +25625,46 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr"/>
       <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>477464</v>
+        <v>477611</v>
       </c>
       <c r="R240" t="n">
-        <v>7033364</v>
+        <v>7033311</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25710,11 +25697,6 @@
       <c r="AA240" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -25741,7 +25723,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>111901544</v>
+        <v>111901548</v>
       </c>
       <c r="B241" t="n">
         <v>56430</v>
@@ -25785,10 +25767,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>477639</v>
+        <v>477476</v>
       </c>
       <c r="R241" t="n">
-        <v>7033515</v>
+        <v>7033385</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25852,10 +25834,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>111901550</v>
+        <v>111901618</v>
       </c>
       <c r="B242" t="n">
-        <v>56430</v>
+        <v>85197</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25868,38 +25850,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100109</v>
+        <v>249278</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>477473</v>
+        <v>477471</v>
       </c>
       <c r="R242" t="n">
-        <v>7033404</v>
+        <v>7033412</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25932,11 +25910,6 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25963,7 +25936,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>111901545</v>
+        <v>111901549</v>
       </c>
       <c r="B243" t="n">
         <v>56430</v>
@@ -26007,10 +25980,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>477667</v>
+        <v>477464</v>
       </c>
       <c r="R243" t="n">
-        <v>7033500</v>
+        <v>7033364</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -26047,7 +26020,7 @@
       </c>
       <c r="AC243" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -26074,10 +26047,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>117085837</v>
+        <v>111901544</v>
       </c>
       <c r="B244" t="n">
-        <v>90463</v>
+        <v>56430</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -26090,37 +26063,41 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>477402</v>
+        <v>477639</v>
       </c>
       <c r="R244" t="n">
-        <v>7033066</v>
+        <v>7033515</v>
       </c>
       <c r="S244" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -26144,12 +26121,17 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -26164,22 +26146,22 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>117130130</v>
+        <v>111901550</v>
       </c>
       <c r="B245" t="n">
-        <v>91236</v>
+        <v>56430</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -26188,44 +26170,45 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>717</v>
+        <v>100109</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Stenbäcken, Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>477651</v>
+        <v>477473</v>
       </c>
       <c r="R245" t="n">
-        <v>7033403</v>
+        <v>7033404</v>
       </c>
       <c r="S245" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -26249,17 +26232,17 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>På levande asp. Trötta fruktkroppar.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -26268,29 +26251,28 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
-      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>117792165</v>
+        <v>111901545</v>
       </c>
       <c r="B246" t="n">
-        <v>90503</v>
+        <v>56430</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -26303,37 +26285,41 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>477450</v>
+        <v>477667</v>
       </c>
       <c r="R246" t="n">
-        <v>7033406</v>
+        <v>7033500</v>
       </c>
       <c r="S246" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -26357,12 +26343,17 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26377,22 +26368,22 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>118701501</v>
+        <v>117085837</v>
       </c>
       <c r="B247" t="n">
-        <v>97856</v>
+        <v>90463</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -26405,34 +26396,34 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>620</v>
+        <v>1202</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>477755</v>
+        <v>477402</v>
       </c>
       <c r="R247" t="n">
-        <v>7033301</v>
+        <v>7033066</v>
       </c>
       <c r="S247" t="n">
         <v>20</v>
@@ -26459,12 +26450,12 @@
       </c>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -26491,10 +26482,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>118703040</v>
+        <v>117130130</v>
       </c>
       <c r="B248" t="n">
-        <v>91803</v>
+        <v>91236</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26503,41 +26494,44 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>4366</v>
+        <v>717</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>477689</v>
+        <v>477651</v>
       </c>
       <c r="R248" t="n">
-        <v>7033262</v>
+        <v>7033403</v>
       </c>
       <c r="S248" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -26561,12 +26555,17 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>På levande asp. Trötta fruktkroppar.</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26575,6 +26574,7 @@
       <c r="AE248" t="b">
         <v>0</v>
       </c>
+      <c r="AF248" t="inlineStr"/>
       <c r="AG248" t="b">
         <v>0</v>
       </c>
@@ -26593,10 +26593,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>118861806</v>
+        <v>117792165</v>
       </c>
       <c r="B249" t="n">
-        <v>91776</v>
+        <v>90503</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26609,34 +26609,34 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1968</v>
+        <v>1202</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>477318</v>
+        <v>477450</v>
       </c>
       <c r="R249" t="n">
-        <v>7033069</v>
+        <v>7033406</v>
       </c>
       <c r="S249" t="n">
         <v>20</v>
@@ -26663,12 +26663,12 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26695,10 +26695,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>119048941</v>
+        <v>118701501</v>
       </c>
       <c r="B250" t="n">
-        <v>87388</v>
+        <v>97856</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26711,34 +26711,34 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>4412</v>
+        <v>620</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>477338</v>
+        <v>477755</v>
       </c>
       <c r="R250" t="n">
-        <v>7033068</v>
+        <v>7033301</v>
       </c>
       <c r="S250" t="n">
         <v>20</v>
@@ -26765,12 +26765,12 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26797,10 +26797,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>119048382</v>
+        <v>118703040</v>
       </c>
       <c r="B251" t="n">
-        <v>91807</v>
+        <v>91803</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26809,25 +26809,25 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1968</v>
+        <v>4366</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -26837,10 +26837,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>477617</v>
+        <v>477689</v>
       </c>
       <c r="R251" t="n">
-        <v>7033532</v>
+        <v>7033262</v>
       </c>
       <c r="S251" t="n">
         <v>20</v>
@@ -26867,12 +26867,12 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26899,10 +26899,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>119221941</v>
+        <v>118861806</v>
       </c>
       <c r="B252" t="n">
-        <v>84007</v>
+        <v>91776</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26915,34 +26915,34 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>5589</v>
+        <v>1968</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>477845</v>
+        <v>477318</v>
       </c>
       <c r="R252" t="n">
-        <v>7033413</v>
+        <v>7033069</v>
       </c>
       <c r="S252" t="n">
         <v>20</v>
@@ -26969,12 +26969,12 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -27001,10 +27001,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>117448064</v>
+        <v>119048941</v>
       </c>
       <c r="B253" t="n">
-        <v>90497</v>
+        <v>87388</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -27017,21 +27017,21 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1108</v>
+        <v>4412</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -27041,10 +27041,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>477365</v>
+        <v>477338</v>
       </c>
       <c r="R253" t="n">
-        <v>7032988</v>
+        <v>7033068</v>
       </c>
       <c r="S253" t="n">
         <v>20</v>
@@ -27071,12 +27071,12 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -27103,10 +27103,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>117448244</v>
+        <v>119048382</v>
       </c>
       <c r="B254" t="n">
-        <v>90519</v>
+        <v>91807</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -27119,34 +27119,34 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5432</v>
+        <v>1968</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>477439</v>
+        <v>477617</v>
       </c>
       <c r="R254" t="n">
-        <v>7033047</v>
+        <v>7033532</v>
       </c>
       <c r="S254" t="n">
         <v>20</v>
@@ -27173,12 +27173,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27205,10 +27205,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>118414846</v>
+        <v>119221941</v>
       </c>
       <c r="B255" t="n">
-        <v>91800</v>
+        <v>84007</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -27217,41 +27217,38 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>4366</v>
+        <v>5589</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
-      <c r="N255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>477357</v>
+        <v>477845</v>
       </c>
       <c r="R255" t="n">
-        <v>7033041</v>
+        <v>7033413</v>
       </c>
       <c r="S255" t="n">
         <v>20</v>
@@ -27278,17 +27275,12 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -27297,7 +27289,6 @@
       <c r="AE255" t="b">
         <v>0</v>
       </c>
-      <c r="AF255" t="inlineStr"/>
       <c r="AG255" t="b">
         <v>0</v>
       </c>
@@ -27316,10 +27307,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>118414787</v>
+        <v>117448064</v>
       </c>
       <c r="B256" t="n">
-        <v>90509</v>
+        <v>90497</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -27356,10 +27347,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>477367</v>
+        <v>477365</v>
       </c>
       <c r="R256" t="n">
-        <v>7032995</v>
+        <v>7032988</v>
       </c>
       <c r="S256" t="n">
         <v>20</v>
@@ -27386,12 +27377,12 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27418,10 +27409,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>118702006</v>
+        <v>117448244</v>
       </c>
       <c r="B257" t="n">
-        <v>91776</v>
+        <v>90519</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -27434,21 +27425,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>1968</v>
+        <v>5432</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -27458,10 +27449,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>477332</v>
+        <v>477439</v>
       </c>
       <c r="R257" t="n">
-        <v>7033029</v>
+        <v>7033047</v>
       </c>
       <c r="S257" t="n">
         <v>20</v>
@@ -27488,12 +27479,12 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27520,10 +27511,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>119477054</v>
+        <v>118414846</v>
       </c>
       <c r="B258" t="n">
-        <v>91883</v>
+        <v>91800</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27532,38 +27523,41 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>5448</v>
+        <v>4366</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Klingvågen, Klingvågen, Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>477342</v>
+        <v>477357</v>
       </c>
       <c r="R258" t="n">
-        <v>7033020</v>
+        <v>7033041</v>
       </c>
       <c r="S258" t="n">
         <v>20</v>
@@ -27590,12 +27584,17 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -27604,6 +27603,7 @@
       <c r="AE258" t="b">
         <v>0</v>
       </c>
+      <c r="AF258" t="inlineStr"/>
       <c r="AG258" t="b">
         <v>0</v>
       </c>
@@ -27619,6 +27619,312 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>118414787</v>
+      </c>
+      <c r="B259" t="n">
+        <v>90509</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr"/>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Klingvågen (Klingvågen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>477367</v>
+      </c>
+      <c r="R259" t="n">
+        <v>7032995</v>
+      </c>
+      <c r="S259" t="n">
+        <v>20</v>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AD259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT259" t="inlineStr"/>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>118702006</v>
+      </c>
+      <c r="B260" t="n">
+        <v>91776</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Bankera violascens</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr"/>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Klingvågen (Klingvågen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>477332</v>
+      </c>
+      <c r="R260" t="n">
+        <v>7033029</v>
+      </c>
+      <c r="S260" t="n">
+        <v>20</v>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT260" t="inlineStr"/>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>119477054</v>
+      </c>
+      <c r="B261" t="n">
+        <v>91883</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr"/>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Klingvågen, Klingvågen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>477342</v>
+      </c>
+      <c r="R261" t="n">
+        <v>7033020</v>
+      </c>
+      <c r="S261" t="n">
+        <v>20</v>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AD261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT261" t="inlineStr"/>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -24252,10 +24252,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119930145</v>
+        <v>119927209</v>
       </c>
       <c r="B227" t="n">
-        <v>91259</v>
+        <v>91832</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24264,25 +24264,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>67</v>
+        <v>4361</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24292,10 +24292,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>478186</v>
+        <v>478801</v>
       </c>
       <c r="R227" t="n">
-        <v>7035146</v>
+        <v>7034150</v>
       </c>
       <c r="S227" t="n">
         <v>20</v>
@@ -24354,10 +24354,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119927209</v>
+        <v>119931445</v>
       </c>
       <c r="B228" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24370,34 +24370,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Storbäcken, Storbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>478801</v>
+        <v>477968</v>
       </c>
       <c r="R228" t="n">
-        <v>7034150</v>
+        <v>7035551</v>
       </c>
       <c r="S228" t="n">
         <v>20</v>
@@ -24456,10 +24456,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119931445</v>
+        <v>119926437</v>
       </c>
       <c r="B229" t="n">
-        <v>91834</v>
+        <v>87392</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24468,38 +24468,38 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4362</v>
+        <v>4405</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Storbäcken, Storbäcken, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>477968</v>
+        <v>478883</v>
       </c>
       <c r="R229" t="n">
-        <v>7035551</v>
+        <v>7034275</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -24558,10 +24558,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119926437</v>
+        <v>119930145</v>
       </c>
       <c r="B230" t="n">
-        <v>87392</v>
+        <v>91259</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24570,25 +24570,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4405</v>
+        <v>67</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24598,10 +24598,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>478883</v>
+        <v>478186</v>
       </c>
       <c r="R230" t="n">
-        <v>7034275</v>
+        <v>7035146</v>
       </c>
       <c r="S230" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -24252,10 +24252,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119927209</v>
+        <v>119930145</v>
       </c>
       <c r="B227" t="n">
-        <v>91832</v>
+        <v>91259</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24264,25 +24264,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4361</v>
+        <v>67</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24292,10 +24292,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>478801</v>
+        <v>478186</v>
       </c>
       <c r="R227" t="n">
-        <v>7034150</v>
+        <v>7035146</v>
       </c>
       <c r="S227" t="n">
         <v>20</v>
@@ -24354,10 +24354,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119931445</v>
+        <v>119927209</v>
       </c>
       <c r="B228" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24370,34 +24370,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Storbäcken, Storbäcken, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>477968</v>
+        <v>478801</v>
       </c>
       <c r="R228" t="n">
-        <v>7035551</v>
+        <v>7034150</v>
       </c>
       <c r="S228" t="n">
         <v>20</v>
@@ -24456,10 +24456,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119926437</v>
+        <v>119931445</v>
       </c>
       <c r="B229" t="n">
-        <v>87392</v>
+        <v>91834</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24468,38 +24468,38 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4405</v>
+        <v>4362</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Storbäcken, Storbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>478883</v>
+        <v>477968</v>
       </c>
       <c r="R229" t="n">
-        <v>7034275</v>
+        <v>7035551</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -24558,10 +24558,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119930145</v>
+        <v>119926437</v>
       </c>
       <c r="B230" t="n">
-        <v>91259</v>
+        <v>87392</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24570,25 +24570,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>67</v>
+        <v>4405</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24598,10 +24598,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>478186</v>
+        <v>478883</v>
       </c>
       <c r="R230" t="n">
-        <v>7035146</v>
+        <v>7034275</v>
       </c>
       <c r="S230" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -21572,7 +21572,7 @@
         <v>119220936</v>
       </c>
       <c r="B201" t="n">
-        <v>86476</v>
+        <v>86478</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
       <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q201" t="n">
@@ -24252,10 +24252,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119930145</v>
+        <v>119927209</v>
       </c>
       <c r="B227" t="n">
-        <v>91259</v>
+        <v>91832</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24264,25 +24264,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>67</v>
+        <v>4361</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24292,10 +24292,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>478186</v>
+        <v>478801</v>
       </c>
       <c r="R227" t="n">
-        <v>7035146</v>
+        <v>7034150</v>
       </c>
       <c r="S227" t="n">
         <v>20</v>
@@ -24354,10 +24354,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119927209</v>
+        <v>119931445</v>
       </c>
       <c r="B228" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24370,34 +24370,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Storbäcken, Storbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>478801</v>
+        <v>477968</v>
       </c>
       <c r="R228" t="n">
-        <v>7034150</v>
+        <v>7035551</v>
       </c>
       <c r="S228" t="n">
         <v>20</v>
@@ -24456,10 +24456,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119931445</v>
+        <v>119926437</v>
       </c>
       <c r="B229" t="n">
-        <v>91834</v>
+        <v>87392</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24468,38 +24468,38 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4362</v>
+        <v>4405</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Storbäcken, Storbäcken, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>477968</v>
+        <v>478883</v>
       </c>
       <c r="R229" t="n">
-        <v>7035551</v>
+        <v>7034275</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -24558,10 +24558,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119926437</v>
+        <v>119930145</v>
       </c>
       <c r="B230" t="n">
-        <v>87392</v>
+        <v>91259</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24570,25 +24570,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4405</v>
+        <v>67</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24598,10 +24598,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>478883</v>
+        <v>478186</v>
       </c>
       <c r="R230" t="n">
-        <v>7034275</v>
+        <v>7035146</v>
       </c>
       <c r="S230" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -17875,7 +17875,7 @@
         <v>117919042</v>
       </c>
       <c r="B165" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>119220936</v>
       </c>
       <c r="B201" t="n">
-        <v>86478</v>
+        <v>86495</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -23742,10 +23742,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119930975</v>
+        <v>119926530</v>
       </c>
       <c r="B222" t="n">
-        <v>91832</v>
+        <v>86351</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23754,38 +23754,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4361</v>
+        <v>445</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Landvågen, Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>477856</v>
+        <v>478870</v>
       </c>
       <c r="R222" t="n">
-        <v>7035623</v>
+        <v>7034193</v>
       </c>
       <c r="S222" t="n">
         <v>20</v>
@@ -23847,7 +23847,7 @@
         <v>119927184</v>
       </c>
       <c r="B223" t="n">
-        <v>86410</v>
+        <v>86427</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23946,10 +23946,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119926530</v>
+        <v>119931445</v>
       </c>
       <c r="B224" t="n">
-        <v>86334</v>
+        <v>91852</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23958,38 +23958,38 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>445</v>
+        <v>4362</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Storbäcken, Storbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>478870</v>
+        <v>477968</v>
       </c>
       <c r="R224" t="n">
-        <v>7034193</v>
+        <v>7035551</v>
       </c>
       <c r="S224" t="n">
         <v>20</v>
@@ -24048,10 +24048,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119927395</v>
+        <v>119926437</v>
       </c>
       <c r="B225" t="n">
-        <v>86289</v>
+        <v>87409</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24060,25 +24060,25 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>427</v>
+        <v>4405</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -24088,10 +24088,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>478642</v>
+        <v>478883</v>
       </c>
       <c r="R225" t="n">
-        <v>7034140</v>
+        <v>7034275</v>
       </c>
       <c r="S225" t="n">
         <v>20</v>
@@ -24150,10 +24150,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119927771</v>
+        <v>119930145</v>
       </c>
       <c r="B226" t="n">
-        <v>91839</v>
+        <v>91277</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24166,21 +24166,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1435</v>
+        <v>67</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -24190,10 +24190,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>478349</v>
+        <v>478186</v>
       </c>
       <c r="R226" t="n">
-        <v>7034098</v>
+        <v>7035146</v>
       </c>
       <c r="S226" t="n">
         <v>20</v>
@@ -24252,10 +24252,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119930145</v>
+        <v>119927209</v>
       </c>
       <c r="B227" t="n">
-        <v>91259</v>
+        <v>91850</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24264,25 +24264,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>67</v>
+        <v>4361</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24292,10 +24292,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>478186</v>
+        <v>478801</v>
       </c>
       <c r="R227" t="n">
-        <v>7035146</v>
+        <v>7034150</v>
       </c>
       <c r="S227" t="n">
         <v>20</v>
@@ -24354,10 +24354,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119927209</v>
+        <v>119927395</v>
       </c>
       <c r="B228" t="n">
-        <v>91832</v>
+        <v>86306</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24370,21 +24370,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4361</v>
+        <v>427</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -24394,10 +24394,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>478801</v>
+        <v>478642</v>
       </c>
       <c r="R228" t="n">
-        <v>7034150</v>
+        <v>7034140</v>
       </c>
       <c r="S228" t="n">
         <v>20</v>
@@ -24456,10 +24456,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119931445</v>
+        <v>119927771</v>
       </c>
       <c r="B229" t="n">
-        <v>91834</v>
+        <v>91857</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24468,38 +24468,38 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4362</v>
+        <v>1435</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Storbäcken, Storbäcken, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>477968</v>
+        <v>478349</v>
       </c>
       <c r="R229" t="n">
-        <v>7035551</v>
+        <v>7034098</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -24558,10 +24558,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119926437</v>
+        <v>119930975</v>
       </c>
       <c r="B230" t="n">
-        <v>87392</v>
+        <v>91850</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24570,38 +24570,38 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4405</v>
+        <v>4361</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Landvågen, Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>478883</v>
+        <v>477856</v>
       </c>
       <c r="R230" t="n">
-        <v>7034275</v>
+        <v>7035623</v>
       </c>
       <c r="S230" t="n">
         <v>20</v>
@@ -24663,7 +24663,7 @@
         <v>120211708</v>
       </c>
       <c r="B231" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>120222779</v>
       </c>
       <c r="B232" t="n">
-        <v>86334</v>
+        <v>86351</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24868,10 +24868,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120224045</v>
+        <v>120219366</v>
       </c>
       <c r="B233" t="n">
-        <v>79478</v>
+        <v>91857</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24884,21 +24884,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>389</v>
+        <v>1435</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24908,10 +24908,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>478726</v>
+        <v>478826</v>
       </c>
       <c r="R233" t="n">
-        <v>7034115</v>
+        <v>7034174</v>
       </c>
       <c r="S233" t="n">
         <v>20</v>
@@ -24970,10 +24970,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120219366</v>
+        <v>120224045</v>
       </c>
       <c r="B234" t="n">
-        <v>91839</v>
+        <v>79494</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24986,21 +24986,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1435</v>
+        <v>389</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -25010,10 +25010,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>478826</v>
+        <v>478726</v>
       </c>
       <c r="R234" t="n">
-        <v>7034174</v>
+        <v>7034115</v>
       </c>
       <c r="S234" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -23742,10 +23742,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119926530</v>
+        <v>119927771</v>
       </c>
       <c r="B222" t="n">
-        <v>86351</v>
+        <v>91857</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23758,21 +23758,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>445</v>
+        <v>1435</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23782,10 +23782,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>478870</v>
+        <v>478349</v>
       </c>
       <c r="R222" t="n">
-        <v>7034193</v>
+        <v>7034098</v>
       </c>
       <c r="S222" t="n">
         <v>20</v>
@@ -23844,10 +23844,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119927184</v>
+        <v>119927395</v>
       </c>
       <c r="B223" t="n">
-        <v>86427</v>
+        <v>86306</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23856,25 +23856,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>249228</v>
+        <v>427</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23884,10 +23884,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>478801</v>
+        <v>478642</v>
       </c>
       <c r="R223" t="n">
-        <v>7034150</v>
+        <v>7034140</v>
       </c>
       <c r="S223" t="n">
         <v>20</v>
@@ -23946,10 +23946,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119931445</v>
+        <v>119926530</v>
       </c>
       <c r="B224" t="n">
-        <v>91852</v>
+        <v>86351</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23958,38 +23958,38 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4362</v>
+        <v>445</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Storbäcken, Storbäcken, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>477968</v>
+        <v>478870</v>
       </c>
       <c r="R224" t="n">
-        <v>7035551</v>
+        <v>7034193</v>
       </c>
       <c r="S224" t="n">
         <v>20</v>
@@ -24048,10 +24048,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119926437</v>
+        <v>119927209</v>
       </c>
       <c r="B225" t="n">
-        <v>87409</v>
+        <v>91850</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24060,25 +24060,25 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4405</v>
+        <v>4361</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -24088,10 +24088,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>478883</v>
+        <v>478801</v>
       </c>
       <c r="R225" t="n">
-        <v>7034275</v>
+        <v>7034150</v>
       </c>
       <c r="S225" t="n">
         <v>20</v>
@@ -24150,10 +24150,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119930145</v>
+        <v>119930975</v>
       </c>
       <c r="B226" t="n">
-        <v>91277</v>
+        <v>91850</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24162,38 +24162,38 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>67</v>
+        <v>4361</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Landvågen, Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>478186</v>
+        <v>477856</v>
       </c>
       <c r="R226" t="n">
-        <v>7035146</v>
+        <v>7035623</v>
       </c>
       <c r="S226" t="n">
         <v>20</v>
@@ -24252,10 +24252,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119927209</v>
+        <v>119930145</v>
       </c>
       <c r="B227" t="n">
-        <v>91850</v>
+        <v>91277</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24264,25 +24264,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4361</v>
+        <v>67</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24292,10 +24292,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>478801</v>
+        <v>478186</v>
       </c>
       <c r="R227" t="n">
-        <v>7034150</v>
+        <v>7035146</v>
       </c>
       <c r="S227" t="n">
         <v>20</v>
@@ -24354,10 +24354,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119927395</v>
+        <v>119931445</v>
       </c>
       <c r="B228" t="n">
-        <v>86306</v>
+        <v>91852</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24370,34 +24370,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>427</v>
+        <v>4362</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Storbäcken, Storbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>478642</v>
+        <v>477968</v>
       </c>
       <c r="R228" t="n">
-        <v>7034140</v>
+        <v>7035551</v>
       </c>
       <c r="S228" t="n">
         <v>20</v>
@@ -24456,10 +24456,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119927771</v>
+        <v>119926437</v>
       </c>
       <c r="B229" t="n">
-        <v>91857</v>
+        <v>87409</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24468,25 +24468,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1435</v>
+        <v>4405</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24496,10 +24496,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>478349</v>
+        <v>478883</v>
       </c>
       <c r="R229" t="n">
-        <v>7034098</v>
+        <v>7034275</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -24558,10 +24558,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119930975</v>
+        <v>119927184</v>
       </c>
       <c r="B230" t="n">
-        <v>91850</v>
+        <v>86427</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24570,38 +24570,38 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4361</v>
+        <v>249228</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Landvågen, Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>477856</v>
+        <v>478801</v>
       </c>
       <c r="R230" t="n">
-        <v>7035623</v>
+        <v>7034150</v>
       </c>
       <c r="S230" t="n">
         <v>20</v>
@@ -24766,10 +24766,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>120222779</v>
+        <v>120224045</v>
       </c>
       <c r="B232" t="n">
-        <v>86351</v>
+        <v>79494</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24782,21 +24782,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>445</v>
+        <v>389</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24806,10 +24806,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>478400</v>
+        <v>478726</v>
       </c>
       <c r="R232" t="n">
-        <v>7034025</v>
+        <v>7034115</v>
       </c>
       <c r="S232" t="n">
         <v>20</v>
@@ -24868,10 +24868,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120219366</v>
+        <v>120222779</v>
       </c>
       <c r="B233" t="n">
-        <v>91857</v>
+        <v>86351</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24884,21 +24884,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1435</v>
+        <v>445</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24908,10 +24908,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>478826</v>
+        <v>478400</v>
       </c>
       <c r="R233" t="n">
-        <v>7034174</v>
+        <v>7034025</v>
       </c>
       <c r="S233" t="n">
         <v>20</v>
@@ -24970,10 +24970,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120224045</v>
+        <v>120219366</v>
       </c>
       <c r="B234" t="n">
-        <v>79494</v>
+        <v>91857</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24986,21 +24986,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>389</v>
+        <v>1435</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -25010,10 +25010,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>478726</v>
+        <v>478826</v>
       </c>
       <c r="R234" t="n">
-        <v>7034115</v>
+        <v>7034174</v>
       </c>
       <c r="S234" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -23742,10 +23742,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119927771</v>
+        <v>119926437</v>
       </c>
       <c r="B222" t="n">
-        <v>91857</v>
+        <v>87409</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23754,25 +23754,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1435</v>
+        <v>4405</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23782,10 +23782,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>478349</v>
+        <v>478883</v>
       </c>
       <c r="R222" t="n">
-        <v>7034098</v>
+        <v>7034275</v>
       </c>
       <c r="S222" t="n">
         <v>20</v>
@@ -23844,10 +23844,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119927395</v>
+        <v>119926530</v>
       </c>
       <c r="B223" t="n">
-        <v>86306</v>
+        <v>86351</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23856,25 +23856,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23884,10 +23884,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>478642</v>
+        <v>478870</v>
       </c>
       <c r="R223" t="n">
-        <v>7034140</v>
+        <v>7034193</v>
       </c>
       <c r="S223" t="n">
         <v>20</v>
@@ -23946,10 +23946,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119926530</v>
+        <v>119930975</v>
       </c>
       <c r="B224" t="n">
-        <v>86351</v>
+        <v>91850</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23958,38 +23958,38 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>445</v>
+        <v>4361</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Landvågen, Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>478870</v>
+        <v>477856</v>
       </c>
       <c r="R224" t="n">
-        <v>7034193</v>
+        <v>7035623</v>
       </c>
       <c r="S224" t="n">
         <v>20</v>
@@ -24048,10 +24048,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119927209</v>
+        <v>119927395</v>
       </c>
       <c r="B225" t="n">
-        <v>91850</v>
+        <v>86306</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24064,21 +24064,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4361</v>
+        <v>427</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -24088,10 +24088,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>478801</v>
+        <v>478642</v>
       </c>
       <c r="R225" t="n">
-        <v>7034150</v>
+        <v>7034140</v>
       </c>
       <c r="S225" t="n">
         <v>20</v>
@@ -24150,10 +24150,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119930975</v>
+        <v>119930145</v>
       </c>
       <c r="B226" t="n">
-        <v>91850</v>
+        <v>91277</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24162,38 +24162,38 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4361</v>
+        <v>67</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Landvågen, Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>477856</v>
+        <v>478186</v>
       </c>
       <c r="R226" t="n">
-        <v>7035623</v>
+        <v>7035146</v>
       </c>
       <c r="S226" t="n">
         <v>20</v>
@@ -24252,10 +24252,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119930145</v>
+        <v>119927184</v>
       </c>
       <c r="B227" t="n">
-        <v>91277</v>
+        <v>86427</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24264,25 +24264,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>67</v>
+        <v>249228</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24292,10 +24292,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>478186</v>
+        <v>478801</v>
       </c>
       <c r="R227" t="n">
-        <v>7035146</v>
+        <v>7034150</v>
       </c>
       <c r="S227" t="n">
         <v>20</v>
@@ -24354,10 +24354,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119931445</v>
+        <v>119927209</v>
       </c>
       <c r="B228" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24370,34 +24370,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Storbäcken, Storbäcken, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>477968</v>
+        <v>478801</v>
       </c>
       <c r="R228" t="n">
-        <v>7035551</v>
+        <v>7034150</v>
       </c>
       <c r="S228" t="n">
         <v>20</v>
@@ -24456,10 +24456,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119926437</v>
+        <v>119927771</v>
       </c>
       <c r="B229" t="n">
-        <v>87409</v>
+        <v>91857</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24468,25 +24468,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4405</v>
+        <v>1435</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24496,10 +24496,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>478883</v>
+        <v>478349</v>
       </c>
       <c r="R229" t="n">
-        <v>7034275</v>
+        <v>7034098</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -24558,10 +24558,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119927184</v>
+        <v>119931445</v>
       </c>
       <c r="B230" t="n">
-        <v>86427</v>
+        <v>91852</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24570,38 +24570,38 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>249228</v>
+        <v>4362</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Storbäcken, Storbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>478801</v>
+        <v>477968</v>
       </c>
       <c r="R230" t="n">
-        <v>7034150</v>
+        <v>7035551</v>
       </c>
       <c r="S230" t="n">
         <v>20</v>
@@ -24766,10 +24766,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>120224045</v>
+        <v>120219366</v>
       </c>
       <c r="B232" t="n">
-        <v>79494</v>
+        <v>91857</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24782,21 +24782,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>389</v>
+        <v>1435</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24806,10 +24806,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>478726</v>
+        <v>478826</v>
       </c>
       <c r="R232" t="n">
-        <v>7034115</v>
+        <v>7034174</v>
       </c>
       <c r="S232" t="n">
         <v>20</v>
@@ -24868,10 +24868,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120222779</v>
+        <v>120224045</v>
       </c>
       <c r="B233" t="n">
-        <v>86351</v>
+        <v>79494</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24884,21 +24884,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>445</v>
+        <v>389</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24908,10 +24908,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>478400</v>
+        <v>478726</v>
       </c>
       <c r="R233" t="n">
-        <v>7034025</v>
+        <v>7034115</v>
       </c>
       <c r="S233" t="n">
         <v>20</v>
@@ -24970,10 +24970,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120219366</v>
+        <v>120222779</v>
       </c>
       <c r="B234" t="n">
-        <v>91857</v>
+        <v>86351</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24986,21 +24986,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1435</v>
+        <v>445</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -25010,10 +25010,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>478826</v>
+        <v>478400</v>
       </c>
       <c r="R234" t="n">
-        <v>7034174</v>
+        <v>7034025</v>
       </c>
       <c r="S234" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -24252,10 +24252,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119927184</v>
+        <v>119927209</v>
       </c>
       <c r="B227" t="n">
-        <v>86427</v>
+        <v>91850</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24264,25 +24264,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>249228</v>
+        <v>4361</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24354,10 +24354,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119927209</v>
+        <v>119927184</v>
       </c>
       <c r="B228" t="n">
-        <v>91850</v>
+        <v>86427</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24366,25 +24366,25 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4361</v>
+        <v>249228</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -23742,10 +23742,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119926437</v>
+        <v>119930975</v>
       </c>
       <c r="B222" t="n">
-        <v>87409</v>
+        <v>91850</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23754,38 +23754,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4405</v>
+        <v>4361</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Landvågen, Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>478883</v>
+        <v>477856</v>
       </c>
       <c r="R222" t="n">
-        <v>7034275</v>
+        <v>7035623</v>
       </c>
       <c r="S222" t="n">
         <v>20</v>
@@ -23844,10 +23844,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119926530</v>
+        <v>119927209</v>
       </c>
       <c r="B223" t="n">
-        <v>86351</v>
+        <v>91850</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23856,25 +23856,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>445</v>
+        <v>4361</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23884,10 +23884,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>478870</v>
+        <v>478801</v>
       </c>
       <c r="R223" t="n">
-        <v>7034193</v>
+        <v>7034150</v>
       </c>
       <c r="S223" t="n">
         <v>20</v>
@@ -23946,10 +23946,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119930975</v>
+        <v>119931445</v>
       </c>
       <c r="B224" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23962,34 +23962,34 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Landvågen, Landvågen, Jmt</t>
+          <t>Storbäcken, Storbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>477856</v>
+        <v>477968</v>
       </c>
       <c r="R224" t="n">
-        <v>7035623</v>
+        <v>7035551</v>
       </c>
       <c r="S224" t="n">
         <v>20</v>
@@ -24048,10 +24048,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119927395</v>
+        <v>119930145</v>
       </c>
       <c r="B225" t="n">
-        <v>86306</v>
+        <v>91277</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24060,25 +24060,25 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>427</v>
+        <v>67</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -24088,10 +24088,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>478642</v>
+        <v>478186</v>
       </c>
       <c r="R225" t="n">
-        <v>7034140</v>
+        <v>7035146</v>
       </c>
       <c r="S225" t="n">
         <v>20</v>
@@ -24150,10 +24150,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119930145</v>
+        <v>119927771</v>
       </c>
       <c r="B226" t="n">
-        <v>91277</v>
+        <v>91857</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24166,21 +24166,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>67</v>
+        <v>1435</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -24190,10 +24190,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>478186</v>
+        <v>478349</v>
       </c>
       <c r="R226" t="n">
-        <v>7035146</v>
+        <v>7034098</v>
       </c>
       <c r="S226" t="n">
         <v>20</v>
@@ -24252,10 +24252,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119927209</v>
+        <v>119927395</v>
       </c>
       <c r="B227" t="n">
-        <v>91850</v>
+        <v>86306</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24268,21 +24268,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4361</v>
+        <v>427</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24292,10 +24292,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>478801</v>
+        <v>478642</v>
       </c>
       <c r="R227" t="n">
-        <v>7034150</v>
+        <v>7034140</v>
       </c>
       <c r="S227" t="n">
         <v>20</v>
@@ -24456,10 +24456,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119927771</v>
+        <v>119926437</v>
       </c>
       <c r="B229" t="n">
-        <v>91857</v>
+        <v>87409</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24468,25 +24468,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1435</v>
+        <v>4405</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24496,10 +24496,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>478349</v>
+        <v>478883</v>
       </c>
       <c r="R229" t="n">
-        <v>7034098</v>
+        <v>7034275</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -24558,10 +24558,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119931445</v>
+        <v>119926530</v>
       </c>
       <c r="B230" t="n">
-        <v>91852</v>
+        <v>86351</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24570,38 +24570,38 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4362</v>
+        <v>445</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Storbäcken, Storbäcken, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>477968</v>
+        <v>478870</v>
       </c>
       <c r="R230" t="n">
-        <v>7035551</v>
+        <v>7034193</v>
       </c>
       <c r="S230" t="n">
         <v>20</v>
@@ -24766,10 +24766,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>120219366</v>
+        <v>120222779</v>
       </c>
       <c r="B232" t="n">
-        <v>91857</v>
+        <v>86351</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24782,21 +24782,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1435</v>
+        <v>445</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24806,10 +24806,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>478826</v>
+        <v>478400</v>
       </c>
       <c r="R232" t="n">
-        <v>7034174</v>
+        <v>7034025</v>
       </c>
       <c r="S232" t="n">
         <v>20</v>
@@ -24970,10 +24970,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120222779</v>
+        <v>120219366</v>
       </c>
       <c r="B234" t="n">
-        <v>86351</v>
+        <v>91857</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24986,21 +24986,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>445</v>
+        <v>1435</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -25010,10 +25010,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>478400</v>
+        <v>478826</v>
       </c>
       <c r="R234" t="n">
-        <v>7034025</v>
+        <v>7034174</v>
       </c>
       <c r="S234" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -23742,7 +23742,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119930975</v>
+        <v>119927209</v>
       </c>
       <c r="B222" t="n">
         <v>91850</v>
@@ -23778,14 +23778,14 @@
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Landvågen, Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>477856</v>
+        <v>478801</v>
       </c>
       <c r="R222" t="n">
-        <v>7035623</v>
+        <v>7034150</v>
       </c>
       <c r="S222" t="n">
         <v>20</v>
@@ -23844,7 +23844,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119927209</v>
+        <v>119930975</v>
       </c>
       <c r="B223" t="n">
         <v>91850</v>
@@ -23880,14 +23880,14 @@
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Landvågen, Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>478801</v>
+        <v>477856</v>
       </c>
       <c r="R223" t="n">
-        <v>7034150</v>
+        <v>7035623</v>
       </c>
       <c r="S223" t="n">
         <v>20</v>
@@ -23946,10 +23946,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119931445</v>
+        <v>119930145</v>
       </c>
       <c r="B224" t="n">
-        <v>91852</v>
+        <v>91277</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23958,38 +23958,38 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4362</v>
+        <v>67</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Storbäcken, Storbäcken, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>477968</v>
+        <v>478186</v>
       </c>
       <c r="R224" t="n">
-        <v>7035551</v>
+        <v>7035146</v>
       </c>
       <c r="S224" t="n">
         <v>20</v>
@@ -24048,10 +24048,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119930145</v>
+        <v>119931445</v>
       </c>
       <c r="B225" t="n">
-        <v>91277</v>
+        <v>91852</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24060,38 +24060,38 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>67</v>
+        <v>4362</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Storbäcken, Storbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>478186</v>
+        <v>477968</v>
       </c>
       <c r="R225" t="n">
-        <v>7035146</v>
+        <v>7035551</v>
       </c>
       <c r="S225" t="n">
         <v>20</v>
@@ -24150,10 +24150,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119927771</v>
+        <v>119926437</v>
       </c>
       <c r="B226" t="n">
-        <v>91857</v>
+        <v>87409</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24162,25 +24162,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1435</v>
+        <v>4405</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -24190,10 +24190,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>478349</v>
+        <v>478883</v>
       </c>
       <c r="R226" t="n">
-        <v>7034098</v>
+        <v>7034275</v>
       </c>
       <c r="S226" t="n">
         <v>20</v>
@@ -24252,10 +24252,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119927395</v>
+        <v>119927771</v>
       </c>
       <c r="B227" t="n">
-        <v>86306</v>
+        <v>91857</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24264,25 +24264,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>427</v>
+        <v>1435</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24292,10 +24292,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>478642</v>
+        <v>478349</v>
       </c>
       <c r="R227" t="n">
-        <v>7034140</v>
+        <v>7034098</v>
       </c>
       <c r="S227" t="n">
         <v>20</v>
@@ -24354,10 +24354,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119927184</v>
+        <v>119927395</v>
       </c>
       <c r="B228" t="n">
-        <v>86427</v>
+        <v>86306</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24366,25 +24366,25 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>249228</v>
+        <v>427</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -24394,10 +24394,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>478801</v>
+        <v>478642</v>
       </c>
       <c r="R228" t="n">
-        <v>7034150</v>
+        <v>7034140</v>
       </c>
       <c r="S228" t="n">
         <v>20</v>
@@ -24456,10 +24456,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119926437</v>
+        <v>119926530</v>
       </c>
       <c r="B229" t="n">
-        <v>87409</v>
+        <v>86351</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24468,25 +24468,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4405</v>
+        <v>445</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24496,10 +24496,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>478883</v>
+        <v>478870</v>
       </c>
       <c r="R229" t="n">
-        <v>7034275</v>
+        <v>7034193</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -24558,10 +24558,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119926530</v>
+        <v>119927184</v>
       </c>
       <c r="B230" t="n">
-        <v>86351</v>
+        <v>86427</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24570,25 +24570,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>445</v>
+        <v>249228</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24598,10 +24598,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>478870</v>
+        <v>478801</v>
       </c>
       <c r="R230" t="n">
-        <v>7034193</v>
+        <v>7034150</v>
       </c>
       <c r="S230" t="n">
         <v>20</v>
@@ -24766,10 +24766,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>120222779</v>
+        <v>120224045</v>
       </c>
       <c r="B232" t="n">
-        <v>86351</v>
+        <v>79494</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -24782,21 +24782,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>445</v>
+        <v>389</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24806,10 +24806,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>478400</v>
+        <v>478726</v>
       </c>
       <c r="R232" t="n">
-        <v>7034025</v>
+        <v>7034115</v>
       </c>
       <c r="S232" t="n">
         <v>20</v>
@@ -24868,10 +24868,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120224045</v>
+        <v>120219366</v>
       </c>
       <c r="B233" t="n">
-        <v>79494</v>
+        <v>91857</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24884,21 +24884,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>389</v>
+        <v>1435</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24908,10 +24908,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>478726</v>
+        <v>478826</v>
       </c>
       <c r="R233" t="n">
-        <v>7034115</v>
+        <v>7034174</v>
       </c>
       <c r="S233" t="n">
         <v>20</v>
@@ -24970,10 +24970,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120219366</v>
+        <v>120222779</v>
       </c>
       <c r="B234" t="n">
-        <v>91857</v>
+        <v>86351</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24986,21 +24986,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1435</v>
+        <v>445</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -25010,10 +25010,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>478826</v>
+        <v>478400</v>
       </c>
       <c r="R234" t="n">
-        <v>7034174</v>
+        <v>7034025</v>
       </c>
       <c r="S234" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -23742,10 +23742,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119927209</v>
+        <v>119927395</v>
       </c>
       <c r="B222" t="n">
-        <v>91850</v>
+        <v>86306</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23758,21 +23758,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4361</v>
+        <v>427</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23782,10 +23782,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>478801</v>
+        <v>478642</v>
       </c>
       <c r="R222" t="n">
-        <v>7034150</v>
+        <v>7034140</v>
       </c>
       <c r="S222" t="n">
         <v>20</v>
@@ -23844,7 +23844,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119930975</v>
+        <v>119927209</v>
       </c>
       <c r="B223" t="n">
         <v>91850</v>
@@ -23880,14 +23880,14 @@
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Landvågen, Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>477856</v>
+        <v>478801</v>
       </c>
       <c r="R223" t="n">
-        <v>7035623</v>
+        <v>7034150</v>
       </c>
       <c r="S223" t="n">
         <v>20</v>
@@ -23946,10 +23946,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119930145</v>
+        <v>119926437</v>
       </c>
       <c r="B224" t="n">
-        <v>91277</v>
+        <v>87409</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23958,25 +23958,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>67</v>
+        <v>4405</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23986,10 +23986,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>478186</v>
+        <v>478883</v>
       </c>
       <c r="R224" t="n">
-        <v>7035146</v>
+        <v>7034275</v>
       </c>
       <c r="S224" t="n">
         <v>20</v>
@@ -24048,10 +24048,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119931445</v>
+        <v>119926530</v>
       </c>
       <c r="B225" t="n">
-        <v>91852</v>
+        <v>86351</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24060,38 +24060,38 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4362</v>
+        <v>445</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Storbäcken, Storbäcken, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>477968</v>
+        <v>478870</v>
       </c>
       <c r="R225" t="n">
-        <v>7035551</v>
+        <v>7034193</v>
       </c>
       <c r="S225" t="n">
         <v>20</v>
@@ -24150,10 +24150,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119926437</v>
+        <v>119927771</v>
       </c>
       <c r="B226" t="n">
-        <v>87409</v>
+        <v>91857</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24162,25 +24162,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4405</v>
+        <v>1435</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -24190,10 +24190,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>478883</v>
+        <v>478349</v>
       </c>
       <c r="R226" t="n">
-        <v>7034275</v>
+        <v>7034098</v>
       </c>
       <c r="S226" t="n">
         <v>20</v>
@@ -24252,10 +24252,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119927771</v>
+        <v>119930975</v>
       </c>
       <c r="B227" t="n">
-        <v>91857</v>
+        <v>91850</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24264,38 +24264,38 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1435</v>
+        <v>4361</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Landvågen, Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>478349</v>
+        <v>477856</v>
       </c>
       <c r="R227" t="n">
-        <v>7034098</v>
+        <v>7035623</v>
       </c>
       <c r="S227" t="n">
         <v>20</v>
@@ -24354,10 +24354,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119927395</v>
+        <v>119931445</v>
       </c>
       <c r="B228" t="n">
-        <v>86306</v>
+        <v>91852</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24370,34 +24370,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>427</v>
+        <v>4362</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Storbäcken, Storbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>478642</v>
+        <v>477968</v>
       </c>
       <c r="R228" t="n">
-        <v>7034140</v>
+        <v>7035551</v>
       </c>
       <c r="S228" t="n">
         <v>20</v>
@@ -24456,10 +24456,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119926530</v>
+        <v>119930145</v>
       </c>
       <c r="B229" t="n">
-        <v>86351</v>
+        <v>91277</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24472,21 +24472,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>445</v>
+        <v>67</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24496,10 +24496,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>478870</v>
+        <v>478186</v>
       </c>
       <c r="R229" t="n">
-        <v>7034193</v>
+        <v>7035146</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -24868,10 +24868,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120219366</v>
+        <v>120222779</v>
       </c>
       <c r="B233" t="n">
-        <v>91857</v>
+        <v>86351</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24884,21 +24884,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1435</v>
+        <v>445</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24908,10 +24908,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>478826</v>
+        <v>478400</v>
       </c>
       <c r="R233" t="n">
-        <v>7034174</v>
+        <v>7034025</v>
       </c>
       <c r="S233" t="n">
         <v>20</v>
@@ -24970,10 +24970,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120222779</v>
+        <v>120219366</v>
       </c>
       <c r="B234" t="n">
-        <v>86351</v>
+        <v>91857</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24986,21 +24986,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>445</v>
+        <v>1435</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -25010,10 +25010,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>478400</v>
+        <v>478826</v>
       </c>
       <c r="R234" t="n">
-        <v>7034025</v>
+        <v>7034174</v>
       </c>
       <c r="S234" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -23742,10 +23742,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119927395</v>
+        <v>119926437</v>
       </c>
       <c r="B222" t="n">
-        <v>86306</v>
+        <v>87409</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23754,25 +23754,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>427</v>
+        <v>4405</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23782,10 +23782,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>478642</v>
+        <v>478883</v>
       </c>
       <c r="R222" t="n">
-        <v>7034140</v>
+        <v>7034275</v>
       </c>
       <c r="S222" t="n">
         <v>20</v>
@@ -23946,10 +23946,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119926437</v>
+        <v>119927771</v>
       </c>
       <c r="B224" t="n">
-        <v>87409</v>
+        <v>91857</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23958,25 +23958,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4405</v>
+        <v>1435</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23986,10 +23986,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>478883</v>
+        <v>478349</v>
       </c>
       <c r="R224" t="n">
-        <v>7034275</v>
+        <v>7034098</v>
       </c>
       <c r="S224" t="n">
         <v>20</v>
@@ -24150,10 +24150,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119927771</v>
+        <v>119930145</v>
       </c>
       <c r="B226" t="n">
-        <v>91857</v>
+        <v>91277</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24166,21 +24166,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1435</v>
+        <v>67</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -24190,10 +24190,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>478349</v>
+        <v>478186</v>
       </c>
       <c r="R226" t="n">
-        <v>7034098</v>
+        <v>7035146</v>
       </c>
       <c r="S226" t="n">
         <v>20</v>
@@ -24252,10 +24252,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119930975</v>
+        <v>119927184</v>
       </c>
       <c r="B227" t="n">
-        <v>91850</v>
+        <v>86427</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24264,38 +24264,38 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4361</v>
+        <v>249228</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Landvågen, Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>477856</v>
+        <v>478801</v>
       </c>
       <c r="R227" t="n">
-        <v>7035623</v>
+        <v>7034150</v>
       </c>
       <c r="S227" t="n">
         <v>20</v>
@@ -24456,10 +24456,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119930145</v>
+        <v>119927395</v>
       </c>
       <c r="B229" t="n">
-        <v>91277</v>
+        <v>86306</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24468,25 +24468,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>67</v>
+        <v>427</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24496,10 +24496,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>478186</v>
+        <v>478642</v>
       </c>
       <c r="R229" t="n">
-        <v>7035146</v>
+        <v>7034140</v>
       </c>
       <c r="S229" t="n">
         <v>20</v>
@@ -24558,10 +24558,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119927184</v>
+        <v>119930975</v>
       </c>
       <c r="B230" t="n">
-        <v>86427</v>
+        <v>91850</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24570,38 +24570,38 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>249228</v>
+        <v>4361</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Landvågen, Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>478801</v>
+        <v>477856</v>
       </c>
       <c r="R230" t="n">
-        <v>7034150</v>
+        <v>7035623</v>
       </c>
       <c r="S230" t="n">
         <v>20</v>
@@ -24868,10 +24868,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120222779</v>
+        <v>120219366</v>
       </c>
       <c r="B233" t="n">
-        <v>86351</v>
+        <v>91857</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24884,21 +24884,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>445</v>
+        <v>1435</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24908,10 +24908,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>478400</v>
+        <v>478826</v>
       </c>
       <c r="R233" t="n">
-        <v>7034025</v>
+        <v>7034174</v>
       </c>
       <c r="S233" t="n">
         <v>20</v>
@@ -24970,10 +24970,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120219366</v>
+        <v>120222779</v>
       </c>
       <c r="B234" t="n">
-        <v>91857</v>
+        <v>86351</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24986,21 +24986,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1435</v>
+        <v>445</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -25010,10 +25010,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>478826</v>
+        <v>478400</v>
       </c>
       <c r="R234" t="n">
-        <v>7034174</v>
+        <v>7034025</v>
       </c>
       <c r="S234" t="n">
         <v>20</v>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -21572,7 +21572,7 @@
         <v>119220936</v>
       </c>
       <c r="B201" t="n">
-        <v>86134</v>
+        <v>86137</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>121241528</v>
       </c>
       <c r="B235" t="n">
-        <v>82382</v>
+        <v>82385</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>121241556</v>
       </c>
       <c r="B257" t="n">
-        <v>79187</v>
+        <v>79190</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -19413,7 +19413,7 @@
         <v>118700504</v>
       </c>
       <c r="B180" t="n">
-        <v>97856</v>
+        <v>98092</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19444,9 +19444,13 @@
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
@@ -19494,6 +19498,7 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
+      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
@@ -21572,7 +21577,7 @@
         <v>119220936</v>
       </c>
       <c r="B201" t="n">
-        <v>86137</v>
+        <v>86143</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -25079,7 +25084,7 @@
         <v>121241528</v>
       </c>
       <c r="B235" t="n">
-        <v>82385</v>
+        <v>82388</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -27420,7 +27425,7 @@
         <v>121241556</v>
       </c>
       <c r="B257" t="n">
-        <v>79190</v>
+        <v>79193</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -19413,7 +19413,7 @@
         <v>118700504</v>
       </c>
       <c r="B180" t="n">
-        <v>98092</v>
+        <v>98093</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -19413,7 +19413,7 @@
         <v>118700504</v>
       </c>
       <c r="B180" t="n">
-        <v>98093</v>
+        <v>98096</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>119220936</v>
       </c>
       <c r="B201" t="n">
-        <v>86143</v>
+        <v>86146</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>121241528</v>
       </c>
       <c r="B235" t="n">
-        <v>82388</v>
+        <v>82391</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>121241556</v>
       </c>
       <c r="B257" t="n">
-        <v>79193</v>
+        <v>79196</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -19413,7 +19413,7 @@
         <v>118700504</v>
       </c>
       <c r="B180" t="n">
-        <v>98096</v>
+        <v>98102</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>119220936</v>
       </c>
       <c r="B201" t="n">
-        <v>86146</v>
+        <v>86150</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>121241528</v>
       </c>
       <c r="B235" t="n">
-        <v>82391</v>
+        <v>82392</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>121241556</v>
       </c>
       <c r="B257" t="n">
-        <v>79196</v>
+        <v>79197</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -19928,11 +19928,11 @@
         <v>118698082</v>
       </c>
       <c r="B185" t="n">
-        <v>85800</v>
+        <v>87896</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dialog hos validator</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -19941,21 +19941,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>236437</v>
+        <v>236435</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Droppklibbskivling</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Limacella guttata</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Pers. : Fr.) Konrad &amp; Maubl.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19964,7 +19964,7 @@
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Storbäcken (Storbäcken), Jmt</t>
+          <t>Storbäcken, Storbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -19413,7 +19413,7 @@
         <v>118700504</v>
       </c>
       <c r="B180" t="n">
-        <v>98102</v>
+        <v>98103</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>119220936</v>
       </c>
       <c r="B201" t="n">
-        <v>86150</v>
+        <v>86151</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>121241528</v>
       </c>
       <c r="B235" t="n">
-        <v>82392</v>
+        <v>82393</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>121241556</v>
       </c>
       <c r="B257" t="n">
-        <v>79197</v>
+        <v>79198</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -21577,7 +21577,7 @@
         <v>119220936</v>
       </c>
       <c r="B201" t="n">
-        <v>86209</v>
+        <v>86210</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>119220331</v>
       </c>
       <c r="B207" t="n">
-        <v>89435</v>
+        <v>89445</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>119473822</v>
       </c>
       <c r="B220" t="n">
-        <v>86236</v>
+        <v>86237</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>119475515</v>
       </c>
       <c r="B221" t="n">
-        <v>86250</v>
+        <v>86251</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>120224045</v>
       </c>
       <c r="B233" t="n">
-        <v>79597</v>
+        <v>79598</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -21577,7 +21577,7 @@
         <v>119220936</v>
       </c>
       <c r="B201" t="n">
-        <v>86210</v>
+        <v>86215</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>119220331</v>
       </c>
       <c r="B207" t="n">
-        <v>89445</v>
+        <v>89457</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>119473822</v>
       </c>
       <c r="B220" t="n">
-        <v>86237</v>
+        <v>86242</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>119475515</v>
       </c>
       <c r="B221" t="n">
-        <v>86251</v>
+        <v>86257</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>120224045</v>
       </c>
       <c r="B233" t="n">
-        <v>79598</v>
+        <v>79603</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -21577,7 +21577,7 @@
         <v>119220936</v>
       </c>
       <c r="B201" t="n">
-        <v>86215</v>
+        <v>86219</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>119220331</v>
       </c>
       <c r="B207" t="n">
-        <v>89457</v>
+        <v>89461</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>119473822</v>
       </c>
       <c r="B220" t="n">
-        <v>86242</v>
+        <v>86246</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>119475515</v>
       </c>
       <c r="B221" t="n">
-        <v>86257</v>
+        <v>86261</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -22198,7 +22198,7 @@
         <v>119220331</v>
       </c>
       <c r="B207" t="n">
-        <v>89598</v>
+        <v>89602</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -24894,7 +24894,7 @@
         <v>120224045</v>
       </c>
       <c r="B233" t="n">
-        <v>79603</v>
+        <v>79718</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>På medelgrov asp i en liten glänta i gammal granskog. Gläntan håller på att växa igen.</t>
+          <t>På medelgrov asp i en liten glänta i gammal granskog.</t>
         </is>
       </c>
       <c r="AD233" t="b">

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -22198,7 +22198,7 @@
         <v>119220331</v>
       </c>
       <c r="B207" t="n">
-        <v>89602</v>
+        <v>89605</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>120224045</v>
       </c>
       <c r="B233" t="n">
-        <v>79718</v>
+        <v>79721</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -22198,7 +22198,7 @@
         <v>119220331</v>
       </c>
       <c r="B207" t="n">
-        <v>89605</v>
+        <v>89607</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>120224045</v>
       </c>
       <c r="B233" t="n">
-        <v>79721</v>
+        <v>79723</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -22198,7 +22198,7 @@
         <v>119220331</v>
       </c>
       <c r="B207" t="n">
-        <v>89607</v>
+        <v>89609</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>120224045</v>
       </c>
       <c r="B233" t="n">
-        <v>79723</v>
+        <v>79724</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY263"/>
+  <dimension ref="A1:AY264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25210,10 +25210,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>111901519</v>
+        <v>125536112</v>
       </c>
       <c r="B236" t="n">
-        <v>86371</v>
+        <v>91219</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25222,38 +25222,41 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4412</v>
+        <v>5321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>477765</v>
+        <v>478730</v>
       </c>
       <c r="R236" t="n">
-        <v>7033404</v>
+        <v>7034435</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25280,12 +25283,12 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25294,28 +25297,44 @@
       <c r="AE236" t="b">
         <v>0</v>
       </c>
+      <c r="AF236" t="inlineStr"/>
       <c r="AG236" t="b">
         <v>0</v>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>Gammal grannaturskog</t>
+        </is>
+      </c>
+      <c r="AL236" t="inlineStr">
+        <is>
+          <t>Asphögstubbe</t>
+        </is>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t>Asphögstubbe</t>
+        </is>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>111901546</v>
+        <v>111901519</v>
       </c>
       <c r="B237" t="n">
-        <v>56430</v>
+        <v>86371</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -25328,38 +25347,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>477668</v>
+        <v>477765</v>
       </c>
       <c r="R237" t="n">
-        <v>7033374</v>
+        <v>7033404</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25392,11 +25407,6 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25423,7 +25433,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>111901547</v>
+        <v>111901546</v>
       </c>
       <c r="B238" t="n">
         <v>56430</v>
@@ -25467,10 +25477,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>477524</v>
+        <v>477668</v>
       </c>
       <c r="R238" t="n">
-        <v>7033330</v>
+        <v>7033374</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25507,7 +25517,7 @@
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -25534,7 +25544,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>111901551</v>
+        <v>111901547</v>
       </c>
       <c r="B239" t="n">
         <v>56430</v>
@@ -25578,10 +25588,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>477433</v>
+        <v>477524</v>
       </c>
       <c r="R239" t="n">
-        <v>7033429</v>
+        <v>7033330</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25645,10 +25655,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>111901518</v>
+        <v>111901551</v>
       </c>
       <c r="B240" t="n">
-        <v>86371</v>
+        <v>56430</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25661,34 +25671,38 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>477674</v>
+        <v>477433</v>
       </c>
       <c r="R240" t="n">
-        <v>7033500</v>
+        <v>7033429</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25721,6 +25735,11 @@
       <c r="AA240" t="inlineStr">
         <is>
           <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -25747,10 +25766,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>111901587</v>
+        <v>111901518</v>
       </c>
       <c r="B241" t="n">
-        <v>56575</v>
+        <v>86371</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25763,46 +25782,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>103021</v>
+        <v>4412</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>477611</v>
+        <v>477674</v>
       </c>
       <c r="R241" t="n">
-        <v>7033311</v>
+        <v>7033500</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25861,10 +25868,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>111901548</v>
+        <v>111901587</v>
       </c>
       <c r="B242" t="n">
-        <v>56430</v>
+        <v>56575</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25877,38 +25884,46 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P242" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>477476</v>
+        <v>477611</v>
       </c>
       <c r="R242" t="n">
-        <v>7033385</v>
+        <v>7033311</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25941,11 +25956,6 @@
       <c r="AA242" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25972,10 +25982,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>111901618</v>
+        <v>111901548</v>
       </c>
       <c r="B243" t="n">
-        <v>85197</v>
+        <v>56430</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25988,34 +25998,38 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>249278</v>
+        <v>100109</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>477471</v>
+        <v>477476</v>
       </c>
       <c r="R243" t="n">
-        <v>7033412</v>
+        <v>7033385</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -26048,6 +26062,11 @@
       <c r="AA243" t="inlineStr">
         <is>
           <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -26074,10 +26093,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>111901549</v>
+        <v>111901618</v>
       </c>
       <c r="B244" t="n">
-        <v>56430</v>
+        <v>85197</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -26090,38 +26109,34 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100109</v>
+        <v>249278</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>477464</v>
+        <v>477471</v>
       </c>
       <c r="R244" t="n">
-        <v>7033364</v>
+        <v>7033412</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -26154,11 +26169,6 @@
       <c r="AA244" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -26185,7 +26195,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>111901544</v>
+        <v>111901549</v>
       </c>
       <c r="B245" t="n">
         <v>56430</v>
@@ -26229,10 +26239,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>477639</v>
+        <v>477464</v>
       </c>
       <c r="R245" t="n">
-        <v>7033515</v>
+        <v>7033364</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -26269,7 +26279,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -26296,7 +26306,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>111901550</v>
+        <v>111901544</v>
       </c>
       <c r="B246" t="n">
         <v>56430</v>
@@ -26340,10 +26350,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>477473</v>
+        <v>477639</v>
       </c>
       <c r="R246" t="n">
-        <v>7033404</v>
+        <v>7033515</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -26407,7 +26417,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>111901545</v>
+        <v>111901550</v>
       </c>
       <c r="B247" t="n">
         <v>56430</v>
@@ -26451,10 +26461,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>477667</v>
+        <v>477473</v>
       </c>
       <c r="R247" t="n">
-        <v>7033500</v>
+        <v>7033404</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26518,10 +26528,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>117085837</v>
+        <v>111901545</v>
       </c>
       <c r="B248" t="n">
-        <v>90463</v>
+        <v>56430</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26534,37 +26544,41 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>477402</v>
+        <v>477667</v>
       </c>
       <c r="R248" t="n">
-        <v>7033066</v>
+        <v>7033500</v>
       </c>
       <c r="S248" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -26588,12 +26602,17 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26608,22 +26627,22 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>117130130</v>
+        <v>117085837</v>
       </c>
       <c r="B249" t="n">
-        <v>91236</v>
+        <v>90463</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26632,44 +26651,41 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>717</v>
+        <v>1202</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Stenbäcken, Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>477651</v>
+        <v>477402</v>
       </c>
       <c r="R249" t="n">
-        <v>7033403</v>
+        <v>7033066</v>
       </c>
       <c r="S249" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26701,18 +26717,12 @@
           <t>2024-05-19</t>
         </is>
       </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>På levande asp. Trötta fruktkroppar.</t>
-        </is>
-      </c>
       <c r="AD249" t="b">
         <v>0</v>
       </c>
       <c r="AE249" t="b">
         <v>0</v>
       </c>
-      <c r="AF249" t="inlineStr"/>
       <c r="AG249" t="b">
         <v>0</v>
       </c>
@@ -26731,10 +26741,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>117792165</v>
+        <v>117130130</v>
       </c>
       <c r="B250" t="n">
-        <v>90503</v>
+        <v>91236</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26743,41 +26753,44 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1202</v>
+        <v>717</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>477450</v>
+        <v>477651</v>
       </c>
       <c r="R250" t="n">
-        <v>7033406</v>
+        <v>7033403</v>
       </c>
       <c r="S250" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -26801,12 +26814,17 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>På levande asp. Trötta fruktkroppar.</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26815,6 +26833,7 @@
       <c r="AE250" t="b">
         <v>0</v>
       </c>
+      <c r="AF250" t="inlineStr"/>
       <c r="AG250" t="b">
         <v>0</v>
       </c>
@@ -26833,10 +26852,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>118701501</v>
+        <v>117792165</v>
       </c>
       <c r="B251" t="n">
-        <v>97856</v>
+        <v>90503</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26849,21 +26868,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>620</v>
+        <v>1202</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -26873,10 +26892,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>477755</v>
+        <v>477450</v>
       </c>
       <c r="R251" t="n">
-        <v>7033301</v>
+        <v>7033406</v>
       </c>
       <c r="S251" t="n">
         <v>20</v>
@@ -26903,12 +26922,12 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26935,10 +26954,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>118703040</v>
+        <v>118701501</v>
       </c>
       <c r="B252" t="n">
-        <v>91803</v>
+        <v>97856</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26947,25 +26966,25 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>4366</v>
+        <v>620</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -26975,10 +26994,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>477689</v>
+        <v>477755</v>
       </c>
       <c r="R252" t="n">
-        <v>7033262</v>
+        <v>7033301</v>
       </c>
       <c r="S252" t="n">
         <v>20</v>
@@ -27037,10 +27056,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>118861806</v>
+        <v>118703040</v>
       </c>
       <c r="B253" t="n">
-        <v>91776</v>
+        <v>91803</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -27049,38 +27068,38 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1968</v>
+        <v>4366</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>477318</v>
+        <v>477689</v>
       </c>
       <c r="R253" t="n">
-        <v>7033069</v>
+        <v>7033262</v>
       </c>
       <c r="S253" t="n">
         <v>20</v>
@@ -27107,12 +27126,12 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -27139,10 +27158,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>119048941</v>
+        <v>118861806</v>
       </c>
       <c r="B254" t="n">
-        <v>87388</v>
+        <v>91776</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -27155,21 +27174,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4412</v>
+        <v>1968</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -27179,10 +27198,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>477338</v>
+        <v>477318</v>
       </c>
       <c r="R254" t="n">
-        <v>7033068</v>
+        <v>7033069</v>
       </c>
       <c r="S254" t="n">
         <v>20</v>
@@ -27209,12 +27228,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27241,10 +27260,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>119048382</v>
+        <v>119048941</v>
       </c>
       <c r="B255" t="n">
-        <v>91807</v>
+        <v>87388</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -27257,34 +27276,34 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1968</v>
+        <v>4412</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>477617</v>
+        <v>477338</v>
       </c>
       <c r="R255" t="n">
-        <v>7033532</v>
+        <v>7033068</v>
       </c>
       <c r="S255" t="n">
         <v>20</v>
@@ -27343,10 +27362,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>119221941</v>
+        <v>119048382</v>
       </c>
       <c r="B256" t="n">
-        <v>84007</v>
+        <v>91807</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -27359,21 +27378,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5589</v>
+        <v>1968</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -27383,10 +27402,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>477845</v>
+        <v>477617</v>
       </c>
       <c r="R256" t="n">
-        <v>7033413</v>
+        <v>7033532</v>
       </c>
       <c r="S256" t="n">
         <v>20</v>
@@ -27413,12 +27432,12 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27445,10 +27464,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>121241556</v>
+        <v>119221941</v>
       </c>
       <c r="B257" t="n">
-        <v>79198</v>
+        <v>84007</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -27461,40 +27480,37 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>229821</v>
+        <v>5589</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
-      <c r="N257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Stenbäcken, Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>478098</v>
+        <v>477845</v>
       </c>
       <c r="R257" t="n">
-        <v>7033575</v>
+        <v>7033413</v>
       </c>
       <c r="S257" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -27518,12 +27534,12 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27532,7 +27548,6 @@
       <c r="AE257" t="b">
         <v>0</v>
       </c>
-      <c r="AF257" t="inlineStr"/>
       <c r="AG257" t="b">
         <v>0</v>
       </c>
@@ -27551,10 +27566,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>117448064</v>
+        <v>121241556</v>
       </c>
       <c r="B258" t="n">
-        <v>90497</v>
+        <v>79198</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27567,37 +27582,40 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>1108</v>
+        <v>229821</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>477365</v>
+        <v>478098</v>
       </c>
       <c r="R258" t="n">
-        <v>7032988</v>
+        <v>7033575</v>
       </c>
       <c r="S258" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -27621,12 +27639,12 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -27635,6 +27653,7 @@
       <c r="AE258" t="b">
         <v>0</v>
       </c>
+      <c r="AF258" t="inlineStr"/>
       <c r="AG258" t="b">
         <v>0</v>
       </c>
@@ -27653,10 +27672,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>117448244</v>
+        <v>117448064</v>
       </c>
       <c r="B259" t="n">
-        <v>90519</v>
+        <v>90497</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27669,21 +27688,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -27693,10 +27712,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>477439</v>
+        <v>477365</v>
       </c>
       <c r="R259" t="n">
-        <v>7033047</v>
+        <v>7032988</v>
       </c>
       <c r="S259" t="n">
         <v>20</v>
@@ -27755,10 +27774,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>118414846</v>
+        <v>117448244</v>
       </c>
       <c r="B260" t="n">
-        <v>91800</v>
+        <v>90519</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27767,41 +27786,38 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>4366</v>
+        <v>5432</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
           <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>477357</v>
+        <v>477439</v>
       </c>
       <c r="R260" t="n">
-        <v>7033041</v>
+        <v>7033047</v>
       </c>
       <c r="S260" t="n">
         <v>20</v>
@@ -27828,17 +27844,12 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -27847,7 +27858,6 @@
       <c r="AE260" t="b">
         <v>0</v>
       </c>
-      <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="b">
         <v>0</v>
       </c>
@@ -27866,10 +27876,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>118414787</v>
+        <v>118414846</v>
       </c>
       <c r="B261" t="n">
-        <v>90509</v>
+        <v>91800</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27878,38 +27888,41 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1108</v>
+        <v>4366</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
           <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>477367</v>
+        <v>477357</v>
       </c>
       <c r="R261" t="n">
-        <v>7032995</v>
+        <v>7033041</v>
       </c>
       <c r="S261" t="n">
         <v>20</v>
@@ -27944,12 +27957,18 @@
           <t>2024-07-13</t>
         </is>
       </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
+        </is>
+      </c>
       <c r="AD261" t="b">
         <v>0</v>
       </c>
       <c r="AE261" t="b">
         <v>0</v>
       </c>
+      <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
         <v>0</v>
       </c>
@@ -27968,10 +27987,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>118702006</v>
+        <v>118414787</v>
       </c>
       <c r="B262" t="n">
-        <v>91776</v>
+        <v>90509</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27984,21 +28003,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -28008,10 +28027,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>477332</v>
+        <v>477367</v>
       </c>
       <c r="R262" t="n">
-        <v>7033029</v>
+        <v>7032995</v>
       </c>
       <c r="S262" t="n">
         <v>20</v>
@@ -28038,12 +28057,12 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -28070,10 +28089,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>119477054</v>
+        <v>118702006</v>
       </c>
       <c r="B263" t="n">
-        <v>91883</v>
+        <v>91776</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -28086,34 +28105,34 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>5448</v>
+        <v>1968</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Klingvågen, Klingvågen, Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>477342</v>
+        <v>477332</v>
       </c>
       <c r="R263" t="n">
-        <v>7033020</v>
+        <v>7033029</v>
       </c>
       <c r="S263" t="n">
         <v>20</v>
@@ -28140,12 +28159,12 @@
       </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -28169,6 +28188,108 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>119477054</v>
+      </c>
+      <c r="B264" t="n">
+        <v>91883</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr"/>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>Klingvågen, Klingvågen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>477342</v>
+      </c>
+      <c r="R264" t="n">
+        <v>7033020</v>
+      </c>
+      <c r="S264" t="n">
+        <v>20</v>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AD264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT264" t="inlineStr"/>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY264" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY264"/>
+  <dimension ref="A1:AY271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25331,10 +25331,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>111901519</v>
+        <v>125652112</v>
       </c>
       <c r="B237" t="n">
-        <v>86371</v>
+        <v>77889</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -25347,37 +25347,40 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4412</v>
+        <v>314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>477765</v>
+        <v>478893</v>
       </c>
       <c r="R237" t="n">
-        <v>7033404</v>
+        <v>7034299</v>
       </c>
       <c r="S237" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -25401,12 +25404,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25415,28 +25418,34 @@
       <c r="AE237" t="b">
         <v>0</v>
       </c>
+      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>Grannaturskog vid bäckdråg</t>
+        </is>
       </c>
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>111901546</v>
+        <v>125653096</v>
       </c>
       <c r="B238" t="n">
-        <v>56430</v>
+        <v>98175</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25445,45 +25454,41 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>100109</v>
+        <v>504</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>477668</v>
+        <v>478457</v>
       </c>
       <c r="R238" t="n">
-        <v>7033374</v>
+        <v>7034140</v>
       </c>
       <c r="S238" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -25507,17 +25512,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -25528,26 +25528,31 @@
       </c>
       <c r="AG238" t="b">
         <v>0</v>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>111901547</v>
+        <v>125654473</v>
       </c>
       <c r="B239" t="n">
-        <v>56430</v>
+        <v>83036</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25556,45 +25561,44 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100109</v>
+        <v>750</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Klotsporig murkla</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gyromitra sphaerospora</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Sacc.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>477524</v>
+        <v>478460</v>
       </c>
       <c r="R239" t="n">
-        <v>7033330</v>
+        <v>7034711</v>
       </c>
       <c r="S239" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -25618,17 +25622,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -25637,28 +25636,44 @@
       <c r="AE239" t="b">
         <v>0</v>
       </c>
+      <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="b">
         <v>0</v>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>Grannaturskog på kalkrik berggrund</t>
+        </is>
+      </c>
+      <c r="AL239" t="inlineStr">
+        <is>
+          <t>På förnalager ovanpå en rötbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>På förnalager ovanpå en rötbruten granlåga</t>
+        </is>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>111901551</v>
+        <v>125652823</v>
       </c>
       <c r="B240" t="n">
-        <v>56430</v>
+        <v>74836</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -25667,45 +25682,41 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>477433</v>
+        <v>478483</v>
       </c>
       <c r="R240" t="n">
-        <v>7033429</v>
+        <v>7034170</v>
       </c>
       <c r="S240" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -25729,17 +25740,12 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -25750,26 +25756,31 @@
       </c>
       <c r="AG240" t="b">
         <v>0</v>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>111901518</v>
+        <v>125652111</v>
       </c>
       <c r="B241" t="n">
-        <v>86371</v>
+        <v>75025</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25782,37 +25793,40 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>4412</v>
+        <v>6440</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>477674</v>
+        <v>478893</v>
       </c>
       <c r="R241" t="n">
-        <v>7033500</v>
+        <v>7034299</v>
       </c>
       <c r="S241" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -25836,12 +25850,12 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -25850,28 +25864,34 @@
       <c r="AE241" t="b">
         <v>0</v>
       </c>
+      <c r="AF241" t="inlineStr"/>
       <c r="AG241" t="b">
         <v>0</v>
+      </c>
+      <c r="AI241" t="inlineStr">
+        <is>
+          <t>Grannaturskog vid bäckdråg</t>
+        </is>
       </c>
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>111901587</v>
+        <v>125654533</v>
       </c>
       <c r="B242" t="n">
-        <v>56575</v>
+        <v>79565</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25884,49 +25904,37 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>477611</v>
+        <v>478484</v>
       </c>
       <c r="R242" t="n">
-        <v>7033311</v>
+        <v>7034809</v>
       </c>
       <c r="S242" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -25950,12 +25958,12 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -25966,26 +25974,31 @@
       </c>
       <c r="AG242" t="b">
         <v>0</v>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>111901548</v>
+        <v>125652229</v>
       </c>
       <c r="B243" t="n">
-        <v>56430</v>
+        <v>79203</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25994,45 +26007,44 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>477476</v>
+        <v>478890</v>
       </c>
       <c r="R243" t="n">
-        <v>7033385</v>
+        <v>7034233</v>
       </c>
       <c r="S243" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -26056,17 +26068,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -26075,28 +26082,34 @@
       <c r="AE243" t="b">
         <v>0</v>
       </c>
+      <c r="AF243" t="inlineStr"/>
       <c r="AG243" t="b">
         <v>0</v>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>Grannaturskog vid bäckdråg</t>
+        </is>
       </c>
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>111901618</v>
+        <v>111901519</v>
       </c>
       <c r="B244" t="n">
-        <v>85197</v>
+        <v>86371</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -26109,21 +26122,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>249278</v>
+        <v>4412</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -26133,10 +26146,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>477471</v>
+        <v>477765</v>
       </c>
       <c r="R244" t="n">
-        <v>7033412</v>
+        <v>7033404</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -26195,7 +26208,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>111901549</v>
+        <v>111901546</v>
       </c>
       <c r="B245" t="n">
         <v>56430</v>
@@ -26239,10 +26252,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>477464</v>
+        <v>477668</v>
       </c>
       <c r="R245" t="n">
-        <v>7033364</v>
+        <v>7033374</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -26279,7 +26292,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -26306,7 +26319,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>111901544</v>
+        <v>111901547</v>
       </c>
       <c r="B246" t="n">
         <v>56430</v>
@@ -26350,10 +26363,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>477639</v>
+        <v>477524</v>
       </c>
       <c r="R246" t="n">
-        <v>7033515</v>
+        <v>7033330</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -26390,7 +26403,7 @@
       </c>
       <c r="AC246" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -26417,7 +26430,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>111901550</v>
+        <v>111901551</v>
       </c>
       <c r="B247" t="n">
         <v>56430</v>
@@ -26461,10 +26474,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>477473</v>
+        <v>477433</v>
       </c>
       <c r="R247" t="n">
-        <v>7033404</v>
+        <v>7033429</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -26501,7 +26514,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -26528,10 +26541,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>111901545</v>
+        <v>111901518</v>
       </c>
       <c r="B248" t="n">
-        <v>56430</v>
+        <v>86371</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26544,35 +26557,31 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>477667</v>
+        <v>477674</v>
       </c>
       <c r="R248" t="n">
         <v>7033500</v>
@@ -26608,11 +26617,6 @@
       <c r="AA248" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -26639,10 +26643,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>117085837</v>
+        <v>111901587</v>
       </c>
       <c r="B249" t="n">
-        <v>90463</v>
+        <v>56575</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -26655,37 +26659,49 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>477402</v>
+        <v>477611</v>
       </c>
       <c r="R249" t="n">
-        <v>7033066</v>
+        <v>7033311</v>
       </c>
       <c r="S249" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -26709,12 +26725,12 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -26729,22 +26745,22 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>117130130</v>
+        <v>111901548</v>
       </c>
       <c r="B250" t="n">
-        <v>91236</v>
+        <v>56430</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26753,44 +26769,45 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>717</v>
+        <v>100109</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
       <c r="N250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Stenbäcken, Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>477651</v>
+        <v>477476</v>
       </c>
       <c r="R250" t="n">
-        <v>7033403</v>
+        <v>7033385</v>
       </c>
       <c r="S250" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -26814,17 +26831,17 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>På levande asp. Trötta fruktkroppar.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26833,29 +26850,28 @@
       <c r="AE250" t="b">
         <v>0</v>
       </c>
-      <c r="AF250" t="inlineStr"/>
       <c r="AG250" t="b">
         <v>0</v>
       </c>
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>117792165</v>
+        <v>111901618</v>
       </c>
       <c r="B251" t="n">
-        <v>90503</v>
+        <v>85197</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26868,37 +26884,37 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1202</v>
+        <v>249278</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>477450</v>
+        <v>477471</v>
       </c>
       <c r="R251" t="n">
-        <v>7033406</v>
+        <v>7033412</v>
       </c>
       <c r="S251" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -26922,12 +26938,12 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26942,22 +26958,22 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>118701501</v>
+        <v>111901549</v>
       </c>
       <c r="B252" t="n">
-        <v>97856</v>
+        <v>56430</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26970,37 +26986,41 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>620</v>
+        <v>100109</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>477755</v>
+        <v>477464</v>
       </c>
       <c r="R252" t="n">
-        <v>7033301</v>
+        <v>7033364</v>
       </c>
       <c r="S252" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -27024,12 +27044,17 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -27044,22 +27069,22 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>118703040</v>
+        <v>111901544</v>
       </c>
       <c r="B253" t="n">
-        <v>91803</v>
+        <v>56430</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -27068,41 +27093,45 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>477689</v>
+        <v>477639</v>
       </c>
       <c r="R253" t="n">
-        <v>7033262</v>
+        <v>7033515</v>
       </c>
       <c r="S253" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -27126,12 +27155,17 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -27146,22 +27180,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>118861806</v>
+        <v>111901550</v>
       </c>
       <c r="B254" t="n">
-        <v>91776</v>
+        <v>56430</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -27174,37 +27208,41 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>1968</v>
+        <v>100109</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>477318</v>
+        <v>477473</v>
       </c>
       <c r="R254" t="n">
-        <v>7033069</v>
+        <v>7033404</v>
       </c>
       <c r="S254" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -27228,12 +27266,17 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27248,22 +27291,22 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>119048941</v>
+        <v>111901545</v>
       </c>
       <c r="B255" t="n">
-        <v>87388</v>
+        <v>56430</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -27276,37 +27319,41 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>477338</v>
+        <v>477667</v>
       </c>
       <c r="R255" t="n">
-        <v>7033068</v>
+        <v>7033500</v>
       </c>
       <c r="S255" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -27330,12 +27377,17 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -27350,22 +27402,22 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>119048382</v>
+        <v>117085837</v>
       </c>
       <c r="B256" t="n">
-        <v>91807</v>
+        <v>90463</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -27378,34 +27430,34 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1968</v>
+        <v>1202</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>477617</v>
+        <v>477402</v>
       </c>
       <c r="R256" t="n">
-        <v>7033532</v>
+        <v>7033066</v>
       </c>
       <c r="S256" t="n">
         <v>20</v>
@@ -27432,12 +27484,12 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27464,10 +27516,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>119221941</v>
+        <v>117130130</v>
       </c>
       <c r="B257" t="n">
-        <v>84007</v>
+        <v>91236</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -27476,41 +27528,44 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>5589</v>
+        <v>717</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>477845</v>
+        <v>477651</v>
       </c>
       <c r="R257" t="n">
-        <v>7033413</v>
+        <v>7033403</v>
       </c>
       <c r="S257" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -27534,12 +27589,17 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>På levande asp. Trötta fruktkroppar.</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -27548,6 +27608,7 @@
       <c r="AE257" t="b">
         <v>0</v>
       </c>
+      <c r="AF257" t="inlineStr"/>
       <c r="AG257" t="b">
         <v>0</v>
       </c>
@@ -27566,10 +27627,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>121241556</v>
+        <v>117792165</v>
       </c>
       <c r="B258" t="n">
-        <v>79198</v>
+        <v>90503</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27582,40 +27643,37 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Stenbäcken, Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>478098</v>
+        <v>477450</v>
       </c>
       <c r="R258" t="n">
-        <v>7033575</v>
+        <v>7033406</v>
       </c>
       <c r="S258" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -27639,12 +27697,12 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -27653,7 +27711,6 @@
       <c r="AE258" t="b">
         <v>0</v>
       </c>
-      <c r="AF258" t="inlineStr"/>
       <c r="AG258" t="b">
         <v>0</v>
       </c>
@@ -27672,10 +27729,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>117448064</v>
+        <v>118701501</v>
       </c>
       <c r="B259" t="n">
-        <v>90497</v>
+        <v>97856</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -27688,34 +27745,34 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>1108</v>
+        <v>620</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>477365</v>
+        <v>477755</v>
       </c>
       <c r="R259" t="n">
-        <v>7032988</v>
+        <v>7033301</v>
       </c>
       <c r="S259" t="n">
         <v>20</v>
@@ -27742,12 +27799,12 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -27774,10 +27831,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>117448244</v>
+        <v>118703040</v>
       </c>
       <c r="B260" t="n">
-        <v>90519</v>
+        <v>91803</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27786,38 +27843,38 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5432</v>
+        <v>4366</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>477439</v>
+        <v>477689</v>
       </c>
       <c r="R260" t="n">
-        <v>7033047</v>
+        <v>7033262</v>
       </c>
       <c r="S260" t="n">
         <v>20</v>
@@ -27844,12 +27901,12 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -27876,10 +27933,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>118414846</v>
+        <v>118861806</v>
       </c>
       <c r="B261" t="n">
-        <v>91800</v>
+        <v>91776</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27888,41 +27945,38 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>4366</v>
+        <v>1968</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
           <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>477357</v>
+        <v>477318</v>
       </c>
       <c r="R261" t="n">
-        <v>7033041</v>
+        <v>7033069</v>
       </c>
       <c r="S261" t="n">
         <v>20</v>
@@ -27949,17 +28003,12 @@
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -27968,7 +28017,6 @@
       <c r="AE261" t="b">
         <v>0</v>
       </c>
-      <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="b">
         <v>0</v>
       </c>
@@ -27987,10 +28035,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>118414787</v>
+        <v>119048941</v>
       </c>
       <c r="B262" t="n">
-        <v>90509</v>
+        <v>87388</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -28003,21 +28051,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1108</v>
+        <v>4412</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -28027,10 +28075,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>477367</v>
+        <v>477338</v>
       </c>
       <c r="R262" t="n">
-        <v>7032995</v>
+        <v>7033068</v>
       </c>
       <c r="S262" t="n">
         <v>20</v>
@@ -28057,12 +28105,12 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -28089,10 +28137,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>118702006</v>
+        <v>119048382</v>
       </c>
       <c r="B263" t="n">
-        <v>91776</v>
+        <v>91807</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -28125,14 +28173,14 @@
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>477332</v>
+        <v>477617</v>
       </c>
       <c r="R263" t="n">
-        <v>7033029</v>
+        <v>7033532</v>
       </c>
       <c r="S263" t="n">
         <v>20</v>
@@ -28159,12 +28207,12 @@
       </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -28191,10 +28239,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>119477054</v>
+        <v>119221941</v>
       </c>
       <c r="B264" t="n">
-        <v>91883</v>
+        <v>84007</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -28207,34 +28255,34 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>5448</v>
+        <v>5589</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Klingvågen, Klingvågen, Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>477342</v>
+        <v>477845</v>
       </c>
       <c r="R264" t="n">
-        <v>7033020</v>
+        <v>7033413</v>
       </c>
       <c r="S264" t="n">
         <v>20</v>
@@ -28261,12 +28309,12 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -28290,6 +28338,733 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>121241556</v>
+      </c>
+      <c r="B265" t="n">
+        <v>79198</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Stenbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>478098</v>
+      </c>
+      <c r="R265" t="n">
+        <v>7033575</v>
+      </c>
+      <c r="S265" t="n">
+        <v>10</v>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="AD265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF265" t="inlineStr"/>
+      <c r="AG265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT265" t="inlineStr"/>
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX265" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>117448064</v>
+      </c>
+      <c r="B266" t="n">
+        <v>90497</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr"/>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Klingvågen (Klingvågen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>477365</v>
+      </c>
+      <c r="R266" t="n">
+        <v>7032988</v>
+      </c>
+      <c r="S266" t="n">
+        <v>20</v>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AD266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT266" t="inlineStr"/>
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX266" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>117448244</v>
+      </c>
+      <c r="B267" t="n">
+        <v>90519</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr"/>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Klingvågen (Klingvågen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>477439</v>
+      </c>
+      <c r="R267" t="n">
+        <v>7033047</v>
+      </c>
+      <c r="S267" t="n">
+        <v>20</v>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AD267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT267" t="inlineStr"/>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>118414846</v>
+      </c>
+      <c r="B268" t="n">
+        <v>91800</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>Klingvågen (Klingvågen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>477357</v>
+      </c>
+      <c r="R268" t="n">
+        <v>7033041</v>
+      </c>
+      <c r="S268" t="n">
+        <v>20</v>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
+        </is>
+      </c>
+      <c r="AD268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF268" t="inlineStr"/>
+      <c r="AG268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT268" t="inlineStr"/>
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX268" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>118414787</v>
+      </c>
+      <c r="B269" t="n">
+        <v>90509</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr"/>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>Klingvågen (Klingvågen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>477367</v>
+      </c>
+      <c r="R269" t="n">
+        <v>7032995</v>
+      </c>
+      <c r="S269" t="n">
+        <v>20</v>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AD269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT269" t="inlineStr"/>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>118702006</v>
+      </c>
+      <c r="B270" t="n">
+        <v>91776</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Bankera violascens</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr"/>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>Klingvågen (Klingvågen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>477332</v>
+      </c>
+      <c r="R270" t="n">
+        <v>7033029</v>
+      </c>
+      <c r="S270" t="n">
+        <v>20</v>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT270" t="inlineStr"/>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>119477054</v>
+      </c>
+      <c r="B271" t="n">
+        <v>91883</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr"/>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Klingvågen, Klingvågen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>477342</v>
+      </c>
+      <c r="R271" t="n">
+        <v>7033020</v>
+      </c>
+      <c r="S271" t="n">
+        <v>20</v>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AD271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT271" t="inlineStr"/>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -25213,12 +25213,7 @@
         <v>125536112</v>
       </c>
       <c r="B236" t="n">
-        <v>91219</v>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91273</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -25331,15 +25326,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>125652112</v>
+        <v>125654533</v>
       </c>
       <c r="B237" t="n">
-        <v>77889</v>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25347,37 +25337,34 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>314</v>
+        <v>6453</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>478893</v>
+        <v>478484</v>
       </c>
       <c r="R237" t="n">
-        <v>7034299</v>
+        <v>7034809</v>
       </c>
       <c r="S237" t="n">
         <v>15</v>
@@ -25418,13 +25405,12 @@
       <c r="AE237" t="b">
         <v>0</v>
       </c>
-      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>Grannaturskog vid bäckdråg</t>
+          <t>Grannaturskog</t>
         </is>
       </c>
       <c r="AT237" t="inlineStr"/>
@@ -25442,50 +25428,48 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>125653096</v>
+        <v>125652112</v>
       </c>
       <c r="B238" t="n">
-        <v>98175</v>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77931</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>504</v>
+        <v>314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>478457</v>
+        <v>478893</v>
       </c>
       <c r="R238" t="n">
-        <v>7034140</v>
+        <v>7034299</v>
       </c>
       <c r="S238" t="n">
         <v>15</v>
@@ -25526,12 +25510,13 @@
       <c r="AE238" t="b">
         <v>0</v>
       </c>
+      <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr"/>
@@ -25552,12 +25537,7 @@
         <v>125654473</v>
       </c>
       <c r="B239" t="n">
-        <v>83036</v>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83078</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25670,50 +25650,48 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>125652823</v>
+        <v>125652111</v>
       </c>
       <c r="B240" t="n">
-        <v>74836</v>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75066</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6428</v>
+        <v>6440</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>478483</v>
+        <v>478893</v>
       </c>
       <c r="R240" t="n">
-        <v>7034170</v>
+        <v>7034299</v>
       </c>
       <c r="S240" t="n">
         <v>15</v>
@@ -25754,12 +25732,13 @@
       <c r="AE240" t="b">
         <v>0</v>
       </c>
+      <c r="AF240" t="inlineStr"/>
       <c r="AG240" t="b">
         <v>0</v>
       </c>
       <c r="AI240" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT240" t="inlineStr"/>
@@ -25777,53 +25756,45 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>125652111</v>
+        <v>125652823</v>
       </c>
       <c r="B241" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>74877</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>478893</v>
+        <v>478483</v>
       </c>
       <c r="R241" t="n">
-        <v>7034299</v>
+        <v>7034170</v>
       </c>
       <c r="S241" t="n">
         <v>15</v>
@@ -25864,13 +25835,12 @@
       <c r="AE241" t="b">
         <v>0</v>
       </c>
-      <c r="AF241" t="inlineStr"/>
       <c r="AG241" t="b">
         <v>0</v>
       </c>
       <c r="AI241" t="inlineStr">
         <is>
-          <t>Grannaturskog vid bäckdråg</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT241" t="inlineStr"/>
@@ -25888,37 +25858,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>125654533</v>
+        <v>125653096</v>
       </c>
       <c r="B242" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98230</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6453</v>
+        <v>504</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25928,10 +25893,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>478484</v>
+        <v>478457</v>
       </c>
       <c r="R242" t="n">
-        <v>7034809</v>
+        <v>7034140</v>
       </c>
       <c r="S242" t="n">
         <v>15</v>
@@ -25977,7 +25942,7 @@
       </c>
       <c r="AI242" t="inlineStr">
         <is>
-          <t>Grannaturskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT242" t="inlineStr"/>
@@ -25998,12 +25963,7 @@
         <v>125652229</v>
       </c>
       <c r="B243" t="n">
-        <v>79203</v>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79223</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -25213,7 +25213,7 @@
         <v>125536112</v>
       </c>
       <c r="B236" t="n">
-        <v>91273</v>
+        <v>91280</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>125653096</v>
       </c>
       <c r="B242" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -25213,7 +25213,7 @@
         <v>125536112</v>
       </c>
       <c r="B236" t="n">
-        <v>91280</v>
+        <v>91281</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>125654533</v>
       </c>
       <c r="B237" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>125652112</v>
       </c>
       <c r="B238" t="n">
-        <v>77931</v>
+        <v>77932</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>125654473</v>
       </c>
       <c r="B239" t="n">
-        <v>83078</v>
+        <v>83079</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>125652111</v>
       </c>
       <c r="B240" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>125652823</v>
       </c>
       <c r="B241" t="n">
-        <v>74877</v>
+        <v>74878</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25858,10 +25858,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>125653096</v>
+        <v>125652229</v>
       </c>
       <c r="B242" t="n">
-        <v>98237</v>
+        <v>79224</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25869,34 +25869,37 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>504</v>
+        <v>6459</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>478457</v>
+        <v>478890</v>
       </c>
       <c r="R242" t="n">
-        <v>7034140</v>
+        <v>7034233</v>
       </c>
       <c r="S242" t="n">
         <v>15</v>
@@ -25937,12 +25940,13 @@
       <c r="AE242" t="b">
         <v>0</v>
       </c>
+      <c r="AF242" t="inlineStr"/>
       <c r="AG242" t="b">
         <v>0</v>
       </c>
       <c r="AI242" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT242" t="inlineStr"/>
@@ -25960,10 +25964,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>125652229</v>
+        <v>125653096</v>
       </c>
       <c r="B243" t="n">
-        <v>79223</v>
+        <v>98240</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25971,37 +25975,34 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6459</v>
+        <v>504</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>478890</v>
+        <v>478457</v>
       </c>
       <c r="R243" t="n">
-        <v>7034233</v>
+        <v>7034140</v>
       </c>
       <c r="S243" t="n">
         <v>15</v>
@@ -26042,13 +26043,12 @@
       <c r="AE243" t="b">
         <v>0</v>
       </c>
-      <c r="AF243" t="inlineStr"/>
       <c r="AG243" t="b">
         <v>0</v>
       </c>
       <c r="AI243" t="inlineStr">
         <is>
-          <t>Grannaturskog vid bäckdråg</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT243" t="inlineStr"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -25213,7 +25213,7 @@
         <v>125536112</v>
       </c>
       <c r="B236" t="n">
-        <v>91281</v>
+        <v>91285</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>125654533</v>
       </c>
       <c r="B237" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>125652112</v>
       </c>
       <c r="B238" t="n">
-        <v>77932</v>
+        <v>77936</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>125654473</v>
       </c>
       <c r="B239" t="n">
-        <v>83079</v>
+        <v>83083</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>125652229</v>
       </c>
       <c r="B242" t="n">
-        <v>79224</v>
+        <v>79228</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>125653096</v>
       </c>
       <c r="B243" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -25967,7 +25967,7 @@
         <v>125653096</v>
       </c>
       <c r="B243" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -25213,7 +25213,7 @@
         <v>125536112</v>
       </c>
       <c r="B236" t="n">
-        <v>91285</v>
+        <v>91287</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>125654533</v>
       </c>
       <c r="B237" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>125652112</v>
       </c>
       <c r="B238" t="n">
-        <v>77936</v>
+        <v>77937</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>125654473</v>
       </c>
       <c r="B239" t="n">
-        <v>83083</v>
+        <v>83084</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>125652111</v>
       </c>
       <c r="B240" t="n">
-        <v>75067</v>
+        <v>75068</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>125652823</v>
       </c>
       <c r="B241" t="n">
-        <v>74878</v>
+        <v>74879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25858,10 +25858,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>125652229</v>
+        <v>125653096</v>
       </c>
       <c r="B242" t="n">
-        <v>79228</v>
+        <v>98247</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25869,37 +25869,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6459</v>
+        <v>504</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>478890</v>
+        <v>478457</v>
       </c>
       <c r="R242" t="n">
-        <v>7034233</v>
+        <v>7034140</v>
       </c>
       <c r="S242" t="n">
         <v>15</v>
@@ -25940,13 +25937,12 @@
       <c r="AE242" t="b">
         <v>0</v>
       </c>
-      <c r="AF242" t="inlineStr"/>
       <c r="AG242" t="b">
         <v>0</v>
       </c>
       <c r="AI242" t="inlineStr">
         <is>
-          <t>Grannaturskog vid bäckdråg</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT242" t="inlineStr"/>
@@ -25964,10 +25960,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>125653096</v>
+        <v>125652229</v>
       </c>
       <c r="B243" t="n">
-        <v>98245</v>
+        <v>79229</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25975,34 +25971,37 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>504</v>
+        <v>6459</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>478457</v>
+        <v>478890</v>
       </c>
       <c r="R243" t="n">
-        <v>7034140</v>
+        <v>7034233</v>
       </c>
       <c r="S243" t="n">
         <v>15</v>
@@ -26043,12 +26042,13 @@
       <c r="AE243" t="b">
         <v>0</v>
       </c>
+      <c r="AF243" t="inlineStr"/>
       <c r="AG243" t="b">
         <v>0</v>
       </c>
       <c r="AI243" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT243" t="inlineStr"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -25213,7 +25213,7 @@
         <v>125536112</v>
       </c>
       <c r="B236" t="n">
-        <v>91287</v>
+        <v>91289</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -25428,32 +25428,32 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>125652112</v>
+        <v>125654473</v>
       </c>
       <c r="B238" t="n">
-        <v>77937</v>
+        <v>83084</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>314</v>
+        <v>750</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Klotsporig murkla</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Gyromitra sphaerospora</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Peck) Sacc.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -25466,10 +25466,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>478893</v>
+        <v>478460</v>
       </c>
       <c r="R238" t="n">
-        <v>7034299</v>
+        <v>7034711</v>
       </c>
       <c r="S238" t="n">
         <v>15</v>
@@ -25516,7 +25516,17 @@
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>Grannaturskog vid bäckdråg</t>
+          <t>Grannaturskog på kalkrik berggrund</t>
+        </is>
+      </c>
+      <c r="AL238" t="inlineStr">
+        <is>
+          <t>På förnalager ovanpå en rötbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO238" t="inlineStr">
+        <is>
+          <t>På förnalager ovanpå en rötbruten granlåga</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr"/>
@@ -25534,32 +25544,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>125654473</v>
+        <v>125652112</v>
       </c>
       <c r="B239" t="n">
-        <v>83084</v>
+        <v>77937</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>750</v>
+        <v>314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Klotsporig murkla</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Gyromitra sphaerospora</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Peck) Sacc.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -25572,10 +25582,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>478460</v>
+        <v>478893</v>
       </c>
       <c r="R239" t="n">
-        <v>7034711</v>
+        <v>7034299</v>
       </c>
       <c r="S239" t="n">
         <v>15</v>
@@ -25622,17 +25632,7 @@
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>Grannaturskog på kalkrik berggrund</t>
-        </is>
-      </c>
-      <c r="AL239" t="inlineStr">
-        <is>
-          <t>På förnalager ovanpå en rötbruten granlåga</t>
-        </is>
-      </c>
-      <c r="AO239" t="inlineStr">
-        <is>
-          <t>På förnalager ovanpå en rötbruten granlåga</t>
+          <t>Grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT239" t="inlineStr"/>
@@ -25858,10 +25858,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>125653096</v>
+        <v>125652229</v>
       </c>
       <c r="B242" t="n">
-        <v>98247</v>
+        <v>79229</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25869,34 +25869,37 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>504</v>
+        <v>6459</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>478457</v>
+        <v>478890</v>
       </c>
       <c r="R242" t="n">
-        <v>7034140</v>
+        <v>7034233</v>
       </c>
       <c r="S242" t="n">
         <v>15</v>
@@ -25937,12 +25940,13 @@
       <c r="AE242" t="b">
         <v>0</v>
       </c>
+      <c r="AF242" t="inlineStr"/>
       <c r="AG242" t="b">
         <v>0</v>
       </c>
       <c r="AI242" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT242" t="inlineStr"/>
@@ -25960,10 +25964,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>125652229</v>
+        <v>125653096</v>
       </c>
       <c r="B243" t="n">
-        <v>79229</v>
+        <v>98249</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25971,37 +25975,34 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6459</v>
+        <v>504</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>478890</v>
+        <v>478457</v>
       </c>
       <c r="R243" t="n">
-        <v>7034233</v>
+        <v>7034140</v>
       </c>
       <c r="S243" t="n">
         <v>15</v>
@@ -26042,13 +26043,12 @@
       <c r="AE243" t="b">
         <v>0</v>
       </c>
-      <c r="AF243" t="inlineStr"/>
       <c r="AG243" t="b">
         <v>0</v>
       </c>
       <c r="AI243" t="inlineStr">
         <is>
-          <t>Grannaturskog vid bäckdråg</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT243" t="inlineStr"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -25428,32 +25428,32 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>125654473</v>
+        <v>125652112</v>
       </c>
       <c r="B238" t="n">
-        <v>83084</v>
+        <v>77937</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>750</v>
+        <v>314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Klotsporig murkla</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Gyromitra sphaerospora</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Peck) Sacc.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -25466,10 +25466,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>478460</v>
+        <v>478893</v>
       </c>
       <c r="R238" t="n">
-        <v>7034711</v>
+        <v>7034299</v>
       </c>
       <c r="S238" t="n">
         <v>15</v>
@@ -25516,17 +25516,7 @@
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>Grannaturskog på kalkrik berggrund</t>
-        </is>
-      </c>
-      <c r="AL238" t="inlineStr">
-        <is>
-          <t>På förnalager ovanpå en rötbruten granlåga</t>
-        </is>
-      </c>
-      <c r="AO238" t="inlineStr">
-        <is>
-          <t>På förnalager ovanpå en rötbruten granlåga</t>
+          <t>Grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr"/>
@@ -25544,32 +25534,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>125652112</v>
+        <v>125654473</v>
       </c>
       <c r="B239" t="n">
-        <v>77937</v>
+        <v>83084</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>314</v>
+        <v>750</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Klotsporig murkla</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Gyromitra sphaerospora</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Peck) Sacc.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -25582,10 +25572,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>478893</v>
+        <v>478460</v>
       </c>
       <c r="R239" t="n">
-        <v>7034299</v>
+        <v>7034711</v>
       </c>
       <c r="S239" t="n">
         <v>15</v>
@@ -25632,7 +25622,17 @@
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>Grannaturskog vid bäckdråg</t>
+          <t>Grannaturskog på kalkrik berggrund</t>
+        </is>
+      </c>
+      <c r="AL239" t="inlineStr">
+        <is>
+          <t>På förnalager ovanpå en rötbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>På förnalager ovanpå en rötbruten granlåga</t>
         </is>
       </c>
       <c r="AT239" t="inlineStr"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -25858,10 +25858,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>125652229</v>
+        <v>125653096</v>
       </c>
       <c r="B242" t="n">
-        <v>79229</v>
+        <v>98251</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25869,37 +25869,34 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6459</v>
+        <v>504</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>478890</v>
+        <v>478457</v>
       </c>
       <c r="R242" t="n">
-        <v>7034233</v>
+        <v>7034140</v>
       </c>
       <c r="S242" t="n">
         <v>15</v>
@@ -25940,13 +25937,12 @@
       <c r="AE242" t="b">
         <v>0</v>
       </c>
-      <c r="AF242" t="inlineStr"/>
       <c r="AG242" t="b">
         <v>0</v>
       </c>
       <c r="AI242" t="inlineStr">
         <is>
-          <t>Grannaturskog vid bäckdråg</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT242" t="inlineStr"/>
@@ -25964,10 +25960,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>125653096</v>
+        <v>125652229</v>
       </c>
       <c r="B243" t="n">
-        <v>98249</v>
+        <v>79229</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25975,34 +25971,37 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>504</v>
+        <v>6459</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>478457</v>
+        <v>478890</v>
       </c>
       <c r="R243" t="n">
-        <v>7034140</v>
+        <v>7034233</v>
       </c>
       <c r="S243" t="n">
         <v>15</v>
@@ -26043,12 +26042,13 @@
       <c r="AE243" t="b">
         <v>0</v>
       </c>
+      <c r="AF243" t="inlineStr"/>
       <c r="AG243" t="b">
         <v>0</v>
       </c>
       <c r="AI243" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT243" t="inlineStr"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -25329,7 +25329,7 @@
         <v>125654533</v>
       </c>
       <c r="B237" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -25428,32 +25428,32 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>125652112</v>
+        <v>125654473</v>
       </c>
       <c r="B238" t="n">
-        <v>77937</v>
+        <v>83088</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>314</v>
+        <v>750</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Klotsporig murkla</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Gyromitra sphaerospora</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Peck) Sacc.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -25466,10 +25466,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>478893</v>
+        <v>478460</v>
       </c>
       <c r="R238" t="n">
-        <v>7034299</v>
+        <v>7034711</v>
       </c>
       <c r="S238" t="n">
         <v>15</v>
@@ -25516,7 +25516,17 @@
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>Grannaturskog vid bäckdråg</t>
+          <t>Grannaturskog på kalkrik berggrund</t>
+        </is>
+      </c>
+      <c r="AL238" t="inlineStr">
+        <is>
+          <t>På förnalager ovanpå en rötbruten granlåga</t>
+        </is>
+      </c>
+      <c r="AO238" t="inlineStr">
+        <is>
+          <t>På förnalager ovanpå en rötbruten granlåga</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr"/>
@@ -25534,32 +25544,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>125654473</v>
+        <v>125652112</v>
       </c>
       <c r="B239" t="n">
-        <v>83084</v>
+        <v>77941</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>750</v>
+        <v>314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Klotsporig murkla</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Gyromitra sphaerospora</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Peck) Sacc.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -25572,10 +25582,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>478460</v>
+        <v>478893</v>
       </c>
       <c r="R239" t="n">
-        <v>7034711</v>
+        <v>7034299</v>
       </c>
       <c r="S239" t="n">
         <v>15</v>
@@ -25622,17 +25632,7 @@
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>Grannaturskog på kalkrik berggrund</t>
-        </is>
-      </c>
-      <c r="AL239" t="inlineStr">
-        <is>
-          <t>På förnalager ovanpå en rötbruten granlåga</t>
-        </is>
-      </c>
-      <c r="AO239" t="inlineStr">
-        <is>
-          <t>På förnalager ovanpå en rötbruten granlåga</t>
+          <t>Grannaturskog vid bäckdråg</t>
         </is>
       </c>
       <c r="AT239" t="inlineStr"/>
@@ -25653,7 +25653,7 @@
         <v>125652111</v>
       </c>
       <c r="B240" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>125652823</v>
       </c>
       <c r="B241" t="n">
-        <v>74879</v>
+        <v>74883</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>125653096</v>
       </c>
       <c r="B242" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>125652229</v>
       </c>
       <c r="B243" t="n">
-        <v>79229</v>
+        <v>79233</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26069,7 +26069,7 @@
         <v>127123931</v>
       </c>
       <c r="B244" t="n">
-        <v>79954</v>
+        <v>79985</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26172,48 +26172,45 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127126133</v>
+        <v>127127145</v>
       </c>
       <c r="B245" t="n">
-        <v>91699</v>
+        <v>96689</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478610</v>
+        <v>478533</v>
       </c>
       <c r="R245" t="n">
-        <v>7034420</v>
+        <v>7034189</v>
       </c>
       <c r="S245" t="n">
         <v>15</v>
@@ -26254,13 +26251,12 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
-      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>Bördigt och örtrikt bäckdråg</t>
+          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
         </is>
       </c>
       <c r="AT245" t="inlineStr"/>
@@ -26278,45 +26274,48 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127127145</v>
+        <v>127126133</v>
       </c>
       <c r="B246" t="n">
-        <v>96614</v>
+        <v>91773</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478533</v>
+        <v>478610</v>
       </c>
       <c r="R246" t="n">
-        <v>7034189</v>
+        <v>7034420</v>
       </c>
       <c r="S246" t="n">
         <v>15</v>
@@ -26357,12 +26356,13 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
+      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
+          <t>Bördigt och örtrikt bäckdråg</t>
         </is>
       </c>
       <c r="AT246" t="inlineStr"/>
@@ -26383,7 +26383,7 @@
         <v>127122571</v>
       </c>
       <c r="B247" t="n">
-        <v>92534</v>
+        <v>92608</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>127122401</v>
       </c>
       <c r="B248" t="n">
-        <v>90782</v>
+        <v>90856</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>127122277</v>
       </c>
       <c r="B249" t="n">
-        <v>92527</v>
+        <v>92601</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26069,7 +26069,7 @@
         <v>127123931</v>
       </c>
       <c r="B244" t="n">
-        <v>79985</v>
+        <v>79988</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>127127145</v>
       </c>
       <c r="B245" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>127126133</v>
       </c>
       <c r="B246" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>127122571</v>
       </c>
       <c r="B247" t="n">
-        <v>92608</v>
+        <v>92614</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>127122401</v>
       </c>
       <c r="B248" t="n">
-        <v>90856</v>
+        <v>90862</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>127122277</v>
       </c>
       <c r="B249" t="n">
-        <v>92601</v>
+        <v>92607</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26172,45 +26172,48 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127127145</v>
+        <v>127126133</v>
       </c>
       <c r="B245" t="n">
-        <v>96695</v>
+        <v>91779</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478533</v>
+        <v>478610</v>
       </c>
       <c r="R245" t="n">
-        <v>7034189</v>
+        <v>7034420</v>
       </c>
       <c r="S245" t="n">
         <v>15</v>
@@ -26251,12 +26254,13 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
+          <t>Bördigt och örtrikt bäckdråg</t>
         </is>
       </c>
       <c r="AT245" t="inlineStr"/>
@@ -26274,48 +26278,45 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127126133</v>
+        <v>127127145</v>
       </c>
       <c r="B246" t="n">
-        <v>91779</v>
+        <v>96695</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478610</v>
+        <v>478533</v>
       </c>
       <c r="R246" t="n">
-        <v>7034420</v>
+        <v>7034189</v>
       </c>
       <c r="S246" t="n">
         <v>15</v>
@@ -26356,13 +26357,12 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>Bördigt och örtrikt bäckdråg</t>
+          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
         </is>
       </c>
       <c r="AT246" t="inlineStr"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26172,48 +26172,45 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127126133</v>
+        <v>127127145</v>
       </c>
       <c r="B245" t="n">
-        <v>91779</v>
+        <v>96696</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478610</v>
+        <v>478533</v>
       </c>
       <c r="R245" t="n">
-        <v>7034420</v>
+        <v>7034189</v>
       </c>
       <c r="S245" t="n">
         <v>15</v>
@@ -26254,13 +26251,12 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
-      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>Bördigt och örtrikt bäckdråg</t>
+          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
         </is>
       </c>
       <c r="AT245" t="inlineStr"/>
@@ -26278,45 +26274,48 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127127145</v>
+        <v>127126133</v>
       </c>
       <c r="B246" t="n">
-        <v>96695</v>
+        <v>91780</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478533</v>
+        <v>478610</v>
       </c>
       <c r="R246" t="n">
-        <v>7034189</v>
+        <v>7034420</v>
       </c>
       <c r="S246" t="n">
         <v>15</v>
@@ -26357,12 +26356,13 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
+      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
+          <t>Bördigt och örtrikt bäckdråg</t>
         </is>
       </c>
       <c r="AT246" t="inlineStr"/>
@@ -26383,7 +26383,7 @@
         <v>127122571</v>
       </c>
       <c r="B247" t="n">
-        <v>92614</v>
+        <v>92615</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>127122401</v>
       </c>
       <c r="B248" t="n">
-        <v>90862</v>
+        <v>90863</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>127122277</v>
       </c>
       <c r="B249" t="n">
-        <v>92607</v>
+        <v>92608</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26172,45 +26172,48 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127127145</v>
+        <v>127126133</v>
       </c>
       <c r="B245" t="n">
-        <v>96696</v>
+        <v>91780</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478533</v>
+        <v>478610</v>
       </c>
       <c r="R245" t="n">
-        <v>7034189</v>
+        <v>7034420</v>
       </c>
       <c r="S245" t="n">
         <v>15</v>
@@ -26251,12 +26254,13 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
+          <t>Bördigt och örtrikt bäckdråg</t>
         </is>
       </c>
       <c r="AT245" t="inlineStr"/>
@@ -26274,48 +26278,45 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127126133</v>
+        <v>127127145</v>
       </c>
       <c r="B246" t="n">
-        <v>91780</v>
+        <v>96696</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478610</v>
+        <v>478533</v>
       </c>
       <c r="R246" t="n">
-        <v>7034420</v>
+        <v>7034189</v>
       </c>
       <c r="S246" t="n">
         <v>15</v>
@@ -26356,13 +26357,12 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>Bördigt och örtrikt bäckdråg</t>
+          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
         </is>
       </c>
       <c r="AT246" t="inlineStr"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26069,7 +26069,7 @@
         <v>127123931</v>
       </c>
       <c r="B244" t="n">
-        <v>79988</v>
+        <v>79992</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>127126133</v>
       </c>
       <c r="B245" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>127127145</v>
       </c>
       <c r="B246" t="n">
-        <v>96696</v>
+        <v>96700</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>127122571</v>
       </c>
       <c r="B247" t="n">
-        <v>92615</v>
+        <v>92619</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>127122401</v>
       </c>
       <c r="B248" t="n">
-        <v>90863</v>
+        <v>90867</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>127122277</v>
       </c>
       <c r="B249" t="n">
-        <v>92608</v>
+        <v>92612</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26172,48 +26172,45 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127126133</v>
+        <v>127127145</v>
       </c>
       <c r="B245" t="n">
-        <v>91784</v>
+        <v>96700</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478610</v>
+        <v>478533</v>
       </c>
       <c r="R245" t="n">
-        <v>7034420</v>
+        <v>7034189</v>
       </c>
       <c r="S245" t="n">
         <v>15</v>
@@ -26254,13 +26251,12 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
-      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>Bördigt och örtrikt bäckdråg</t>
+          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
         </is>
       </c>
       <c r="AT245" t="inlineStr"/>
@@ -26278,45 +26274,48 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127127145</v>
+        <v>127126133</v>
       </c>
       <c r="B246" t="n">
-        <v>96700</v>
+        <v>91784</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478533</v>
+        <v>478610</v>
       </c>
       <c r="R246" t="n">
-        <v>7034189</v>
+        <v>7034420</v>
       </c>
       <c r="S246" t="n">
         <v>15</v>
@@ -26357,12 +26356,13 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
+      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
+          <t>Bördigt och örtrikt bäckdråg</t>
         </is>
       </c>
       <c r="AT246" t="inlineStr"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26172,45 +26172,48 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127127145</v>
+        <v>127126133</v>
       </c>
       <c r="B245" t="n">
-        <v>96700</v>
+        <v>91784</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478533</v>
+        <v>478610</v>
       </c>
       <c r="R245" t="n">
-        <v>7034189</v>
+        <v>7034420</v>
       </c>
       <c r="S245" t="n">
         <v>15</v>
@@ -26251,12 +26254,13 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
+          <t>Bördigt och örtrikt bäckdråg</t>
         </is>
       </c>
       <c r="AT245" t="inlineStr"/>
@@ -26274,48 +26278,45 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127126133</v>
+        <v>127127145</v>
       </c>
       <c r="B246" t="n">
-        <v>91784</v>
+        <v>96700</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478610</v>
+        <v>478533</v>
       </c>
       <c r="R246" t="n">
-        <v>7034420</v>
+        <v>7034189</v>
       </c>
       <c r="S246" t="n">
         <v>15</v>
@@ -26356,13 +26357,12 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>Bördigt och örtrikt bäckdråg</t>
+          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
         </is>
       </c>
       <c r="AT246" t="inlineStr"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26069,7 +26069,7 @@
         <v>127123931</v>
       </c>
       <c r="B244" t="n">
-        <v>79992</v>
+        <v>79994</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26172,45 +26172,48 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127127145</v>
+        <v>127126133</v>
       </c>
       <c r="B245" t="n">
-        <v>96700</v>
+        <v>91786</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478533</v>
+        <v>478610</v>
       </c>
       <c r="R245" t="n">
-        <v>7034189</v>
+        <v>7034420</v>
       </c>
       <c r="S245" t="n">
         <v>15</v>
@@ -26251,12 +26254,13 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
+          <t>Bördigt och örtrikt bäckdråg</t>
         </is>
       </c>
       <c r="AT245" t="inlineStr"/>
@@ -26274,48 +26278,45 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127126133</v>
+        <v>127127145</v>
       </c>
       <c r="B246" t="n">
-        <v>91784</v>
+        <v>96702</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478610</v>
+        <v>478533</v>
       </c>
       <c r="R246" t="n">
-        <v>7034420</v>
+        <v>7034189</v>
       </c>
       <c r="S246" t="n">
         <v>15</v>
@@ -26356,13 +26357,12 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>Bördigt och örtrikt bäckdråg</t>
+          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
         </is>
       </c>
       <c r="AT246" t="inlineStr"/>
@@ -26383,7 +26383,7 @@
         <v>127122571</v>
       </c>
       <c r="B247" t="n">
-        <v>92619</v>
+        <v>92621</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>127122401</v>
       </c>
       <c r="B248" t="n">
-        <v>90867</v>
+        <v>90869</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>127122277</v>
       </c>
       <c r="B249" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26172,48 +26172,45 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127126133</v>
+        <v>127127145</v>
       </c>
       <c r="B245" t="n">
-        <v>91786</v>
+        <v>96702</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478610</v>
+        <v>478533</v>
       </c>
       <c r="R245" t="n">
-        <v>7034420</v>
+        <v>7034189</v>
       </c>
       <c r="S245" t="n">
         <v>15</v>
@@ -26254,13 +26251,12 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
-      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>Bördigt och örtrikt bäckdråg</t>
+          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
         </is>
       </c>
       <c r="AT245" t="inlineStr"/>
@@ -26278,45 +26274,48 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127127145</v>
+        <v>127126133</v>
       </c>
       <c r="B246" t="n">
-        <v>96702</v>
+        <v>91786</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478533</v>
+        <v>478610</v>
       </c>
       <c r="R246" t="n">
-        <v>7034189</v>
+        <v>7034420</v>
       </c>
       <c r="S246" t="n">
         <v>15</v>
@@ -26357,12 +26356,13 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
+      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
+          <t>Bördigt och örtrikt bäckdråg</t>
         </is>
       </c>
       <c r="AT246" t="inlineStr"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26172,45 +26172,48 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127127145</v>
+        <v>127126133</v>
       </c>
       <c r="B245" t="n">
-        <v>96702</v>
+        <v>91786</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478533</v>
+        <v>478610</v>
       </c>
       <c r="R245" t="n">
-        <v>7034189</v>
+        <v>7034420</v>
       </c>
       <c r="S245" t="n">
         <v>15</v>
@@ -26251,12 +26254,13 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
+          <t>Bördigt och örtrikt bäckdråg</t>
         </is>
       </c>
       <c r="AT245" t="inlineStr"/>
@@ -26274,48 +26278,45 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127126133</v>
+        <v>127127145</v>
       </c>
       <c r="B246" t="n">
-        <v>91786</v>
+        <v>96702</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478610</v>
+        <v>478533</v>
       </c>
       <c r="R246" t="n">
-        <v>7034420</v>
+        <v>7034189</v>
       </c>
       <c r="S246" t="n">
         <v>15</v>
@@ -26356,13 +26357,12 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>Bördigt och örtrikt bäckdråg</t>
+          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
         </is>
       </c>
       <c r="AT246" t="inlineStr"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26175,7 +26175,7 @@
         <v>127126133</v>
       </c>
       <c r="B245" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>127127145</v>
       </c>
       <c r="B246" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>127122571</v>
       </c>
       <c r="B247" t="n">
-        <v>92621</v>
+        <v>92627</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>127122401</v>
       </c>
       <c r="B248" t="n">
-        <v>90869</v>
+        <v>90875</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>127122277</v>
       </c>
       <c r="B249" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26069,7 +26069,7 @@
         <v>127123931</v>
       </c>
       <c r="B244" t="n">
-        <v>79994</v>
+        <v>79997</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26172,48 +26172,45 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127126133</v>
+        <v>127127145</v>
       </c>
       <c r="B245" t="n">
-        <v>91792</v>
+        <v>96711</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478610</v>
+        <v>478533</v>
       </c>
       <c r="R245" t="n">
-        <v>7034420</v>
+        <v>7034189</v>
       </c>
       <c r="S245" t="n">
         <v>15</v>
@@ -26254,13 +26251,12 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
-      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>Bördigt och örtrikt bäckdråg</t>
+          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
         </is>
       </c>
       <c r="AT245" t="inlineStr"/>
@@ -26278,45 +26274,48 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127127145</v>
+        <v>127126133</v>
       </c>
       <c r="B246" t="n">
-        <v>96708</v>
+        <v>91795</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478533</v>
+        <v>478610</v>
       </c>
       <c r="R246" t="n">
-        <v>7034189</v>
+        <v>7034420</v>
       </c>
       <c r="S246" t="n">
         <v>15</v>
@@ -26357,12 +26356,13 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
+      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
+          <t>Bördigt och örtrikt bäckdråg</t>
         </is>
       </c>
       <c r="AT246" t="inlineStr"/>
@@ -26383,7 +26383,7 @@
         <v>127122571</v>
       </c>
       <c r="B247" t="n">
-        <v>92627</v>
+        <v>92630</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>127122401</v>
       </c>
       <c r="B248" t="n">
-        <v>90875</v>
+        <v>90878</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>127122277</v>
       </c>
       <c r="B249" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26069,7 +26069,7 @@
         <v>127123931</v>
       </c>
       <c r="B244" t="n">
-        <v>79997</v>
+        <v>80003</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26172,45 +26172,48 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127127145</v>
+        <v>127126133</v>
       </c>
       <c r="B245" t="n">
-        <v>96711</v>
+        <v>91803</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478533</v>
+        <v>478610</v>
       </c>
       <c r="R245" t="n">
-        <v>7034189</v>
+        <v>7034420</v>
       </c>
       <c r="S245" t="n">
         <v>15</v>
@@ -26251,12 +26254,13 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
+          <t>Bördigt och örtrikt bäckdråg</t>
         </is>
       </c>
       <c r="AT245" t="inlineStr"/>
@@ -26274,48 +26278,45 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127126133</v>
+        <v>127127145</v>
       </c>
       <c r="B246" t="n">
-        <v>91795</v>
+        <v>96719</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478610</v>
+        <v>478533</v>
       </c>
       <c r="R246" t="n">
-        <v>7034420</v>
+        <v>7034189</v>
       </c>
       <c r="S246" t="n">
         <v>15</v>
@@ -26356,13 +26357,12 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>Bördigt och örtrikt bäckdråg</t>
+          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
         </is>
       </c>
       <c r="AT246" t="inlineStr"/>
@@ -26383,7 +26383,7 @@
         <v>127122571</v>
       </c>
       <c r="B247" t="n">
-        <v>92630</v>
+        <v>92638</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>127122401</v>
       </c>
       <c r="B248" t="n">
-        <v>90878</v>
+        <v>90886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>127122277</v>
       </c>
       <c r="B249" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY277"/>
+  <dimension ref="A1:AY280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26698,53 +26698,51 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>111901519</v>
+        <v>128562104</v>
       </c>
       <c r="B250" t="n">
-        <v>86371</v>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>86774</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>4412</v>
+        <v>248952</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blåfotad fagerspindling</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Cortinarius barbaricus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Brandrud) Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>477765</v>
+        <v>478897</v>
       </c>
       <c r="R250" t="n">
-        <v>7033404</v>
+        <v>7034253</v>
       </c>
       <c r="S250" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -26768,12 +26766,17 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>Ska mikras</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -26782,75 +26785,75 @@
       <c r="AE250" t="b">
         <v>0</v>
       </c>
+      <c r="AF250" t="inlineStr"/>
       <c r="AG250" t="b">
         <v>0</v>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>Friskt bäckdråg</t>
+        </is>
       </c>
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>111901546</v>
+        <v>128562098</v>
       </c>
       <c r="B251" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>86808</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>100109</v>
+        <v>445</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr"/>
       <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>477668</v>
+        <v>478897</v>
       </c>
       <c r="R251" t="n">
-        <v>7033374</v>
+        <v>7034253</v>
       </c>
       <c r="S251" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -26874,17 +26877,12 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -26893,75 +26891,75 @@
       <c r="AE251" t="b">
         <v>0</v>
       </c>
+      <c r="AF251" t="inlineStr"/>
       <c r="AG251" t="b">
         <v>0</v>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>Friskt bäckdråg</t>
+        </is>
       </c>
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>111901547</v>
+        <v>128562339</v>
       </c>
       <c r="B252" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92741</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>100109</v>
+        <v>1435</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
-      <c r="M252" t="inlineStr"/>
       <c r="N252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Landvågen, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>477524</v>
+        <v>478831</v>
       </c>
       <c r="R252" t="n">
-        <v>7033330</v>
+        <v>7034176</v>
       </c>
       <c r="S252" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -26985,17 +26983,12 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -27004,28 +26997,34 @@
       <c r="AE252" t="b">
         <v>0</v>
       </c>
+      <c r="AF252" t="inlineStr"/>
       <c r="AG252" t="b">
         <v>0</v>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>Friskt bäckdråg</t>
+        </is>
       </c>
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>111901551</v>
+        <v>111901519</v>
       </c>
       <c r="B253" t="n">
-        <v>56430</v>
+        <v>86371</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -27038,38 +27037,34 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr"/>
-      <c r="N253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>477433</v>
+        <v>477765</v>
       </c>
       <c r="R253" t="n">
-        <v>7033429</v>
+        <v>7033404</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -27102,11 +27097,6 @@
       <c r="AA253" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -27133,10 +27123,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>111901518</v>
+        <v>111901546</v>
       </c>
       <c r="B254" t="n">
-        <v>86371</v>
+        <v>56430</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -27149,34 +27139,38 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>477674</v>
+        <v>477668</v>
       </c>
       <c r="R254" t="n">
-        <v>7033500</v>
+        <v>7033374</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -27209,6 +27203,11 @@
       <c r="AA254" t="inlineStr">
         <is>
           <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -27235,10 +27234,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>111901587</v>
+        <v>111901547</v>
       </c>
       <c r="B255" t="n">
-        <v>56575</v>
+        <v>56430</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -27251,46 +27250,38 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr"/>
       <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>477611</v>
+        <v>477524</v>
       </c>
       <c r="R255" t="n">
-        <v>7033311</v>
+        <v>7033330</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -27323,6 +27314,11 @@
       <c r="AA255" t="inlineStr">
         <is>
           <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -27349,7 +27345,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>111901548</v>
+        <v>111901551</v>
       </c>
       <c r="B256" t="n">
         <v>56430</v>
@@ -27393,10 +27389,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>477476</v>
+        <v>477433</v>
       </c>
       <c r="R256" t="n">
-        <v>7033385</v>
+        <v>7033429</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -27433,7 +27429,7 @@
       </c>
       <c r="AC256" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -27460,10 +27456,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>111901618</v>
+        <v>111901518</v>
       </c>
       <c r="B257" t="n">
-        <v>85197</v>
+        <v>86371</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -27476,21 +27472,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>249278</v>
+        <v>4412</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -27500,10 +27496,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>477471</v>
+        <v>477674</v>
       </c>
       <c r="R257" t="n">
-        <v>7033412</v>
+        <v>7033500</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27562,10 +27558,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>111901549</v>
+        <v>111901587</v>
       </c>
       <c r="B258" t="n">
-        <v>56430</v>
+        <v>56575</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -27578,38 +27574,46 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>477464</v>
+        <v>477611</v>
       </c>
       <c r="R258" t="n">
-        <v>7033364</v>
+        <v>7033311</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27642,11 +27646,6 @@
       <c r="AA258" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC258" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -27673,7 +27672,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>111901544</v>
+        <v>111901548</v>
       </c>
       <c r="B259" t="n">
         <v>56430</v>
@@ -27717,10 +27716,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>477639</v>
+        <v>477476</v>
       </c>
       <c r="R259" t="n">
-        <v>7033515</v>
+        <v>7033385</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27784,10 +27783,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>111901550</v>
+        <v>111901618</v>
       </c>
       <c r="B260" t="n">
-        <v>56430</v>
+        <v>85197</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27800,38 +27799,34 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>100109</v>
+        <v>249278</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
           <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>477473</v>
+        <v>477471</v>
       </c>
       <c r="R260" t="n">
-        <v>7033404</v>
+        <v>7033412</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27864,11 +27859,6 @@
       <c r="AA260" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -27895,7 +27885,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>111901545</v>
+        <v>111901549</v>
       </c>
       <c r="B261" t="n">
         <v>56430</v>
@@ -27939,10 +27929,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>477667</v>
+        <v>477464</v>
       </c>
       <c r="R261" t="n">
-        <v>7033500</v>
+        <v>7033364</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27979,7 +27969,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -28006,10 +27996,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>117085837</v>
+        <v>111901544</v>
       </c>
       <c r="B262" t="n">
-        <v>90463</v>
+        <v>56430</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -28022,37 +28012,41 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>477402</v>
+        <v>477639</v>
       </c>
       <c r="R262" t="n">
-        <v>7033066</v>
+        <v>7033515</v>
       </c>
       <c r="S262" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -28076,12 +28070,17 @@
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -28096,22 +28095,22 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>117130130</v>
+        <v>111901550</v>
       </c>
       <c r="B263" t="n">
-        <v>91236</v>
+        <v>56430</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -28120,44 +28119,45 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>717</v>
+        <v>100109</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
       <c r="N263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Stenbäcken, Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>477651</v>
+        <v>477473</v>
       </c>
       <c r="R263" t="n">
-        <v>7033403</v>
+        <v>7033404</v>
       </c>
       <c r="S263" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -28181,17 +28181,17 @@
       </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>På levande asp. Trötta fruktkroppar.</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -28200,29 +28200,28 @@
       <c r="AE263" t="b">
         <v>0</v>
       </c>
-      <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>117792165</v>
+        <v>111901545</v>
       </c>
       <c r="B264" t="n">
-        <v>90503</v>
+        <v>56430</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -28235,37 +28234,41 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Landvågen, Jmt</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>477450</v>
+        <v>477667</v>
       </c>
       <c r="R264" t="n">
-        <v>7033406</v>
+        <v>7033500</v>
       </c>
       <c r="S264" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -28289,12 +28292,17 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -28309,22 +28317,22 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>118701501</v>
+        <v>117085837</v>
       </c>
       <c r="B265" t="n">
-        <v>97856</v>
+        <v>90463</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -28337,34 +28345,34 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>620</v>
+        <v>1202</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>477755</v>
+        <v>477402</v>
       </c>
       <c r="R265" t="n">
-        <v>7033301</v>
+        <v>7033066</v>
       </c>
       <c r="S265" t="n">
         <v>20</v>
@@ -28391,12 +28399,12 @@
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -28423,10 +28431,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>118703040</v>
+        <v>117130130</v>
       </c>
       <c r="B266" t="n">
-        <v>91803</v>
+        <v>91236</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -28435,41 +28443,44 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>4366</v>
+        <v>717</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>477689</v>
+        <v>477651</v>
       </c>
       <c r="R266" t="n">
-        <v>7033262</v>
+        <v>7033403</v>
       </c>
       <c r="S266" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -28493,12 +28504,17 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>På levande asp. Trötta fruktkroppar.</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -28507,6 +28523,7 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
+      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
       </c>
@@ -28525,10 +28542,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>118861806</v>
+        <v>117792165</v>
       </c>
       <c r="B267" t="n">
-        <v>91776</v>
+        <v>90503</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -28541,34 +28558,34 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>1968</v>
+        <v>1202</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>477318</v>
+        <v>477450</v>
       </c>
       <c r="R267" t="n">
-        <v>7033069</v>
+        <v>7033406</v>
       </c>
       <c r="S267" t="n">
         <v>20</v>
@@ -28595,12 +28612,12 @@
       </c>
       <c r="Y267" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -28627,10 +28644,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>119048941</v>
+        <v>118701501</v>
       </c>
       <c r="B268" t="n">
-        <v>87388</v>
+        <v>97856</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -28643,34 +28660,34 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>4412</v>
+        <v>620</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>477338</v>
+        <v>477755</v>
       </c>
       <c r="R268" t="n">
-        <v>7033068</v>
+        <v>7033301</v>
       </c>
       <c r="S268" t="n">
         <v>20</v>
@@ -28697,12 +28714,12 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28729,10 +28746,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>119048382</v>
+        <v>118703040</v>
       </c>
       <c r="B269" t="n">
-        <v>91807</v>
+        <v>91803</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -28741,25 +28758,25 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>1968</v>
+        <v>4366</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -28769,10 +28786,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>477617</v>
+        <v>477689</v>
       </c>
       <c r="R269" t="n">
-        <v>7033532</v>
+        <v>7033262</v>
       </c>
       <c r="S269" t="n">
         <v>20</v>
@@ -28799,12 +28816,12 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -28831,10 +28848,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>119221941</v>
+        <v>118861806</v>
       </c>
       <c r="B270" t="n">
-        <v>84007</v>
+        <v>91776</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28847,34 +28864,34 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>5589</v>
+        <v>1968</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>477845</v>
+        <v>477318</v>
       </c>
       <c r="R270" t="n">
-        <v>7033413</v>
+        <v>7033069</v>
       </c>
       <c r="S270" t="n">
         <v>20</v>
@@ -28901,12 +28918,12 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -28933,10 +28950,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>121241556</v>
+        <v>119048941</v>
       </c>
       <c r="B271" t="n">
-        <v>79198</v>
+        <v>87388</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28949,40 +28966,37 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>229821</v>
+        <v>4412</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Stenbäcken, Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>478098</v>
+        <v>477338</v>
       </c>
       <c r="R271" t="n">
-        <v>7033575</v>
+        <v>7033068</v>
       </c>
       <c r="S271" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -29006,12 +29020,12 @@
       </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -29020,7 +29034,6 @@
       <c r="AE271" t="b">
         <v>0</v>
       </c>
-      <c r="AF271" t="inlineStr"/>
       <c r="AG271" t="b">
         <v>0</v>
       </c>
@@ -29039,10 +29052,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>117448064</v>
+        <v>119048382</v>
       </c>
       <c r="B272" t="n">
-        <v>90497</v>
+        <v>91807</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -29055,34 +29068,34 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>477365</v>
+        <v>477617</v>
       </c>
       <c r="R272" t="n">
-        <v>7032988</v>
+        <v>7033532</v>
       </c>
       <c r="S272" t="n">
         <v>20</v>
@@ -29109,12 +29122,12 @@
       </c>
       <c r="Y272" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-08-11</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -29141,10 +29154,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>117448244</v>
+        <v>119221941</v>
       </c>
       <c r="B273" t="n">
-        <v>90519</v>
+        <v>84007</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -29157,34 +29170,34 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>5432</v>
+        <v>5589</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>477439</v>
+        <v>477845</v>
       </c>
       <c r="R273" t="n">
-        <v>7033047</v>
+        <v>7033413</v>
       </c>
       <c r="S273" t="n">
         <v>20</v>
@@ -29211,12 +29224,12 @@
       </c>
       <c r="Y273" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -29243,10 +29256,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>118414846</v>
+        <v>121241556</v>
       </c>
       <c r="B274" t="n">
-        <v>91800</v>
+        <v>79198</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -29255,25 +29268,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>4366</v>
+        <v>229821</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -29282,17 +29295,17 @@
       <c r="N274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Klingvågen (Klingvågen), Jmt</t>
+          <t>Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>477357</v>
+        <v>478098</v>
       </c>
       <c r="R274" t="n">
-        <v>7033041</v>
+        <v>7033575</v>
       </c>
       <c r="S274" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -29316,17 +29329,12 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -29354,10 +29362,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>118414787</v>
+        <v>117448064</v>
       </c>
       <c r="B275" t="n">
-        <v>90509</v>
+        <v>90497</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -29394,10 +29402,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>477367</v>
+        <v>477365</v>
       </c>
       <c r="R275" t="n">
-        <v>7032995</v>
+        <v>7032988</v>
       </c>
       <c r="S275" t="n">
         <v>20</v>
@@ -29424,12 +29432,12 @@
       </c>
       <c r="Y275" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -29456,10 +29464,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>118702006</v>
+        <v>117448244</v>
       </c>
       <c r="B276" t="n">
-        <v>91776</v>
+        <v>90519</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -29472,21 +29480,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>1968</v>
+        <v>5432</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -29496,10 +29504,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>477332</v>
+        <v>477439</v>
       </c>
       <c r="R276" t="n">
-        <v>7033029</v>
+        <v>7033047</v>
       </c>
       <c r="S276" t="n">
         <v>20</v>
@@ -29526,12 +29534,12 @@
       </c>
       <c r="Y276" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -29558,10 +29566,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>119477054</v>
+        <v>118414846</v>
       </c>
       <c r="B277" t="n">
-        <v>91883</v>
+        <v>91800</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -29570,38 +29578,41 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>5448</v>
+        <v>4366</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Klingvågen, Klingvågen, Jmt</t>
+          <t>Klingvågen (Klingvågen), Jmt</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>477342</v>
+        <v>477357</v>
       </c>
       <c r="R277" t="n">
-        <v>7033020</v>
+        <v>7033041</v>
       </c>
       <c r="S277" t="n">
         <v>20</v>
@@ -29628,12 +29639,17 @@
       </c>
       <c r="Y277" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -29642,6 +29658,7 @@
       <c r="AE277" t="b">
         <v>0</v>
       </c>
+      <c r="AF277" t="inlineStr"/>
       <c r="AG277" t="b">
         <v>0</v>
       </c>
@@ -29657,6 +29674,312 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>118414787</v>
+      </c>
+      <c r="B278" t="n">
+        <v>90509</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>Klingvågen (Klingvågen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q278" t="n">
+        <v>477367</v>
+      </c>
+      <c r="R278" t="n">
+        <v>7032995</v>
+      </c>
+      <c r="S278" t="n">
+        <v>20</v>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AD278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT278" t="inlineStr"/>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>118702006</v>
+      </c>
+      <c r="B279" t="n">
+        <v>91776</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Bankera violascens</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>Klingvågen (Klingvågen), Jmt</t>
+        </is>
+      </c>
+      <c r="Q279" t="n">
+        <v>477332</v>
+      </c>
+      <c r="R279" t="n">
+        <v>7033029</v>
+      </c>
+      <c r="S279" t="n">
+        <v>20</v>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT279" t="inlineStr"/>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>119477054</v>
+      </c>
+      <c r="B280" t="n">
+        <v>91883</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Klingvågen, Klingvågen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q280" t="n">
+        <v>477342</v>
+      </c>
+      <c r="R280" t="n">
+        <v>7033020</v>
+      </c>
+      <c r="S280" t="n">
+        <v>20</v>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AD280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT280" t="inlineStr"/>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26701,7 +26701,7 @@
         <v>128562104</v>
       </c>
       <c r="B250" t="n">
-        <v>86774</v>
+        <v>86778</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>128562098</v>
       </c>
       <c r="B251" t="n">
-        <v>86808</v>
+        <v>86812</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>128562339</v>
       </c>
       <c r="B252" t="n">
-        <v>92741</v>
+        <v>92747</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26701,7 +26701,7 @@
         <v>128562104</v>
       </c>
       <c r="B250" t="n">
-        <v>86778</v>
+        <v>86784</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>128562098</v>
       </c>
       <c r="B251" t="n">
-        <v>86812</v>
+        <v>86818</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>128562339</v>
       </c>
       <c r="B252" t="n">
-        <v>92747</v>
+        <v>92753</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26701,7 +26701,7 @@
         <v>128562104</v>
       </c>
       <c r="B250" t="n">
-        <v>86784</v>
+        <v>86786</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>128562098</v>
       </c>
       <c r="B251" t="n">
-        <v>86818</v>
+        <v>86820</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>128562339</v>
       </c>
       <c r="B252" t="n">
-        <v>92753</v>
+        <v>92755</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26918,7 +26918,7 @@
         <v>128562339</v>
       </c>
       <c r="B252" t="n">
-        <v>92755</v>
+        <v>92756</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26701,7 +26701,7 @@
         <v>128562104</v>
       </c>
       <c r="B250" t="n">
-        <v>86786</v>
+        <v>86813</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>128562098</v>
       </c>
       <c r="B251" t="n">
-        <v>86820</v>
+        <v>86847</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>128562339</v>
       </c>
       <c r="B252" t="n">
-        <v>92756</v>
+        <v>92783</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26701,7 +26701,7 @@
         <v>128562104</v>
       </c>
       <c r="B250" t="n">
-        <v>86813</v>
+        <v>86817</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>128562098</v>
       </c>
       <c r="B251" t="n">
-        <v>86847</v>
+        <v>86851</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>128562339</v>
       </c>
       <c r="B252" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26698,10 +26698,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128562104</v>
+        <v>128562098</v>
       </c>
       <c r="B250" t="n">
-        <v>86817</v>
+        <v>86851</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26709,21 +26709,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>248952</v>
+        <v>445</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Brandrud) Frøslev &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -26774,11 +26774,6 @@
           <t>2025-09-20</t>
         </is>
       </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>Ska mikras</t>
-        </is>
-      </c>
       <c r="AD250" t="b">
         <v>0</v>
       </c>
@@ -26809,10 +26804,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128562098</v>
+        <v>128562339</v>
       </c>
       <c r="B251" t="n">
-        <v>86851</v>
+        <v>92793</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26820,21 +26815,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>445</v>
+        <v>1435</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -26847,10 +26842,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>478897</v>
+        <v>478831</v>
       </c>
       <c r="R251" t="n">
-        <v>7034253</v>
+        <v>7034176</v>
       </c>
       <c r="S251" t="n">
         <v>15</v>
@@ -26915,10 +26910,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128562339</v>
+        <v>128562104</v>
       </c>
       <c r="B252" t="n">
-        <v>92788</v>
+        <v>86817</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -26926,21 +26921,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1435</v>
+        <v>248952</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Blåfotad fagerspindling</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Cortinarius barbaricus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Brandrud) Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -26953,10 +26948,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>478831</v>
+        <v>478897</v>
       </c>
       <c r="R252" t="n">
-        <v>7034176</v>
+        <v>7034253</v>
       </c>
       <c r="S252" t="n">
         <v>15</v>
@@ -26991,19 +26986,28 @@
           <t>2025-09-20</t>
         </is>
       </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>Konsekvent stora, citronformade sporer</t>
+        </is>
+      </c>
       <c r="AD252" t="b">
         <v>0</v>
       </c>
       <c r="AE252" t="b">
         <v>0</v>
       </c>
-      <c r="AF252" t="inlineStr"/>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG252" t="b">
         <v>0</v>
       </c>
       <c r="AI252" t="inlineStr">
         <is>
-          <t>Friskt bäckdråg</t>
+          <t>Friskt bäckdråg i kalkgranskog</t>
         </is>
       </c>
       <c r="AT252" t="inlineStr"/>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26701,7 +26701,7 @@
         <v>128562098</v>
       </c>
       <c r="B250" t="n">
-        <v>86851</v>
+        <v>86855</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>128562339</v>
       </c>
       <c r="B251" t="n">
-        <v>92793</v>
+        <v>92797</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>128562104</v>
       </c>
       <c r="B252" t="n">
-        <v>86817</v>
+        <v>86821</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26701,7 +26701,7 @@
         <v>128562098</v>
       </c>
       <c r="B250" t="n">
-        <v>86855</v>
+        <v>86860</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>128562339</v>
       </c>
       <c r="B251" t="n">
-        <v>92797</v>
+        <v>92802</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>128562104</v>
       </c>
       <c r="B252" t="n">
-        <v>86821</v>
+        <v>86826</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26701,7 +26701,7 @@
         <v>128562098</v>
       </c>
       <c r="B250" t="n">
-        <v>86862</v>
+        <v>86867</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>128562339</v>
       </c>
       <c r="B251" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26913,7 +26913,7 @@
         <v>128562104</v>
       </c>
       <c r="B252" t="n">
-        <v>86833</v>
+        <v>86836</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26701,7 +26701,7 @@
         <v>128562098</v>
       </c>
       <c r="B250" t="n">
-        <v>86867</v>
+        <v>86873</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>128562339</v>
       </c>
       <c r="B251" t="n">
-        <v>92810</v>
+        <v>92818</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>128562104</v>
       </c>
       <c r="B252" t="n">
-        <v>86836</v>
+        <v>86839</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26913,7 +26913,7 @@
         <v>128562104</v>
       </c>
       <c r="B252" t="n">
-        <v>86839</v>
+        <v>86843</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26913,7 +26913,7 @@
         <v>128562104</v>
       </c>
       <c r="B252" t="n">
-        <v>86843</v>
+        <v>86850</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26913,7 +26913,7 @@
         <v>128562104</v>
       </c>
       <c r="B252" t="n">
-        <v>86850</v>
+        <v>86852</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26913,7 +26913,7 @@
         <v>128562104</v>
       </c>
       <c r="B252" t="n">
-        <v>86852</v>
+        <v>86853</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26913,7 +26913,7 @@
         <v>128562104</v>
       </c>
       <c r="B252" t="n">
-        <v>86853</v>
+        <v>86856</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26913,7 +26913,7 @@
         <v>128562104</v>
       </c>
       <c r="B252" t="n">
-        <v>86856</v>
+        <v>86858</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -26069,7 +26069,7 @@
         <v>127123931</v>
       </c>
       <c r="B244" t="n">
-        <v>80003</v>
+        <v>79985</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26172,48 +26172,45 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127126133</v>
+        <v>127127145</v>
       </c>
       <c r="B245" t="n">
-        <v>91803</v>
+        <v>96689</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478610</v>
+        <v>478533</v>
       </c>
       <c r="R245" t="n">
-        <v>7034420</v>
+        <v>7034189</v>
       </c>
       <c r="S245" t="n">
         <v>15</v>
@@ -26254,13 +26251,12 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
-      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>Bördigt och örtrikt bäckdråg</t>
+          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
         </is>
       </c>
       <c r="AT245" t="inlineStr"/>
@@ -26278,45 +26274,48 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127127145</v>
+        <v>127126133</v>
       </c>
       <c r="B246" t="n">
-        <v>96719</v>
+        <v>91773</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478533</v>
+        <v>478610</v>
       </c>
       <c r="R246" t="n">
-        <v>7034189</v>
+        <v>7034420</v>
       </c>
       <c r="S246" t="n">
         <v>15</v>
@@ -26357,12 +26356,13 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
+      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
+          <t>Bördigt och örtrikt bäckdråg</t>
         </is>
       </c>
       <c r="AT246" t="inlineStr"/>
@@ -26383,7 +26383,7 @@
         <v>127122571</v>
       </c>
       <c r="B247" t="n">
-        <v>92638</v>
+        <v>92608</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>127122401</v>
       </c>
       <c r="B248" t="n">
-        <v>90886</v>
+        <v>90856</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>127122277</v>
       </c>
       <c r="B249" t="n">
-        <v>92631</v>
+        <v>92601</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -26069,7 +26069,7 @@
         <v>127123931</v>
       </c>
       <c r="B244" t="n">
-        <v>79985</v>
+        <v>80003</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26172,45 +26172,48 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>127127145</v>
+        <v>127126133</v>
       </c>
       <c r="B245" t="n">
-        <v>96689</v>
+        <v>91803</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478533</v>
+        <v>478610</v>
       </c>
       <c r="R245" t="n">
-        <v>7034189</v>
+        <v>7034420</v>
       </c>
       <c r="S245" t="n">
         <v>15</v>
@@ -26251,12 +26254,13 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
+          <t>Bördigt och örtrikt bäckdråg</t>
         </is>
       </c>
       <c r="AT245" t="inlineStr"/>
@@ -26274,48 +26278,45 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>127126133</v>
+        <v>127127145</v>
       </c>
       <c r="B246" t="n">
-        <v>91773</v>
+        <v>96719</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478610</v>
+        <v>478533</v>
       </c>
       <c r="R246" t="n">
-        <v>7034420</v>
+        <v>7034189</v>
       </c>
       <c r="S246" t="n">
         <v>15</v>
@@ -26356,13 +26357,12 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>Bördigt och örtrikt bäckdråg</t>
+          <t>Örtrik och bördig gransumpskog med inslag av sälg</t>
         </is>
       </c>
       <c r="AT246" t="inlineStr"/>
@@ -26383,7 +26383,7 @@
         <v>127122571</v>
       </c>
       <c r="B247" t="n">
-        <v>92608</v>
+        <v>92638</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>127122401</v>
       </c>
       <c r="B248" t="n">
-        <v>90856</v>
+        <v>90886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>127122277</v>
       </c>
       <c r="B249" t="n">
-        <v>92601</v>
+        <v>92631</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY299"/>
+  <dimension ref="A1:AZ299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269159</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117079707</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127127145</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117786220</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117919197</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930145</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118409948</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117787185</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117791069</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118417044</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125652112</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1863,6 +1923,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120224045</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1969,6 +2034,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127123931</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225839</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2163,6 +2238,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225844</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2260,6 +2340,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225874</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2357,6 +2442,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119927395</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2454,6 +2544,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225864</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2551,6 +2646,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119926530</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2648,6 +2748,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120222779</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2754,6 +2859,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128562098</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2860,6 +2970,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119475515</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2966,6 +3081,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110968033</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3072,6 +3192,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117228332</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3183,6 +3308,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117444330</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3280,6 +3410,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117791178</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3377,6 +3512,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118417219</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3481,6 +3621,11 @@
       <c r="AY29" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6768184</t>
         </is>
       </c>
     </row>
@@ -3585,6 +3730,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113266325</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3692,6 +3842,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117075700</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3799,6 +3954,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117444567</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3896,6 +4056,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117786555</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3998,6 +4163,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125653096</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4095,6 +4265,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117076709</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4192,6 +4367,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117080856</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4289,6 +4469,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117918578</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4386,6 +4571,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118700473</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4483,6 +4673,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118699023</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4585,6 +4780,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118700504</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4682,6 +4882,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118701025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4779,6 +4984,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119053337</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4876,6 +5086,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117078381</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4973,6 +5188,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117790354</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5089,6 +5309,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125654473</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5190,6 +5415,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117787692</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5289,6 +5519,11 @@
       <c r="AY47" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269160</t>
         </is>
       </c>
     </row>
@@ -5392,6 +5627,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113419329</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5489,6 +5729,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117227533</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5586,6 +5831,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117228580</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5683,6 +5933,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117787893</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5784,6 +6039,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269208</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5881,6 +6141,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117228593</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5978,6 +6243,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117442455</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6079,6 +6349,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117546456</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6176,6 +6451,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117790359</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6281,6 +6561,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269157</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6387,6 +6672,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127126133</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6488,6 +6778,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113408220</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6585,6 +6880,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117787464</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6686,6 +6986,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241528</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6792,6 +7097,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219738</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6889,6 +7199,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119220292</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6986,6 +7301,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119225816</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7083,6 +7403,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119927771</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7180,6 +7505,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120219366</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7286,6 +7616,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127122571</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7392,6 +7727,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128562339</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7489,6 +7829,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119220976</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7586,6 +7931,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119224034</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7683,6 +8033,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119225825</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7780,6 +8135,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119328581</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7877,6 +8237,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225847</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7974,6 +8339,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225857</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8071,6 +8441,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225872</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8168,6 +8543,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118858244</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8269,6 +8649,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117546452</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8385,6 +8770,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/751525</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8486,6 +8876,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269203</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8583,6 +8978,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225835</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8688,6 +9088,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117919042</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8785,6 +9190,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117787304</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8882,6 +9292,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118697497</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8979,6 +9394,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225818</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9076,6 +9496,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225842</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9173,6 +9598,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225862</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9281,6 +9711,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112102606</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9378,6 +9813,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119053044</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9484,6 +9924,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119473822</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9577,6 +10022,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225841</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9670,6 +10120,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225849</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9763,6 +10218,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225852</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9856,6 +10316,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225855</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9953,6 +10418,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119474691</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10050,6 +10520,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119927209</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10147,6 +10622,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930975</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10253,6 +10733,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127122277</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10350,6 +10835,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225843</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10447,6 +10937,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119051484</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10544,6 +11039,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119931445</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10641,6 +11141,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118854549</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10738,6 +11243,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225824</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10835,6 +11345,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225828</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10932,6 +11447,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225838</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11029,6 +11549,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119330421</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11126,6 +11651,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119926437</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11223,6 +11753,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225816</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11320,6 +11855,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225827</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11417,6 +11957,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225832</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11514,6 +12059,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225866</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11611,6 +12161,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225883</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11708,6 +12263,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225888</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11805,6 +12365,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225895</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11906,6 +12471,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269214</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12007,6 +12577,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113006309</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12108,6 +12683,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113006313</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12205,6 +12785,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225817</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12302,6 +12887,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225819</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12399,6 +12989,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225822</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12496,6 +13091,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225845</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12593,6 +13193,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225850</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12690,6 +13295,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225854</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12787,6 +13397,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225856</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12884,6 +13499,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225861</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12981,6 +13601,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225868</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13078,6 +13703,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225871</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13175,6 +13805,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225875</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13272,6 +13907,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225876</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13369,6 +14009,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225882</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13466,6 +14111,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225886</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13563,6 +14213,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225887</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13660,6 +14315,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225893</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13757,6 +14417,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225897</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13854,6 +14519,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118854701</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13951,6 +14621,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225825</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14048,6 +14723,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225884</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14145,6 +14825,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119469453</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14261,6 +14946,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125536112</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14362,6 +15052,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269162</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14459,6 +15154,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118696189</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14556,6 +15256,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118696519</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14653,6 +15358,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118700665</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14750,6 +15460,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118700794</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14847,6 +15562,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119047541</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14944,6 +15664,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119050745</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15041,6 +15766,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119053131</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15138,6 +15868,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119220053</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15235,6 +15970,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119224645</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15332,6 +16072,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119328587</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15429,6 +16174,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225865</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15526,6 +16276,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119220135</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15623,6 +16378,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119472835</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15729,6 +16489,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127122401</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15830,6 +16595,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118698422</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15931,6 +16701,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113006308</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16028,6 +16803,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225848</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16125,6 +16905,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225853</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16222,6 +17007,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225858</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16319,6 +17109,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225881</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16416,6 +17211,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225894</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16517,6 +17317,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119045477</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16614,6 +17419,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119330001</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16715,6 +17525,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269170</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16812,6 +17627,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225820</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16909,6 +17729,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225829</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17011,6 +17836,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225869</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17113,6 +17943,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225877</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17215,6 +18050,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225896</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17317,6 +18157,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125652823</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17418,6 +18263,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113408219</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17524,6 +18374,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125652111</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17625,6 +18480,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269190</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17727,6 +18587,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125654533</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17841,6 +18706,11 @@
       <c r="AY174" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1920559</t>
         </is>
       </c>
     </row>
@@ -17963,6 +18833,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269194</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18083,6 +18958,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269196</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18203,6 +19083,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269197</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18300,6 +19185,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901596</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18401,6 +19291,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113006321</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18502,6 +19397,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113006322</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18614,6 +19514,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225836</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18731,6 +19636,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225870</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18828,6 +19738,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117920532</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18934,6 +19849,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125652229</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19031,6 +19951,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118699891</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19147,6 +20072,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2027785</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19251,6 +20181,11 @@
       <c r="AY187" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269166</t>
         </is>
       </c>
     </row>
@@ -19373,6 +20308,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269193</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19474,6 +20414,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269200</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19575,6 +20520,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113006314</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19676,6 +20626,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269220</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19792,6 +20747,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1953256</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19899,6 +20859,11 @@
       <c r="AY193" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269225</t>
         </is>
       </c>
     </row>
@@ -20007,6 +20972,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901584</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20113,6 +21083,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901585</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20220,6 +21195,11 @@
       <c r="AY196" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113006310</t>
         </is>
       </c>
     </row>
@@ -20323,6 +21303,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120211708</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20420,6 +21405,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225873</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20525,6 +21515,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114476706</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20622,6 +21617,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225834</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20719,6 +21719,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117787276</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20816,6 +21821,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118697531</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20917,6 +21927,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269223</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21018,6 +22033,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269228</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21115,6 +22135,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118410708</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21216,6 +22241,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269167</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21317,6 +22347,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269202</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21418,6 +22453,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269217</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21519,6 +22559,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269221</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21620,6 +22665,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269222</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21721,6 +22771,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269235</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21822,6 +22877,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269238</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21919,6 +22979,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117787268</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22020,6 +23085,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269172</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22121,6 +23191,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269180</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22222,6 +23297,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269182</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22323,6 +23403,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269198</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22424,6 +23509,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269212</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22535,6 +23625,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2448901</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22632,6 +23727,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117787324</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22729,6 +23829,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118409601</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22830,6 +23935,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269168</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22931,6 +24041,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269169</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23032,6 +24147,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269188</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -23146,6 +24266,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269229</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23257,6 +24382,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4037045</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23354,6 +24484,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117787995</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23451,6 +24586,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117087415</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -23553,6 +24693,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121122098</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23654,6 +24799,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269210</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -23751,6 +24901,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117443188</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -23848,6 +25003,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117787350</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -23949,6 +25109,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269175</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -24050,6 +25215,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269171</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -24151,6 +25321,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269201</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -24252,6 +25427,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269209</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -24353,6 +25533,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269236</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -24450,6 +25635,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225860</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -24547,6 +25737,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225879</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -24658,6 +25853,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5679646</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -24759,6 +25959,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269179</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -24860,6 +26065,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269211</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -24961,6 +26171,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269216</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -25062,6 +26277,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269226</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -25163,6 +26383,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269234</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -25260,6 +26485,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117444345</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -25361,6 +26591,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269178</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -25458,6 +26693,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117788387</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -25559,6 +26799,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269230</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -25656,6 +26901,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119329964</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -25776,6 +27026,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269195</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -25881,6 +27136,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269218</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -25978,6 +27238,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117444411</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -26079,6 +27344,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118698082</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -26176,6 +27446,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119051044</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -26291,6 +27566,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128562104</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -26398,6 +27678,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225821</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -26505,6 +27790,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225833</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -26602,6 +27892,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225880</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -26699,6 +27994,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119927184</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -26800,6 +28100,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269174</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -26897,6 +28202,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901619</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -26999,6 +28309,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225823</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -27096,6 +28411,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119220164</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -27202,6 +28522,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119220331</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -27308,6 +28633,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119223791</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -27414,6 +28744,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119220936</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -27517,6 +28852,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113225890</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -27610,6 +28950,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119051508</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -27707,6 +29052,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118701501</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -27813,6 +29163,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117130130</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -27910,6 +29265,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117085837</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -28007,6 +29367,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117792165</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -28104,6 +29469,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118861806</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -28201,6 +29571,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119048382</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -28302,6 +29677,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119048435</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -28399,6 +29779,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118703040</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -28496,6 +29881,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901518</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -28593,6 +29983,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901519</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -28690,6 +30085,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119048390</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -28787,6 +30187,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119048941</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -28884,6 +30289,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119221941</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -28990,6 +30400,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901544</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -29096,6 +30511,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901545</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -29202,6 +30622,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901546</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -29308,6 +30733,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901547</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -29414,6 +30844,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901548</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -29520,6 +30955,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901549</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -29626,6 +31066,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901550</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -29732,6 +31177,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901551</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -29841,6 +31291,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901587</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -29942,6 +31397,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241556</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -30039,6 +31499,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901618</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -30140,6 +31605,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119048771</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -30237,6 +31707,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117448064</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -30334,6 +31809,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118702006</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -30440,6 +31920,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118414846</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -30537,6 +32022,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119477054</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -30634,8 +32124,313 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118414642</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -2453,7 +2453,7 @@
         <v>136327182</v>
       </c>
       <c r="B19" t="n">
-        <v>87341</v>
+        <v>87347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>136327177</v>
       </c>
       <c r="B24" t="n">
-        <v>87383</v>
+        <v>87389</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136327181</v>
       </c>
       <c r="B25" t="n">
-        <v>87383</v>
+        <v>87389</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>136327187</v>
       </c>
       <c r="B91" t="n">
-        <v>91512</v>
+        <v>91518</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>136328907</v>
       </c>
       <c r="B94" t="n">
-        <v>87385</v>
+        <v>87391</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>136327186</v>
       </c>
       <c r="B106" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>136327171</v>
       </c>
       <c r="B161" t="n">
-        <v>91594</v>
+        <v>91600</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>136327168</v>
       </c>
       <c r="B169" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>136327174</v>
       </c>
       <c r="B264" t="n">
-        <v>90021</v>
+        <v>90027</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>136327185</v>
       </c>
       <c r="B269" t="n">
-        <v>87436</v>
+        <v>87442</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>136327179</v>
       </c>
       <c r="B271" t="n">
-        <v>87468</v>
+        <v>87474</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>136327173</v>
       </c>
       <c r="B279" t="n">
-        <v>87358</v>
+        <v>87364</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>136327175</v>
       </c>
       <c r="B282" t="n">
-        <v>93386</v>
+        <v>93392</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -2453,7 +2453,7 @@
         <v>136327182</v>
       </c>
       <c r="B19" t="n">
-        <v>87347</v>
+        <v>87354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>136327177</v>
       </c>
       <c r="B24" t="n">
-        <v>87389</v>
+        <v>87396</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136327181</v>
       </c>
       <c r="B25" t="n">
-        <v>87389</v>
+        <v>87396</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>136327187</v>
       </c>
       <c r="B91" t="n">
-        <v>91518</v>
+        <v>91525</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>136328907</v>
       </c>
       <c r="B94" t="n">
-        <v>87391</v>
+        <v>87398</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>136327186</v>
       </c>
       <c r="B106" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>136327171</v>
       </c>
       <c r="B161" t="n">
-        <v>91600</v>
+        <v>91607</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>136327168</v>
       </c>
       <c r="B169" t="n">
-        <v>93414</v>
+        <v>93421</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>136327174</v>
       </c>
       <c r="B264" t="n">
-        <v>90027</v>
+        <v>90034</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>136327185</v>
       </c>
       <c r="B269" t="n">
-        <v>87442</v>
+        <v>87449</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>136327179</v>
       </c>
       <c r="B271" t="n">
-        <v>87474</v>
+        <v>87481</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>136327173</v>
       </c>
       <c r="B279" t="n">
-        <v>87364</v>
+        <v>87371</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>136327175</v>
       </c>
       <c r="B282" t="n">
-        <v>93392</v>
+        <v>93399</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -10043,7 +10043,7 @@
         <v>136327187</v>
       </c>
       <c r="B91" t="n">
-        <v>91525</v>
+        <v>91526</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>136327186</v>
       </c>
       <c r="B106" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>136327171</v>
       </c>
       <c r="B161" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>136327168</v>
       </c>
       <c r="B169" t="n">
-        <v>93421</v>
+        <v>93422</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>136327174</v>
       </c>
       <c r="B264" t="n">
-        <v>90034</v>
+        <v>90035</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>136327175</v>
       </c>
       <c r="B282" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -2453,7 +2453,7 @@
         <v>136327182</v>
       </c>
       <c r="B19" t="n">
-        <v>87354</v>
+        <v>87367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>136327177</v>
       </c>
       <c r="B24" t="n">
-        <v>87396</v>
+        <v>87409</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136327181</v>
       </c>
       <c r="B25" t="n">
-        <v>87396</v>
+        <v>87409</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>136327187</v>
       </c>
       <c r="B91" t="n">
-        <v>91526</v>
+        <v>91539</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>136328907</v>
       </c>
       <c r="B94" t="n">
-        <v>87398</v>
+        <v>87411</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>136327186</v>
       </c>
       <c r="B106" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>136327171</v>
       </c>
       <c r="B161" t="n">
-        <v>91608</v>
+        <v>91621</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>136327168</v>
       </c>
       <c r="B169" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>136327174</v>
       </c>
       <c r="B264" t="n">
-        <v>90035</v>
+        <v>90048</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>136327185</v>
       </c>
       <c r="B269" t="n">
-        <v>87449</v>
+        <v>87462</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>136327179</v>
       </c>
       <c r="B271" t="n">
-        <v>87481</v>
+        <v>87494</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>136327173</v>
       </c>
       <c r="B279" t="n">
-        <v>87371</v>
+        <v>87384</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>136327175</v>
       </c>
       <c r="B282" t="n">
-        <v>93400</v>
+        <v>93413</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>

--- a/artfynd/A 29992-2023 artfynd.xlsx
+++ b/artfynd/A 29992-2023 artfynd.xlsx
@@ -2453,7 +2453,7 @@
         <v>136327182</v>
       </c>
       <c r="B19" t="n">
-        <v>87367</v>
+        <v>87368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>136327177</v>
       </c>
       <c r="B24" t="n">
-        <v>87409</v>
+        <v>87410</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>136327181</v>
       </c>
       <c r="B25" t="n">
-        <v>87409</v>
+        <v>87410</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>136327187</v>
       </c>
       <c r="B91" t="n">
-        <v>91539</v>
+        <v>91540</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>136328907</v>
       </c>
       <c r="B94" t="n">
-        <v>87411</v>
+        <v>87412</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>136327186</v>
       </c>
       <c r="B106" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>136327171</v>
       </c>
       <c r="B161" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>136327168</v>
       </c>
       <c r="B169" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>136327174</v>
       </c>
       <c r="B264" t="n">
-        <v>90048</v>
+        <v>90049</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>136327185</v>
       </c>
       <c r="B269" t="n">
-        <v>87462</v>
+        <v>87463</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>136327179</v>
       </c>
       <c r="B271" t="n">
-        <v>87494</v>
+        <v>87495</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>136327173</v>
       </c>
       <c r="B279" t="n">
-        <v>87384</v>
+        <v>87385</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>136327175</v>
       </c>
       <c r="B282" t="n">
-        <v>93413</v>
+        <v>93414</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
